--- a/Датасет.xlsx
+++ b/Датасет.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Влада\Desktop\Учеба\Туристический маршрут\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACDBAA2-5F44-42AD-8485-EE0B4411AD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD03A63-D0D6-4807-931D-01D571419231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5627" uniqueCount="2316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="2873">
   <si>
     <t>place_id</t>
   </si>
@@ -6126,14 +6126,6 @@
     <t>132.924746</t>
   </si>
   <si>
-    <t>Биробиджан
-Биробиджан был основан в 1916 году как станция Тихонькая в рамках освоения земель вокруг Амурской железной дороги. При станции был основан поселок. В 1928 году, после принятия постановления Президиума ЦИК СССР о закреплении за трудящимися евреями свободных земель в Приамурье Тихонькая стала базой приема переселенцев и центром снабжения переселенческого района. В 1931 году поселку было присвоено название Биробиджан – в честь протекающих в нем рек, а в 1937 году он уже стал городом.
-В 1930-х годах Биробиджан активно застраивался и развивался: возникали артели, строились дома, школы, издавались газеты и журналы, работало радио, увеличивалось население. Биробиджан являлся распределительным железнодорожным центром Еврейской автономной области.
-В годы репрессий и Великой Отечественной войны население города сильно пострадало: многие были арестованы и сосланы в лагеря, во время войны ушли на фронт и не вернулись. После войны Биробиджан не избежал гонений в связи с борьбой с космополитизмом.
-Послевоенные репрессии нанесли решающий удар проекту развития Биробиджана как национального центра. Практически прекратилась официальная поддержка инициатив, связанных с развитием и поддержанием еврейской культуры.
-В 1990-е годы подавляющее большинство биробиджанских евреев эмигрировало из России, преимущественно, в Израиль, отчего количество еврейского населения в городе сильно упало. Постепенно стали закрываться городские предприятия. Однако, произошло значительное оживление в развитии еврейской культуры: в городе начали работать еврейские общины, в университете открыта кафедра по изучению идиша, проводятся регулярные фестивали и праздники.</t>
-  </si>
-  <si>
     <t>first_settlers</t>
   </si>
   <si>
@@ -6233,18 +6225,9 @@
     <t>Флаг г. Биробиджана</t>
   </si>
   <si>
-    <t>Проектирование большого Биробиджана. 1932-1934 гг.</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
-    <t>Ударники бригады. Артель "Колесо революции". 1935-1937 гг.</t>
-  </si>
-  <si>
-    <t>Школа. 1935-1937 гг.</t>
-  </si>
-  <si>
     <t>Послевоенные переселенцы</t>
   </si>
   <si>
@@ -6422,34 +6405,18 @@
     <t>Женщина, 1954 г.р., жительница Биробиджана</t>
   </si>
   <si>
-    <t>А до этого я приехала со Ставрополья, тогда было переселение, и мы, как переселенцы, муж, двое детей и я приехали сюда.
-Тут деревня Благословенное называется так.  [СП: В области?]  Да, да, в области, в Еврейской автономной области. Это Октябрьский район, рядом с Амурзетом. Может, знаете Амурзет наш?  [СП: Ну вот вчера были там, посещали.]  Там были?  Да.  Ну вот, вы когда из Амурзета выехали сюда, в Биробиджан, вы проезжали село вот это Благословенное. Вот я там жила. Оно как раз в то время строилось, расстраивалось, улицы новые были, там были сначала деревянные дома, и таких блочных мало было. А потом, когда оно расстроилось, и вот было переселение. Нужны были работники сельского хозяйства, там совхоз был очень богатый, и все села в Октябрьском районе хорошо жили, богатые жили там.</t>
-  </si>
-  <si>
     <t>return_to_JAO</t>
   </si>
   <si>
-    <t>Популярна была шутка:"Когда из Биробиджана будет уезжать последний еврей, на вокзал его провожать придут десять тысяч евреев". Я тоже вернулась из Израиля. Я вернулась, я не могла без Биробиджана.</t>
-  </si>
-  <si>
-    <t>Ну, поехали. [В.Ш: Подскажите, пожалуйста, в каком году вы родились и где?] АС: Я родился в 1956 году, 19 сентября, в городе Биробиджане. [ВШ: В Биробиджане. А родители ваши?] АС: Папа мой родился на Украине. Ну, село Ольховатка, Валуйского района. [ВШ: И приехал сюда в каком году?] АС: Значит, мои родители, мои предки, вот $Пелагея Федотовна/П.Ф.$ и $Степан Васильевич/С.В.$ приехали сюда ориентировочно в &lt;19&gt;35-34 году.</t>
-  </si>
-  <si>
     <t>Мужчина, 1956 г.р., потомок первых переселенцев</t>
   </si>
   <si>
-    <t xml:space="preserve">МА: Нет, в дальневосточных регионах, конечно же, это процент большой, то есть все равно мы коммуницируем. И тут еще на Дальнем Востоке есть большой фактор это семьи, то есть, ну, очень много жителей Еврейской автономной области уезжают в соседние регионы. То есть отток населения у нас продолжается, и, к сожалению, его сложно остановить, когда вот мы посерединке, с одной стороны находится Хабаровск, с другой стороны Благовещенск, два крупных мегаполиса совершенно с другими заработными платами. И они вот высасывают просто людей, в том числе, ну, конечно, большинство молодых людей, когда они поступают в хабаровские ВУЗы, в благовещенские ВУЗы, или там Владивосток, ДВФУ, они остаются там. Но связь вот эта семейная, то есть родители здесь остались, друзья, она сохраняется, и поэтому, конечно, на Дальнем Востоке одна большая семья. </t>
-  </si>
-  <si>
     <t>Мужчина, 1989 г.р., житель Биробджана</t>
   </si>
   <si>
     <t>post_war_settlers</t>
   </si>
   <si>
-    <t>ХТА: С Украины. ПИВ: С Украины, да. Они из Винницкой области. [С обеих линий, получается, приехали?] ПИВ: Папина бабушка с Винницкой области, и баба Соня, по маминой – тоже, по-моему, они отттуда. [А в какое время они, получается, приехали сюда?] ХТА: Во время войны была репатриация. ПИВ: После войны. Там, буквально в сороковые, может, в сорок шестом. Ну, то есть вот-вот, прям совсем. Бабушка была ребёнком маленьким. Она рассказывала, что когда она приехала сюда, она знала только идиш. Её определили в какой-то интернат местный, то есть, соответственно, он никакой не еврейский, обычный, да, интернат для детей. Потому что, ну, просто родителям надо было работать, жить негде было и всё такое. Дети были там недели в интернате, на выходные их забирали домой – такая обычная практика.</t>
-  </si>
-  <si>
     <t>[Ну да, я так понимаю, большая часть все-таки не из еврейских семей, и они никогда не видели идишскую литературу.]   Не, ну если говорить вообще по правде, да, сама, наша область, то коренных-то евреев и было-то не так много, то есть их процентов тридцать от всего населения было. На момент зарождения области, то есть это же вообще переселенцы были из Центральной России, из Белоруссии, из Украины, Казахстан, Узбекистан, то есть очень много. Вот моя бабушка, допустим, она была переселенка с Украины.</t>
   </si>
   <si>
@@ -6462,21 +6429,12 @@
     <t>Одесса</t>
   </si>
   <si>
-    <t>АС: Они в юношеском возрасте уехали, будем так говорить. Не катит, все сюда приехали. В Биробиджане живут. [ВШ: А людей побуждает вернуться вот любовь к Биробиджану или, скорее, какие-то другие факторы?] АС: Значит, есть такая поговорка. Рыба ищет, где глубже, а человек ищет… [ВШ: Где лучше?] АС: Где рыба. &lt;смеется&gt; ВИ: Ну, даже вот мы смотрим пост в интернете, смотрим, что многие же представляют наши фотографии нашего города, и пошла ностальгия. Вот прекрасно все, и столько теплых чувств у людей, но вернуться они не могут. И они живут тем Биробиджаном, который был, когда они уехали. Поэтому это же две большие разницы. Тогда были заводы, тогда во дворах сидели мужчины, играли в домино. АС: Я им только рассказал анекдот. Я им рассказывал уже.</t>
-  </si>
-  <si>
     <t>Мужчина, 1951 г.р., житель Биробиджана</t>
   </si>
   <si>
     <t>Феодосия</t>
   </si>
   <si>
-    <t>А мне-таки есть о чём рассказывать, потому что по линии моей жены её папа приехал сюда в начале тридцатых годов, тридцать первый, тридцать второй год, в посёлке Биракан Еврейской автономной области был еврейский колхоз. Найе Лебен назывался. Новая жизнь. Его родители привезли туда всю свою семью. Его. И он там жил, и рос, и учился. Моя тёща, любимая, ныне, к сожалению, покойная, мир праху её, приехала сюда из Крыма. Вот вам еще одна эпопея еврейской жизни, крымский вариант, Феодосия. Мои дедушка и бабушка по маминой линии приехали сюда из славного города Николаева. Догадываетесь, где это? [Угу.] Да? Да, да. А по папиной линии? Знаменитый город Белая Церковь. То есть вся моя родня как бы показывала маршрутизацию, маршруты, как сюда попали евреи, когда и зачем. То есть мне в этом отношении довольно просто увязывать историю движения еврейского населения на Дальний Восток. Вот это надо знать и надо понимать, что всё это пережито, прочувствованно через свои личные воспоминания, да? И знания.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Значит, я чистокровный еврей, то есть и папа, и мама, они евреи. Значит… Как оказался отец мой на Дальнем Востоке, в Биробиджане. Значит, это как раз, когда организовывали нашу область… Украина. Есть такой славный город Бердичев в Житомирской области. Он уроженец города Бердичева. Значит, и…</t>
-  </si>
-  <si>
     <t>Мужчина, 1947 г.р., потомок первых переселенцев</t>
   </si>
   <si>
@@ -6486,9 +6444,6 @@
     <t>Мужчина, житель Амурзета</t>
   </si>
   <si>
-    <t xml:space="preserve"> [А как папа приехал? Вот как родители приехали в Биробиджан?]  Родители… Ну, папу привезли, это моя бабушка и дедушка – они жили уже под Гомелем. И в тридцать втором году, когда после погромов еврейских в Белоруссии, они убежали оттуда сюда, на Дальний Восток, и оказались тут есть недалеко, в сторону Облучья, в поселке Биракан. И, в общем, они там жили до определенного возраста, мне кажется, до сороковых годов они там жили.</t>
-  </si>
-  <si>
     <t>Так, мои родители, мать приехала до... В 37-м году где-то они приехали из Каменец-Подольска. [Замечательный город] Значит, с родителями, она еще тогда девчонка, приехала сюда с родителями. Приехали сперва в Биракан. Ее отец, то есть мой дед, он был жестянщиком. То есть, ну, те специальности. Никого из них силой сюда не пригоняли, потому что, извините, там, где они были, в то время было плохо. Поэтому они с большим... С большой надеждой, наверное, на лучшую жизнь, приехали сюда.</t>
   </si>
   <si>
@@ -6514,9 +6469,6 @@
   </si>
   <si>
     <t>Мужчина, 1958 г.р., потомок первых переселенцев</t>
-  </si>
-  <si>
-    <t>[ПМВ: А как родители сюда попали?] Могу сказать. Отец попал во время эвакуации. Он жил в Евпатории. Когда немцы пришли, они бежали-бежали, ну… там, в Среднюю Азию. И попали в Биробиджан.</t>
   </si>
   <si>
     <t>47.693379</t>
@@ -6807,9 +6759,6 @@
     <t>subtitle</t>
   </si>
   <si>
-    <t>А мама… мама, была голодовка на Украине. Ее семья, там даже умирали, вот они решили ее спасти. Она была первым ребенком, ей было восемь месяцев. И не было просто еды на Украине, и работы не было. И сюда уехали родители ее. [ПМВ: В каком году?] В 1934-м. [ПМВ: То есть прям в основании, да?] Да. Дело в том, что они в начале жили в Амурзете, а потом перебрались сюда, в Биробиджан. Вот. Некоторое время они там перебрались.</t>
-  </si>
-  <si>
     <t>О причине переезда</t>
   </si>
   <si>
@@ -6828,9 +6777,6 @@
     <t>Об изменении круга общения</t>
   </si>
   <si>
-    <t>А из Биробиджана уезжали, ну, мне кажется, это все вот тяжелые вот эти &lt;19&gt;90-е, люди боялись и уезжали туда. Тем более это была, ну, как видно, реклама у них там была, что как там хорошо, как там все прекрасно. Но я не видела, чтобы прям там расцвели в Израиле, нет, средненькие. Вот те, кто здесь работал учителем, то полы моют, то где-то на заводе на каком-то там работает, какой-то там известковый или на вредных каких-то там производствах работает.</t>
-  </si>
-  <si>
     <t>О причине переезда и жизни в Израиле</t>
   </si>
   <si>
@@ -6978,18 +6924,12 @@
     <t>https://vk.com/photo-40023088_324633313</t>
   </si>
   <si>
-    <t>Завод "Дальсельмаш"</t>
-  </si>
-  <si>
     <t>48.808186</t>
   </si>
   <si>
     <t>132.887052</t>
   </si>
   <si>
-    <t>Вообще завод «Дальсельмаш» был большой. Ну к тому моменту где-то более трех тысяч человек там работало. [А сейчас?] А сейчас этого завода нету, в период нашей так сказать перестройки он где-то до 2000-го года еще существовал, что-то делал. Вообще раньше было плановое производство, и как бы завод мог существовать только в связи с тем, что были предприятия, которые снабжали их чем-то. Ну то есть, допустим, здесь на завод с Красноярска приходили молотилки для комбайна, а на заводе «Дальсельмаш» собирали хода на гусеничном ходу: вот ставили эти молотилки, которые приходили с Красноярска. Здесь ставили на хода гусеничные и всё. И это обеспечило… Здесь у нас местность такая болотистая. По-видимому, для нашей местности более были приемлемые комбайны, которые не на колесах, а на гусеничном ходу. Завод сам тоже производил комбайны, но тоже мы зависели от комплектующих. Комплектующие были, я не помню, откуда приходили двигателя, то есть все было взаимосвязано. Когда в начале 90-х пошла эта перестройка, всё это закрывалось, естественно, завод не мог сам существовать, сам не быть самодостаточным. Он зависел от многих факторов. Ну, естественно, вот он потихонечку, потихонечку и закрылся. Хотя я считаю, что завод был на тот момент очень сильный.</t>
-  </si>
-  <si>
     <t>audio/EAO_25_12_Bb_15.mp3</t>
   </si>
   <si>
@@ -7005,9 +6945,6 @@
     <t>audio/EAO_25_12_Bb_13.mp3</t>
   </si>
   <si>
-    <t>Обозный завод – это будущий завод «Дальсельмаш», который был родным и для меня, и для моего отца, и для матери. Мы все там были. Она работала сразу в войну. И вот то, что много рассказывают и пишут про фронтовую бригаду, фронтовые бригады, одна из лучших фронтовых бригад, передовых, о которых много говорят, бригада $Кириллова/К.$, это та бригада, в которой работала и моя мать. И вот $Остапенко/О.$, $Кириллов/К.$... Еще несколько человек, ну, девушки такие же и мужчины, они были в этой бригаде, всю войну она проработала, естественно, у станка.</t>
-  </si>
-  <si>
     <t>audio/EAO_25_26_Bb_3.mp3</t>
   </si>
   <si>
@@ -7074,18 +7011,6 @@
     <t>audio/EAO_25_11_Bb_31.mp3</t>
   </si>
   <si>
-    <t>[А как Биробиджан называть сокращенно? Или, может быть, какое-то есть слово для Биробиджана?] Ну, обычно «Бирик», а если просто уже как быдло рассказывать, то просто «Бирдон». [ПМВ: Как-как?] «Бирдон». [Почему?] Я не знаю, ты просто периодически слышишь, типа, это такое слово, как будто бы… Что-то плохое, прям, откуда ты? с Бирдона. А так, если просто сокращённо, то просто «Бирик».</t>
-  </si>
-  <si>
-    <t>[А, и ещё вспомнила вот такое уже не совсем еврейское, а скорее про какие-то уменьшительно-ласкательные или не очень ласкательные названия Биробиджана и Еврейской автономной областьи — как-то принято называть это коротко.] Бирдон. Бирдон, да. Бирик. Бирик. Бирдон. Я не знаю, я так не говорю. Ну, типа поехать в Бирик. ПИВ: Ну, я так тоже не говорю, Бирик. Конечно, нет. Да, ну и никогда не говорила. Ну, это больше какой-то молодёжный сленг, да, я не знаю. Вообще так говорят, да. Мы не употребляем.</t>
-  </si>
-  <si>
-    <t>Элемент этой конструкции, потому что это первая еврейская территория, которая появилась вообще на карте мира. Мы с вами понимаем, да? И когда в &lt;19&gt;48-м году было создано государство Израиль, а в &lt;19&gt;49-м году... Пошли вот эти сюжеты, наверное, знаете, опять-таки из истории, борьба с космополитизмом и прочее. В Биробиджане закрывались еврейские школы, сжигались книги, ну и все остальное. И последствия вот этого очень долго-долго-долго это были до &lt;19&gt;90-го года. Да, в семьях это как-то помнилось, и была идишистская речь на улицах, но это было в семьях. А вот с &lt;19&gt;90-го года немножечко пошло, там воскресная школа, потом Еврейский филиал открылся, и потихонечку что-то мы пытались сделать. Но тогда еще. Как же правильно сказать? В &lt;19&gt;95-м году был принят закон «О языках народов России», сейчас, кстати, принят новый, вы знаете, вот сейчас совсем недавно подписали «Закон о языках народов России».</t>
-  </si>
-  <si>
-    <t>Вообще это было когда-то окраина. В пятидесятых годах это было окраина. То есть, ну, в принципе, этих домов ещё ж не было. Тут просто частный сектор был. Синагога даже высока, это сейчас просто насыпь. Это был вообще отшиб. Но дом уже стоял, он уже после войны, этот дом. Зимой волки приходили. [Ну, хоть не тигры. ПМВ: Да, уже хорошо]. То есть в пятьдесятых годах еще волки приходили. Это сейчас уже не это. Тигры, тигры, вот. Тигры, мы это зимой видели, тигры. Уже две зимы подряд тигры. Они ходят и собак едят по городу. Это уже обычное явление стало. [По городу?] Да, край города уже... [Заходят, да?] Да, тигры уже заходят. Уже мы как-то едем в Хабаровск вечером.</t>
-  </si>
-  <si>
     <t>[Класс. Скажи, пожалуйста, какие есть, может, символы официальные, неофициальные вашего города или области? Вот так, чтобы точно сказать, что вот символ.] Символ, наверное, который все знают — это наш любимый флаг, который выглядит как радуга. И вот кому-то он прям очень сильно не нравится и негативно к этому относятся: «Что за радуга у нас тут на флаге?» А на самом деле это же просто означает «мир». Это же ничего плохого в этом нет. Почему так все реагируют? Не знаю. Просто, наверное, от незнания. [А мир? Расшифруй это слово. Мир какой?]</t>
   </si>
   <si>
@@ -7101,9 +7026,6 @@
     <t>Пойдем. [ Какое самое существенное изменение произошло в Биробиджане с вашего детства?]   Я не знаю.  Для меня... Ну, во-первых, давайте так. В моем детстве больше любили город, чем любят его сейчас. [ Более патриотично.]   Да патриотично я не люблю это слово, патриотично. Просто не люблю. Вот есть слово, понимаете, вот у вас есть любимый человек? Он же не назовет себя патриотом Катерины. Он скажет, что он любит Катерину, да? Ну, к примеру. Я не люблю вот. Больше любили город, как-то к нему относились, как к дому. Понимаете? А сейчас этого я меньше наблюдаю намного.</t>
   </si>
   <si>
-    <t>И вот этот момент типа «ненавижу евреев», он связан именно на бытовом каком-то уровне, он не связан с национальностью, он перерастал иногда в какие-то социальных сетях были моменты. И $Эли Рисс$ хорошо тогда раскладывал, давал понять, что есть бытовой... Потому что в Биробиджане ты в кипе можешь прогуляться, и евреи ходят к мусульманам на праздники, мусульмане к евреям, православные и туда, и туда. И поэтому спокойно в Биробиджане, тут компактно. То есть, например, приезжают люди, которые вот хотят на старости спокойно пожить. У них есть там уже хорошая пенсия или какой-то пассивный доход.</t>
-  </si>
-  <si>
     <t>Здесь не это. Все закрыли, все школы закрыли, театр закрыли. Газета, когда на идиш стала опять выходить? В восемьдесят каком году? А уже толку, если двадцать лет прошло забвенья такого,  [ Да, но при этом же в вашем детстве люди-то говорили на идиши?] Да. [то есть речь-то вы слышали?] Очень было слышно, да, но боялись, где не везде это можно было услышать. [А вот как давно здесь стали названия улиц на идише писать?] Да это уже с перестройкой пришло. [Понятное дело. Но это был заметный момент в городе, что поменяли, например, автобусную остановку.] Да я вас умоляю.</t>
   </si>
   <si>
@@ -7152,9 +7074,6 @@
     <t>О мемориальных традициях</t>
   </si>
   <si>
-    <t>[А вот Вы уже начали говорить про названия улиц, а ещё были какие-то альтернативные названия?] Да, районы были, это типично биробиджанский — «Фаланга». «Фаланга-один», «Фаланга-два», «Фаланга-три». [А какие у них были официальные названия?] Это все Дальсельмаш, посёлок Дальсельмаш. Был завод, градообразующий строительный и туда, у, как правило, на Дальнем Востоке кто жил, кто приехал, люди, которые.. С небольшой судимостью. Люди приезжали на заводы, работали. Да, химики и так далее. У них было прошлое там, поэтому были определенные свои посёлки, где жили рабочие люди, рабочий лад, которые вот..</t>
-  </si>
-  <si>
     <t>О специфике районов завода</t>
   </si>
   <si>
@@ -7176,15 +7095,6 @@
     <t>images/bir_dalselmash_1.jpg</t>
   </si>
   <si>
-    <t>Общий вид завода "Дальсельмаш". Сентябрь 1972 г.</t>
-  </si>
-  <si>
-    <t>Завод "Дальсельмаш". Современное состояние</t>
-  </si>
-  <si>
-    <t>Механообрабатывающий цех № 9 завода Дальсельмаш. 1980-е гг.</t>
-  </si>
-  <si>
     <t>https://eaomedia.ru/f/big/2940/2939886.jpg?82b4191803cdf2c1c8fbd994beb82ae5</t>
   </si>
   <si>
@@ -7234,13 +7144,1886 @@
   </si>
   <si>
     <t>images/bir_memorial_3.jpg</t>
+  </si>
+  <si>
+    <t>Сквер им. И.Р. Бумагина</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_12_Bb_50.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_35_Bb_93.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1947 г.р., житель Биробиджана</t>
+  </si>
+  <si>
+    <t>там есть такой «Дальсельмаш». Одна треть или даже четвертая часть города все там когда-то работали. Я в 16 лет работал там. Ученик токаря, потом токарем назовут, в Дальсельмаш. И там есть сейчас сквер Победы. Ой, сквер имени Бумагина. Бумагина, как же его звали, Иосиф? Иосиф Бумагин. Герой Советского Союза. Иосиф Романович Бумагин. Герой Советского Союза. Он повторил подвиг Александра Матросова. Вам, это, слышали о таком? [Про Матросова слышали.] Нет, что… [Закрыл амбразуру…] Закрыл амбразуру, да, своим телом. И вот сейчас там памятник еврею, который повторил это. А тем более, да… А сейчас везде стали благоустраивать, сейчас настоящие места отдыха всякие там, места увода и так далее. Я никак не могу добраться, так хочется посмотреть, как сделали.</t>
+  </si>
+  <si>
+    <t>О появлении района и сквера</t>
+  </si>
+  <si>
+    <t>О сквере и подвиге И.Р. Бумагина</t>
+  </si>
+  <si>
+    <t>Мемориал в сквере И.Р. Бумагина</t>
+  </si>
+  <si>
+    <t>https://pomnim.1sept.ru/image/image/01/94/ef/37/0194ef37-427f-7d15-9488-16a319d5a9b8/1600x1115@2.webp?version=0194ef37-427f-7d15-9488-16a319d5a9b8</t>
+  </si>
+  <si>
+    <t>images/bir_bumagin_skver_1.webp</t>
+  </si>
+  <si>
+    <t>Барельеф героя Советского Союза И.Р. Бумагина</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/original/1349/1348190.jpg?b1b96af51fd4482f99f80fe3d2324036%20alt=</t>
+  </si>
+  <si>
+    <t>images/bir_bumagin_skver_2.jpg</t>
+  </si>
+  <si>
+    <t>132.929176</t>
+  </si>
+  <si>
+    <t>48.792431</t>
+  </si>
+  <si>
+    <t>Гимназия №1 (бывш. школа №2)</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_52.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> А вот там вот сейчас стоит школа, там стояла наша вторая школа, в которой я учился. Я очень любил эту школу.   Хоть я учился очень плохо, просто супер плохо учился, школу я любил. Ну, в смысле, атмосферу школьную, мы дружили все и так далее. [ В вашем классе было много евреев?]   Чтоб я их считал. Евреев не считали. Да, ну вы что? Я говорю, что мы тогда не делились, евреи, не евреи. На это не обращали внимания.   Никогда не обращали внимания. Это уже потом начали вот эти заморочки. Никогда...</t>
+  </si>
+  <si>
+    <t>Об отношении к школе</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_18.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_59.mp3</t>
+  </si>
+  <si>
+    <t>которая здесь была, сейчас её нет, вместо неё Гимназия №1. [Она была еврейская?] Сначала она была советская, а в 90-е годы, в 90-е годы, когда в нашей стране происходил взлёт самоидентичности, патриотизма, решили сделать вторую школу, вторую школу — она №2 тогда считалась — еврейской. И там вели отдельные еврейские предметы — идиш, иврит, еврейская история, традиция, обычаи. Но это считалось как бы школьный компонент, да? Помимо обязательных предметов, ещё и школьный компонент вводился. Кстати, меня он попросил тогда вести в школе типа факультатива “История и география Еврейской Автономной Области”.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_27_Bb_13.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_51.mp3</t>
+  </si>
+  <si>
+    <t>О возникновении гимназии, соблюдении шаббата и еврейских праздников в школе</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_09_Bb_19.mp3</t>
+  </si>
+  <si>
+    <t>Ну вот у нас вот есть двадцать третья школа – к сожалению, сейчас на ремонте. Но я там училась, и у нас проводили праздники, прям чуть ли не... Ну ладно, не каждый праздник, но такие, как Рош ха-Шана какой-нибудь или Ту би-Шват У нас было мероприятие, рассказывали историю, потом… все любили эти яблоки с мёдом, которые давали. То есть у нас был отдельный предмет еврейских традиций в пятом классе. Мы учили даже и пытались учить язык, ну там чуть-чуть, потому что у нас был буквально полгода-год. И в пятом классе там особо всем было всё равно, только перешли в среднюю школу. А так... [Это прям предмет или...] Да, прям предмет. [И за него оценки ставили?] Да, да, да.</t>
+  </si>
+  <si>
+    <t>Об учебе и праздниках в еврейской гимназии</t>
+  </si>
+  <si>
+    <t>132.943880</t>
+  </si>
+  <si>
+    <t>48.778795</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_22_Bb_11.mp3</t>
+  </si>
+  <si>
+    <t>[А так в... А вот это здание, получается, с какого года используется?] Здание давно, а здесь потом стали собираться, здесь жила одна бабушка, ну там на тот момент не бабушка, стали собираться. Вот тогда сразу, в шестьдесят третьем где-то, начали здесь собираться. Но официально это здание отдали (синагоге) в восемьдесят шестом году, уже закрепили официально. А там до этого все прекрасно знали, что здесь синагога. Почему-то евреи ходят, ничего, не было никакой ни надписи, ни магендавидов, ничего не было. [Вы здесь с 1986 года?] Ну да, получается, с 1986 года, как официально, как в документах, получено разрешение.</t>
+  </si>
+  <si>
+    <t>Об открытии синагоги</t>
+  </si>
+  <si>
+    <t>О пожаре в первом здании синагоги</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_22_Bb_2.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_23_Bb_22.mp3</t>
+  </si>
+  <si>
+    <t>Об отношении к синагоге</t>
+  </si>
+  <si>
+    <t>Мужчина, 1958 г.р., житель Биробиджана</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_16_Bb_39.mp3</t>
+  </si>
+  <si>
+    <t>Вот представьте, Биробиджан — это как микрорайон в Москве, не знаю, какой-то. Ну просто, ну что тут, я не знаю. Ничего. Всё, синагога. Да, наверное, если бы мы не занимались бы общиной жизнью, нам было бы здесь очень тяжело жить и, скорее всего, мы бы здесь не жили. С большей вероятностью. Потому что, скорее всего, это главный фактор, который нас очень крепко здесь держит. То есть мы не рассматриваем вообще варианты уехать отсюда, да, с Биробиджана.</t>
+  </si>
+  <si>
+    <t>О синагоге, как главном факторе, сдерживающем переезд</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_26_Bb_52.mp3</t>
+  </si>
+  <si>
+    <t>Об истории синагоги</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_22_Bb_10.mp3</t>
+  </si>
+  <si>
+    <t>О закрытом поселке</t>
+  </si>
+  <si>
+    <t>Ну, я не соблюдаю. Но я прихожу несколько раз в год в синагогу с удовольствием. [А в какие дни приходите? Есть определенные?] Нет. Я обычно на праздники какие-то прихожу. [А на какие праздники?] Ну, Йом-Кипур, там еще какие-то вот такие праздники. Приглашают — я прихожу. Я прихожу, мне интересно. Я, конечно, сижу, смотрю, больше смотрю, чем молюсь, конечно. Мне уже тяжело молиться. У нас очень интересный раввин. Я с ним общаюсь, он очень хорошо рассказывает многие истории, он знает историю. Я когда что-то не знаю, я иду к нему, говорю, ребе, ну почему так? Он объясняет. Да, вот я вот тоже вот, допустим, я не мог понять, как так?</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_42_Vald_26.mp3</t>
+  </si>
+  <si>
+    <t>[Подскажите, пожалуйста, какие места вы считаете наиболее значимыми с точки зрения истории области, города?] АС: Значимые… Вообще, сам Биробиджан — это уникальное, это Тихонькая, вот. Сама сопка — вот это уникально, вот это. Почему? Потому что там постоянно возле вот... Вот эта огромная сопка, где сейчас вышка стоит, там приходили сезонники, добывали... Били зверей, добывали шкуры зверей, а потом уезжали все в Хабаровск. Там была активная торговля. Вот эта сопка значимая, я считаю. Потом здесь у нас эвены еще жили, тоже очень много.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_35_Bb_108.mp3</t>
+  </si>
+  <si>
+    <t>Я где только не был. И вот как я отсутствую, 15-20 дней, и когда еду с Хабаровска до Биробиджана, я смотрю, я вижу, это, а, символ нашего города — телевизионная вышка. Когда я вижу телевизионную вышку… Ой все, становится дышать легче, дышать легче. А у меня еще сейчас дом я построил, и мое окно, если я ночью встану, в пятницу, она же пятница, начинается Шаббат, уже в пятницу.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_32_Bb_34.mp3</t>
+  </si>
+  <si>
+    <t>[какие еще можно было бы назвать символы автономной области? Символы и области, и города, вот так вот если.] Символы в целом области или еврейской культуры области? [Нет, именно в целом области, да. Потому что есть государственный, да, как бы вот там флаг, герб...] Ну, узнаваемое то, что мы используем, это вот расположение, так повезло, это сопка, телевышка биробиджанская, мы ее часто используем везде, что набережная, вот есть там сопка Тихонькая, и на ней как раз вот эта телевышка. Понятно, что наша телевышка, она не одна в стране такая. Но если взять ее аналоги, они где-то стоят там на окраине, на опушке, а нам так повезло, что когда планировали город, поставили ее прямо на сопочку, и она красиво смотрится.</t>
+  </si>
+  <si>
+    <t>132.900213</t>
+  </si>
+  <si>
+    <t>48.789908</t>
+  </si>
+  <si>
+    <t>Телевизионная вышка (сопка)</t>
+  </si>
+  <si>
+    <t>Железнодорожный вокзал</t>
+  </si>
+  <si>
+    <t>132.934563</t>
+  </si>
+  <si>
+    <t>48.792934</t>
+  </si>
+  <si>
+    <t>Вокзал железнодорожный видели? Это первое каменное здание Биробиджана. Кто построили? Зэки. Кто Дальсельмаш строил? Зэки. Кто швейную фабрику строил? И за то, что зэки сдали железнодорожный вокзал досрочно, 31 декабря 1936 года, их отпустили на свободу. А в 1937 уже никого не освобождали. Все сидели по полному сроку.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_56.mp3</t>
+  </si>
+  <si>
+    <t>А что было? Была библиотека, первая библиотека, и биробиджанцы ходили на вокзал не для того, чтобы купить билет, уехать куда-то, а взять книжку почитать, газетку, журнал. И был ресторанчик на вокзале. И все старые биробиджанцы любили ходить не в ресторан Центральный или в Восток, а на вокзал. Там их встречала официантка. Пышная, крупная женщина, которая говорила так: “Боря, не надо мне меню. Я знаю, что сегодня ты будешь кушать”. — Я спрашиваю: “Что?” — “Сегодня у нас вот такая солянка, сборная солянка. Сегодня у нас бульон с манделах”. — “Замечательно”. — “И компот”. — “Несите всё сразу”. Платил рубль и там обедал. Чувствуете?</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_62.mp3</t>
+  </si>
+  <si>
+    <t>У нас в том числе, ну вот начнем, допустим, вокзал – уже более взрослый, мы ходили туда. Там был свой определенный бренд – салат амурский и пельмени по-таежному в горшочке. Потом у нас были, ну это уже мое детство.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_12_Bb_44.mp3</t>
+  </si>
+  <si>
+    <t>Слушай меня, душа моя. Этой истории никакой нет. Вот смотрите. Вы видите памятник Шолом-Алейхему.   Он стоит лицом к дому Шолом-Алейхема, вот где мы с вами сидим, один. А почему Шолом-Алейхем, а не кто-то другой? Все мы сидим с вами на улице, которая называлась вообще как? «Партизанская». И потом ее называли… А именно Шолом-Алейхема почему? Никто не задумывался?   Что такое евреи? Вы же пошли по следам искателей счастья, правильно? Евреи – люди мечты. Евреи всегда о чем-то мечтали. И чаще всего пролетали.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_125.mp3</t>
+  </si>
+  <si>
+    <t>132.908953</t>
+  </si>
+  <si>
+    <t>48.799618</t>
+  </si>
+  <si>
+    <t>Памятник Шолом-Алейхему</t>
+  </si>
+  <si>
+    <t>48.792008</t>
+  </si>
+  <si>
+    <t>132.929980</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_27_Bb_56.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_30_Bb_50.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_37_Bb_10.mp3</t>
+  </si>
+  <si>
+    <t>132.941314</t>
+  </si>
+  <si>
+    <t>48.773213</t>
+  </si>
+  <si>
+    <t>ПГУ им. Шолом-Алейхема</t>
+  </si>
+  <si>
+    <t>48.789745</t>
+  </si>
+  <si>
+    <t>132.931221</t>
+  </si>
+  <si>
+    <t>48.793663</t>
+  </si>
+  <si>
+    <t>132.928572</t>
+  </si>
+  <si>
+    <t>132.801365</t>
+  </si>
+  <si>
+    <t>48.417457</t>
+  </si>
+  <si>
+    <t>131.938369</t>
+  </si>
+  <si>
+    <t>47.973965</t>
+  </si>
+  <si>
+    <t>131.639481</t>
+  </si>
+  <si>
+    <t>49.204973</t>
+  </si>
+  <si>
+    <t>131.883688</t>
+  </si>
+  <si>
+    <t>49.010945</t>
+  </si>
+  <si>
+    <t>Биджан</t>
+  </si>
+  <si>
+    <t>Кульдур</t>
+  </si>
+  <si>
+    <t>Теплоозерск</t>
+  </si>
+  <si>
+    <t>Научная библиотека им. Шолом-Алейхема</t>
+  </si>
+  <si>
+    <t>48.793060</t>
+  </si>
+  <si>
+    <t>132.928779</t>
+  </si>
+  <si>
+    <t>48.790245</t>
+  </si>
+  <si>
+    <t>132.933174</t>
+  </si>
+  <si>
+    <t>Мемориальная доска Л. Вассерман</t>
+  </si>
+  <si>
+    <t>48.791564</t>
+  </si>
+  <si>
+    <t>132.930317</t>
+  </si>
+  <si>
+    <t>132.900931</t>
+  </si>
+  <si>
+    <t>48.796122</t>
+  </si>
+  <si>
+    <t>Набережная р. Бира</t>
+  </si>
+  <si>
+    <t>Бродвей</t>
+  </si>
+  <si>
+    <t>132.931348</t>
+  </si>
+  <si>
+    <t>48.790632</t>
+  </si>
+  <si>
+    <t>Бира</t>
+  </si>
+  <si>
+    <t>Лондоко</t>
+  </si>
+  <si>
+    <t>132.463074</t>
+  </si>
+  <si>
+    <t>49.000934</t>
+  </si>
+  <si>
+    <t>49.011808</t>
+  </si>
+  <si>
+    <t>131.936671</t>
+  </si>
+  <si>
+    <t>Я была приглашена для... проведения и организации всей работы для создания Биробиджанского педагогического института. На тот момент в Еврейской автономной области ни одного высшего учебного заведения не было. Ну, там я долго размышляла, думала, но в конце концов я переехала, потому что та социальная несправедливость, которую я обнаружила, она меня поразила, потрясла. Это первое. Ну и второе – вот вся эта симпатичность Биробиджана, она меня тоже привлекла, потому что нет таких громадных расстояний по два часа в одну сторону на работу и прочее. Наверное, вы это тоже уже увидели, оценили.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_28_Bb_1.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_23.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_09_Bb_26.mp3</t>
+  </si>
+  <si>
+    <t>Много песен о населенных пунктах области. [А часто исполняются эти песни? И где они исполняются? И кто их исполняет?] Исполняются часто. Завтра, в это воскресенье, если вы придете в ДК... Ну, вот будут мои песни исполняться, наверное, 3 песни, и... Я в свое время создал вокальный ансамбль, 5 человек. Назвали мы его «Алэ инейнэм», это означает «все вместе». И мы с этим ансамблем практически все мои песни, или группы, или по одному вокально исполняем очень часто и в ДК, и в филармонии, и на выезде, в районах.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_37_Bb_13.mp3</t>
+  </si>
+  <si>
+    <t>[А на каком языке?] На идише. [То есть она чем там занималась?] Она газету корректировала. [Она была корректором?] Да. [И учила она язык в школе?] В школе. [А вот такой вопрос...] Она там всю жизнь отработала.  Всю жизнь. Я знал всех, кто там работал. Я их всех знал. Почему? Потому что я учился во второй школе, сейчас ее нет. А на этом месте стоит первая школа. С первого класса… мама там работала, и с первого класса, ну обычно как? Вот я закончил, куда я бегу? К маме, на работу. И вот я, естественно, всех знал. [Понятно.]</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_24_Bb_59.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_37_Bb_7.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1953 г.р., житель Биробиджана</t>
+  </si>
+  <si>
+    <t>Да, «Школа добра». [ Это вы только бирофельдская?] Ну, как, это вот наша школа, мы себя ассоциируем как «Школа добра». То есть мы стараемся делать добрые дела, то есть это и помощь жителям, и уборка тех же, допустим, могил ветеранам, волонтерская деятельность. То есть участие, вот у меня в этом году, получается, медийная команда... проекта «МедиаПритяжение» заняли на региональном этапе второе место, как раз под брендом «80 добрых дел к Великой победе». Собирали информационные карточки, готовили статьи, освещали эту деятельность.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_18_Bf_24.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1983 г.р., житель Бирофельда</t>
+  </si>
+  <si>
+    <t>Вот как у вас с этим в школе? Много ли евреев? Много ли себя идентифицируют как евреи?] Мы на этом акцент, на самом деле, не делаем. Мы обычная школа, то есть мы конфликта межнационального, да, именно нету, то есть получается.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_18_Bf_7.mp3</t>
+  </si>
+  <si>
+    <t>Мне грустно, когда... [Но люди уезжают, да?] ВИ: Конечно, конечно, потому что сокращения неоправданные. Когда у нас село Биджан, конкретно село Биджан, мы выращивали культуры, у нас было животноводство, это конкретно, у нас была засолка, там солили помидоры, огурцы, капусту, и это обеспечивали вот область, или Хабаровский край мы куда-то, наверное, отправляли, не просто же, то есть это... Массовое такое производство было. А сейчас что? А ничего нет. А что, мы перестали кушать, что ли, или что? Мясо мы перестали есть? У нас были эти, ферма. Картошку выращивали, куузику, эту, кукурузу, свёклу. Мы, школы, классами ездили, всё это убирали.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_30_Bb_33.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_28_Bb_154.mp3</t>
+  </si>
+  <si>
+    <t>[А в области вот какие-то такие…] А в области, это значит, надо думать о Кульдуре. Сейчас мы выкупили, забираем здание Кульдурского санатория, там сто миллионов. Это профсоюзный был санаторий, еще помню, когда строили все это дело. [Это источники теплые там, да?] Там термальные источники, да, очень уникальные. Воды, женские болезни, кожа, вот эти вот вещи, очень хорошие воды. Нужно развивать. Частный санаторий есть, на 50 человек, 60 человек, забит всегда. Я несколько раз был там с женой.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_26_Bb_96.mp3</t>
+  </si>
+  <si>
+    <t>это у нас санаторий Кульдур, и там не только термальные источники, но в Кульдур мы предпочитаем возить людей зимой, когда снег, когда вокруг у тебя -40, а у тебя вот эта ванна с горячей водой, ты опускаешься там в купальнике или в плавках, вокруг снег лежит, а ты вот в этой ванночке лежишь. И люди, конечно же, за этими фоточками в первую очередь едут в санаторий Кульдур. И вот там есть ещё заброшенный мраморный рудник. Когда я говорю «мрамор», на самом деле это кальцифир зелёный такой изумрудного цвета, а кальцифир — это недозрелый мрамор. И люди, которые ходят туда, вот именно, во-первых, добраться до рудника, он такой красивый такой, стена такая. Ну и взять себе на память маленький изумрудного такого, ну, короче, он зеленоватый, зелёный, жёлтый, бирюзовый такой, очень цвет интересный, который сложно, вот, чтобы человеку сказать, и он сразу представил.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_32_Bb_54.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_6.mp3</t>
+  </si>
+  <si>
+    <t>Эта территория, там есть посёлочек, он называется Лондоко, с эвенкийского он переводится как «тигровая падь» или «тигровая долина». И там, ну, кто-то называет, что это местная Швейцария, то есть кто-то называет, что это местная Новая Зеландия, и как раз вот эти сопки зелёные, которые там есть, это вот из «Властелин колец», вот эти сопки, перевалы, вот эта долина.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_32_Bb_41.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Здесь уже вот так. Когда я учился потом заочно, опять же, после армии в институте, то у нас тогда еще не было интернета. И нужную книжку, материал надо было искать в библиотеке. Поэтому все субботы и воскресенья были... в этой нашей научной библиотеке. Ещё надо было по блату уговорить, чтоб тебе оставили эту книжку или ещё что-то. Вот там и познакомился со своей женой, которая уже тоже к этому времени закончила институт. Ну, в библиотеку ходил, там познакомился так вот. </t>
+  </si>
+  <si>
+    <t>audio/EAO_25_26_Bb_28.mp3</t>
+  </si>
+  <si>
+    <t>Вот, это место. Ну самый пуп, пуп нашего города — это кинотеатр «Родина». Тогда и народу было вечером полно, вот. Очень хорошо придумали, что сделали прямо сейчас в этом же месте, на «Бродвее».</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_35_Bb_67.mp3</t>
+  </si>
+  <si>
+    <t>Ну, сколько я себя помню, что он был Родиной, хотя он какое-то время носил имя Генриха Казакевича. Он, в принципе, и построен был, ой, он был построен по инициативе Казакевича Генриха. Это отец того самого Эммануила Казакевича, вот в тридцать седьмом году.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_71.mp3</t>
+  </si>
+  <si>
+    <t>Так вот, Любовь Вассерман, и когда мы проходим по этому переулочку, я говорю, знаменитая женщина, поэтесса, рассказываю её судьбу, как она из Польши бежала, как она и в Израиле жила, как она поехала строить Биробиджан. Как ее в &lt;19&gt;52-м году посадили. За что? За одну строчку в её стихах: “Люблю тебя, Биробиджан, моя страна”. Её вызвали в определённое место и сказали: “Биробиджан — это не страна, это только город.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_65.mp3</t>
+  </si>
+  <si>
+    <t>Если мы себя позиционируем как автономная область, еврейская автономная, значит, идиш должен стать разговорным языком. Вот идёте вы обедать в Симху, еврейское, казалось бы, да, кафе, ресторан. Официанты мало того, что должны быть одеты в национальную одежду, они должны</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_24.mp3</t>
+  </si>
+  <si>
+    <t>Вот. Мы… Но не исключено, не исключено, если жители области, многие жители области понимают это, что развитие нашей маленькой территории... Оно может быть в том числе за счет уникальности вот ее еврейской составляющей. Если еврейская составляющая из области уйдет, у нас будет какой-то хиленький… Какая-то хиленькая территория, непонятно, какая. [То есть можно сказать, что туристы сюда едут как раз-таки в том числе, чтобы вот посмотреть на вот этот еврейский компонент? То есть это такое для привлечения туристов в том числе важно?] Да, конечно. [Как бы экзотика действительно?] Нет, конечно, конечно, особенности Еврейской автономной области, конечно, в том числе и в этом. И когда мы говорили, я не называла ресторан «Симха», кафе «Симха», где национальная кухня. И, конечно, когда у нас бывают все гости, мы как-то стараемся людей туда сводить, угостить, вот, когда это как бы запланированные, не внезапные вещи.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_28_Bb_147.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_23_Bb_33.mp3</t>
+  </si>
+  <si>
+    <t>Очень, конечно, сегодня объект показа, и мы сами ходим с семьей, с внуками я хожу туда – на набережную нашу. Я бы сказал, чем он отличается от других, очень много естественного, особенно когда смотришь на Биру, вот этот остров. Это, конечно, интересно.</t>
+  </si>
+  <si>
+    <t>Ну вот, допустим, у нас в последнее время часто праздники начали выносить за пределы синагоги и всей вот этой территории. То есть, допустим, у нас... В том году мы зажигали свечи на общей набережной, то есть на миноре… ой, нет, ханукию. И просто всех оповестили о том, что будет зажжение свечей. И это начали выносить просто в люди, чтобы больше все об этом знали. И у нас стояла ледяная... ледяной подсвечник, на который были свечи, которые, я честно не знаю, они были или просто на кнопочке обычной, или их зажигали – скорее всего, просто включали. Вот.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_09_Bb_41.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Набережную, у нас набережная красивая. Мы там гуляем вечером. Не то, что это достопримечательность, это наше обычное место. Мы вечером ходим там гулять. Там вот, к водичке подошли, там в парк вот так поднялись, парк туда вверх, тоже прям по набережной там гуляем. Вот это наши достопримечательности. Те, кто работает, у них не так много времени, чтобы, ну, свободного, чтобы гулять. А вот когда есть время, летом вот. Особенно тогда, да, на велосипеде там. </t>
+  </si>
+  <si>
+    <t>audio/EAO_25_31_Bb_26.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_42_Vald_75.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_48.mp3</t>
+  </si>
+  <si>
+    <t>ул. Ленина (Постышева)</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_11_Bb_54.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_21_Bb_18.mp3</t>
+  </si>
+  <si>
+    <t>вот Бира, чем она знаменита — в период Великой Отечественной войны в Бире находился районный центр. И вот как раз вы изучаете историю становления Еврейской автономной области, когда вот был еврейский проект и планировали создать Еврейскую автономную область, в том числе рассматривалась как одна из альтернатив Биробиджану именно поселок Бира, чтобы поселок Бира сделать именно центром Еврейской автономной области, потому что он был более развит поселок, он появился много раньше станции Тихонькая.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_32_Bb_6.mp3</t>
+  </si>
+  <si>
+    <t>Я говорю: «Ну что, тебе понравился в "Бастаке"»? Она говорит: «Я никогда в жизни не думала, что мне так понравится просто гулять по лесу». А там вот действительно вот это, сохранили природу, то есть там есть ограничения по заповеднику, плюс они сделали эко-тропы, смотровые площадки. Действительно, в заповедник стоит съездить, побывать. Тем более я всегда говорю, что самое лучшее время для туризма в ЕАО — это сентябрь. Во-первых, нет комаров, во-вторых, нет повышенной влажности, духота, ее нет в сентябре, ну и еще не так холодно. Плюс сейчас как раз уже с этой недели все деревья покрасятся в красно-желто-оранжевые оттенки, и очень будет красиво.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_32_Bb_53.mp3</t>
+  </si>
+  <si>
+    <t>132.988282</t>
+  </si>
+  <si>
+    <t>48.891419</t>
+  </si>
+  <si>
+    <t>132.929929</t>
+  </si>
+  <si>
+    <t>48.792710</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_41_Vald_3.mp3</t>
+  </si>
+  <si>
+    <t>[Ну к вам приезжают из Валдгейма, да? А там много в Валдгейме человек живет? Ну, по крайней мере, тех, кого вы знаете.] Да. Там евреев много живут, там все фермеры евреи, все это еврейское, все управление, все это. А никто, в синагогу. [Не, ну вы знаете там людей]. Ну да. От Валдгейма что там? Почти что ничего не осталось.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_22_Bb_47.mp3</t>
+  </si>
+  <si>
+    <t>Просто я, допустим, даже как бы меня не заманивали, я все равно бы не уехал. [А почему?] Ну, у меня отношение такое, что, во-первых, надо везде работать, а работать в Израиле — это... Лучше я здесь на себя буду работать, чем в Израиле. [Ну, понятно, у Вас своя земля, это Вас держит.] Конечно... Она по-любому, любой год, какой бы ни был год, она кормит.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_40_Vald_22.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1961 г.р., житель Валдгейма</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_40_Vald_7.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_42_Vald_49.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_42_Vald_76.mp3</t>
+  </si>
+  <si>
+    <t>Биробиджан-строй, участок здесь был. И райком партии построили, райсполком построили, сдавался в эксплуатацию... дом культуры и строился детский сад. И я так посмотрел, у меня же каменщик, это самое, специальность, и я решил строить Амурзет. И вот стал строить Амурзет, и получилось, что я так попал,уже стало самостоятельно строительное монтажное управление номер пять, и это самое. И он, это, строили промбазу, а промбаза там расстроена - столярный цех и пилорама. И главный механик, Лопатин Владимир Федотович - он говорит, Михаил говорит, это самое, ты бывший тракторист, надо вот это самое на растворный узел, вот это самое, мотористом, это самое. И я согласился, стал работать там, это... Раствор… так же в каждом доме есть, хоть они кирпичной кладки, но частица моего труда, получается, в каждом доме здесь есть частица моего труда. Ну, рос Амурзет, ну, и с ним рос и я.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_19_Am_19.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1935 г.р., житель Амурзета</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_19_Am_25.mp3</t>
+  </si>
+  <si>
+    <t>[Скажите, пожалуйста, вот когда вы в (19)54-м году приехали в Амурзет, и вы говорите, что здесь было довольно много евреев, жителей евреев.] Да, да. [А здесь было где-то люди собирались молиться, там праздники отмечать?] Нет, нет, нет, нет, и до сих пор нету, и никогда не было. [Ну хорошо, а вот, хорошо, вот Пейсах, например, вы... Был у вас в Пейсах?] Ну, знаешь, получалось, что каждая семья самостоятельно справляла этот праздник.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_19_Am_47.mp3</t>
+  </si>
+  <si>
+    <t>И это, знаешь, за...баржи приезжали. И за километр от Амура стояли машины в очереди, чтобы там разгрузить. [То есть это сельскохозяйственный район?] Сельскохозяйственный район. И у нас такие урожаи хорошие были. Хорошее сельское хозяйство, и сам Амурзет, я говорю, я строил, как каменщик, когда я это самое смотрю, люди это самое, мы строим дома, люди это самое поселяются в этих домах, так радостно душе, что ты вложил свой труд, что люди сейчас живут хорошо.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_19_Am_56.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_26_Bb_90.mp3</t>
+  </si>
+  <si>
+    <t>Мы пытались, но поддержки от других жителей села здесь чисто не было. [Сколько, думаете, процентов?]   Я думаю, процента два осталось. Если есть, то это хорошо, а кто-то, может быть, уже просто забыл. Хотя в этом году произошло много праздников с еврейской тематикой. В этот год у нас интересные праздники, мероприятия. И приятно, что говорят о еврейской культуре, это тоже очень хорошо.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_18_Bf_9.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_25_Bb_11.mp3</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_42_Vald_27.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бесплатно перевезём? Да. Подъёмные дадим? Да. Для трудоустройства занимайтесь. Хотите сельским хозяйством, хотите артели создавайте. У нас же здесь много было еврейских артелей. Даже целые посёлки потом возникли на базе этих артелей. И все знают, что Теплоозёрск - это еврейский населенный пункт, артель, хотя ничего в названии еврейского нет. </t>
+  </si>
+  <si>
+    <t>Мужчина и женщина, жители Валдгейма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[А скажите, пожалуйста, когда вы здесь вот начали свою жизнь в Амурзете, здесь много евреев тогда же?] Считай, 90% и больше были евреи. [Понятно. А потом уехали как...] Ну, это получалось, что многие в город поехали, много туда-сюда. И это так получилось. Посмотри, если маленький Амурзет, допустим, как бы две улицы, а сейчас десять улиц. Ясное дело, что нас много стало. И кажется, что это... А так получалось, что это... [Понятно.]А здесь, в Амурзете еврейский язык преподавали. Они учились на еврейском языке в Амурзете. Вот моя жена училась на еврейском языке, а преподавали еще русский. Вот такая история. [А вот вы с женой, например, дома на каком языке разговаривали? На русском или на еврейском?] По-разному. И по-русски, по-еврейски разговаривали. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все первые упоминания о синагоге появляются где-то в двадцать восьмом году. И то не в Биробиджане, а в районе села Бирофельд. Один журналист увидел землянку. Поинтересовался, что там, зашел, а там старики молились. Была синагога самодельная. Это двадцать восьмой год, а потом это отдельная история уже. Поэтому вот как-то, как-то вот так. </t>
+  </si>
+  <si>
+    <t>[Ну, например, если к вам приедут гости из другого региона и попросят показать им какие-то места, вы им что покажете?] Ну, наверное, всё-таки я отвезу их на сопочку, чтобы они посмотрели вниз. Это первое, да. Второе, потом я показал бы им нашу природу, которая у нас шикарная. Вот, допустим, если уехать в сторону Бирофельда, там вообще шикарно, там красота. Какой лес у нас, какая природа, вообще ж замечательная.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_01_Izr_31.mp3</t>
+  </si>
+  <si>
+    <t>Но в нашей библиотеке почти все еврейские книги были уничтожены. А... Значит, как ты, может быть, историю если ты изучала, ты знаешь, что вот во время вот этой вот кампании, которая была развязана в 1947- 53 году,  когда с евреями решили покончить. Вот. Наша библиотека, которая имела огромнейший, э, значит, комплект различных книг на еврейском языке, это было более тридцати тысяч, ну, говорят, тридцать пять тысяч, они были сожжены. И в нашей библиотеке осталось несколько, может быть, там тысяч книг, там четыре-пять тысяч всего. Вот.</t>
+  </si>
+  <si>
+    <t>О численности евреев</t>
+  </si>
+  <si>
+    <t>И когда ставится вопрос о том, что будет область или не будет существовать, когда многие задают вопрос, зачем эта область, если там нет ни одного еврея. И сегодня там полторы тысячи, если и есть лиц еврейской национальности, ну, — в Биробиджане. А в Валдгейме остались, там, может быть, несколько сот. И то не знаю, есть ли там столько, понимаешь? Вот. Но в Валдгейме ты хоть что-то увидишь, ты хоть с чем-то столкнешься. Просто иногда хочется что-то услышать, иногда хочется кого-то увидеть. Там есть ветераны, там есть люди, которые приехали… их родители там начинали, и они там до сих пор работают в Валдгейме. И это, это разогревает, это немножко это вот возбуждает.</t>
+  </si>
+  <si>
+    <t>audio/EAO_25_01_Izr_72.mp3</t>
+  </si>
+  <si>
+    <t>Мужчина, 1949 г.р. эмигрант из Израиля</t>
+  </si>
+  <si>
+    <t>В Биробиджане было такое понятие — «пойти на брод». Бродвей. Брод. Это улица Октябрьская и улица Горького. И вот в моё детство было так. Я сам ходил на брод. Парни шли по одной улице, скажем, по Октябрьской. Девушки шли по Горькому, по параллельной. Встречались у вокзала. А на вокзале был фонтан круглый, и считалось нормальным способом макнуть мальчишку в фонтан.</t>
+  </si>
+  <si>
+    <t>там до Амурзета двести сорок, долго ехать, а Ленинск половина, сто двадцать, там тоже пункт пропуска. [А из Амурзета тоже есть паром в Китай? ] Да, тоже есть, да. [Не через Никольское, да?] Нет, не через Никольское, а прямо в Амурзете, в Амурзете на окраине, северная часть, справа по дороге проехать. В Амурзет заезжаешь в центре, так, и проехать надо еще вдоль Амура метров пятьсот. [И там переправа?] Переправа там, да. [Нет, мы просто вчера, когда ехали в Амурзет по дороге, меня совершенно поразила просто до глубины души вот красота ландшафта, потому что это невероятно красивая дорога. То есть само созерцание этой дороги, по-моему, вот что-то необыкновенное.] Особенно, знаешь, красиво было. Вот не сейчас, а чуть раньше, когда было сильное развитие сельского хозяйства, и вот в это время, когда шла, ну, чуть раньше уборка картофеля, когда здесь выращивали картофеля сто пятьдесят тысяч тонн, и когда половина студенчества Хабаровска было в Никольском и других селах, и вот когда ехал, допустим, КамАЗ, груженный картофелем, то после него песчаный этот пыльный след, и ты приезжаешь в Амурзет, все приезжали одного цвета.</t>
+  </si>
+  <si>
+    <t>Есть у нас такой отсюда 130 километров Соцгородок. Вы, может быть, слышали. [Мы были]. От него ничего не осталось. Да. В мое детство этот Соцгородок... То есть как такового, видишь, был Биробиджанский район, Облучье, может быть. На границу, как ни странно, была латина. А Соцгородок говорил на иврите. Я помню это хорошо. И туда нельзя было попасть. Года до 78-го, до 79-го туда нельзя было просто приехать. Это была закрытая территория. Ее охраняло КГБ. Там оставались еще евреи, иностранцы. То есть...</t>
+  </si>
+  <si>
+    <t>Женщина, жительнийа Валдгейма</t>
+  </si>
+  <si>
+    <t>О сопке Тихонькой до евреев</t>
+  </si>
+  <si>
+    <t>О телевышке как символе</t>
+  </si>
+  <si>
+    <t>О строительстве вокзала</t>
+  </si>
+  <si>
+    <t>О вокзальных библиотеке и ресторане</t>
+  </si>
+  <si>
+    <t>О фирменных блюдах в вокзальном ресторане</t>
+  </si>
+  <si>
+    <t>О памятнике и Шолом-Алейхеме как символе еврейской мечты</t>
+  </si>
+  <si>
+    <t>О деятельности общины</t>
+  </si>
+  <si>
+    <t>О создании университета</t>
+  </si>
+  <si>
+    <t>О факультете "англоидиш" в университете</t>
+  </si>
+  <si>
+    <t>О выставках в ДК</t>
+  </si>
+  <si>
+    <t>Об ансамбле «Алэ инейнэм»</t>
+  </si>
+  <si>
+    <t>О связи с редакцией через семью</t>
+  </si>
+  <si>
+    <t>О специфике газеты и ее тиражах</t>
+  </si>
+  <si>
+    <t>О «Школе добра»</t>
+  </si>
+  <si>
+    <t>О составе учеников</t>
+  </si>
+  <si>
+    <t>О производстве и его утрате</t>
+  </si>
+  <si>
+    <t>О состоянии санатория и его перспективах</t>
+  </si>
+  <si>
+    <t>О зимних термальных ваннах и заброшенном руднике</t>
+  </si>
+  <si>
+    <t>Об уникальности вод</t>
+  </si>
+  <si>
+    <t>О еврейской артели</t>
+  </si>
+  <si>
+    <t>О происхождении названия поселка</t>
+  </si>
+  <si>
+    <t>О судьбоносных встречах в библиотеке</t>
+  </si>
+  <si>
+    <t>О кинотеатре «Родина» как центре города</t>
+  </si>
+  <si>
+    <t>О строительстве кинотеатра</t>
+  </si>
+  <si>
+    <t>О репрессиях за строчку в стихотворении</t>
+  </si>
+  <si>
+    <t>О еврейской составляющей "Симхи"</t>
+  </si>
+  <si>
+    <t>О предложении усилить еврейскую составляющую</t>
+  </si>
+  <si>
+    <t>О красоте набережной</t>
+  </si>
+  <si>
+    <t>О зажжении ханукии</t>
+  </si>
+  <si>
+    <t>О месте вечерних прогулок</t>
+  </si>
+  <si>
+    <t>О разливах Биры и ее былой судоходности</t>
+  </si>
+  <si>
+    <t>О молодежных гуляниях на «броде»</t>
+  </si>
+  <si>
+    <t>О переименовании улицы</t>
+  </si>
+  <si>
+    <t>Об улице как настоящем еврейском месте</t>
+  </si>
+  <si>
+    <t>О поселке Бира как претенденте на роль центра ЕАО</t>
+  </si>
+  <si>
+    <t>О природе заповедника и осенних красках сентября</t>
+  </si>
+  <si>
+    <t>О работе в колхозе</t>
+  </si>
+  <si>
+    <t>О Валдгейме в 1960-е годы</t>
+  </si>
+  <si>
+    <t>О детских домах</t>
+  </si>
+  <si>
+    <t>О происхождении названия села</t>
+  </si>
+  <si>
+    <t>О строительстве Амурзета</t>
+  </si>
+  <si>
+    <t>Об отсутствии синагоги</t>
+  </si>
+  <si>
+    <t>О радости строителя</t>
+  </si>
+  <si>
+    <t>О настоящей и былой красоте Амурзета</t>
+  </si>
+  <si>
+    <t>О первой синагоге</t>
+  </si>
+  <si>
+    <t>О красоте природы</t>
+  </si>
+  <si>
+    <t>О массовом сожжении еврейских книг</t>
+  </si>
+  <si>
+    <t>О еврейских праздниках</t>
+  </si>
+  <si>
+    <t>О причинах оставаться в Валдгейме</t>
+  </si>
+  <si>
+    <t>images/londoko_1.jpg</t>
+  </si>
+  <si>
+    <t>Общий вид на курорт Кульдур. 1912 год.</t>
+  </si>
+  <si>
+    <t>Примитивные ванны курортников 1910-1915 годов.</t>
+  </si>
+  <si>
+    <t>Общий вид курорта Кульдур. 1926 год.</t>
+  </si>
+  <si>
+    <t>Общий вид на поселок Кульдур. 1976 год.</t>
+  </si>
+  <si>
+    <t>images/kuldur_1.jpg</t>
+  </si>
+  <si>
+    <t>images/kuldur_2.jpg</t>
+  </si>
+  <si>
+    <t>images/kuldur_3.jpg</t>
+  </si>
+  <si>
+    <t>images/kuldur_4.jpg</t>
+  </si>
+  <si>
+    <t>https://kuldurdv.ru/%d1%84%d0%be%d1%82%d0%be%d0%b3%d0%b0%d0%bb%d0%b5%d1%80%d0%b5%d1%8f/</t>
+  </si>
+  <si>
+    <t>images/kuldur_5.jpg</t>
+  </si>
+  <si>
+    <t>Санаторий Кульдур. Современное состояние.</t>
+  </si>
+  <si>
+    <t>Термальные воды Кульдура.</t>
+  </si>
+  <si>
+    <t>images/kuldur_6.jpg</t>
+  </si>
+  <si>
+    <t>Церковь Веры, Надежды, Любви и матери их Софии в с. Валдгейм</t>
+  </si>
+  <si>
+    <t>Стелла с надписью Валдгейм на въезде в село</t>
+  </si>
+  <si>
+    <t>Памятник переселенцам в селе Валдгейм</t>
+  </si>
+  <si>
+    <t>images/vald_1.jpg</t>
+  </si>
+  <si>
+    <t>images/vald_2.jpg</t>
+  </si>
+  <si>
+    <t>images/vald_3.jpg</t>
+  </si>
+  <si>
+    <t>images/vald_4.jpg</t>
+  </si>
+  <si>
+    <t>images/vald_5.jpg</t>
+  </si>
+  <si>
+    <t>images/vald_6.jpg</t>
+  </si>
+  <si>
+    <t>Здание Дома культуры в селе Валдгейм</t>
+  </si>
+  <si>
+    <t>https://br.eao.ru/work/munuchradm/dkadm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Памятный знак на месте строительства первого дома в Соцгородке </t>
+  </si>
+  <si>
+    <t>images/socgorodok.jpg</t>
+  </si>
+  <si>
+    <t>Общий вид села Бирофельд</t>
+  </si>
+  <si>
+    <t>images/birofeld_1.jpg</t>
+  </si>
+  <si>
+    <t>images/birofeld_2.jpg</t>
+  </si>
+  <si>
+    <t>images/birofeld_3.jpg</t>
+  </si>
+  <si>
+    <t>images/birofeld_4.jpg</t>
+  </si>
+  <si>
+    <t>Памятник героям Великой Отечественной войны в селе Бирофельд</t>
+  </si>
+  <si>
+    <t>Открытие площади Ленина в Теплоозерске</t>
+  </si>
+  <si>
+    <t>images/teploozersk_1.jpg</t>
+  </si>
+  <si>
+    <t>https://cyberleninka.ru/article/n/istoriya-formirovaniya-i-perspektivy-razvitiya-teploozerska-v-evreyskoy-avtonomnoy-oblast</t>
+  </si>
+  <si>
+    <t>images/teploozersk_2.jpg</t>
+  </si>
+  <si>
+    <t>https://teploozersk.eao.ru/city/photogallery/?PAGE_NAME=detail&amp;SECTION_ID=9&amp;ELEMENT_ID=281</t>
+  </si>
+  <si>
+    <t>images/teploozersk_3.jpg</t>
+  </si>
+  <si>
+    <t>https://teploozersk.eao.ru/city/photogallery/?PAGE_NAME=detail&amp;SECTION_ID=4&amp;ELEMENT_ID=367</t>
+  </si>
+  <si>
+    <t>images/teploozersk_4.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/news/1590027/</t>
+  </si>
+  <si>
+    <t>images/teploozersk_5.jpg</t>
+  </si>
+  <si>
+    <t>Бира. 1913 год</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/No-nb_bldsa_3f211.jpg/1280px-No-nb_bldsa_3f211.jpg</t>
+  </si>
+  <si>
+    <t>images/bira_1.jpg</t>
+  </si>
+  <si>
+    <t>Стахановец Теплоозерского рыборазводного завода. Фото: Наследие ЕАО</t>
+  </si>
+  <si>
+    <t>Железнодорожная станция Бира. Фото: Artem Svetlov</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2a/Bira_2024-08_1724617405.jpg/1920px-Bira_2024-08_1724617405.jpg</t>
+  </si>
+  <si>
+    <t>images/bira_2.jpg</t>
+  </si>
+  <si>
+    <t>Станция Бира. Улица. 1929 год</t>
+  </si>
+  <si>
+    <t>http://humus.livejournal.com/3599445.html</t>
+  </si>
+  <si>
+    <t>images/bira_3.webp</t>
+  </si>
+  <si>
+    <t>images/bira_4.webp</t>
+  </si>
+  <si>
+    <t>https://www.bankgorodov.ru/place/bira/photos</t>
+  </si>
+  <si>
+    <t>На субботнике. 1985-1995 года</t>
+  </si>
+  <si>
+    <t>https://bastak-eao.ru/thumb/2/L0hsuyCtesmF-wk0Hi4ffA/1280r/d/b_50_869048.jpg</t>
+  </si>
+  <si>
+    <t>images/bastak_1.webp</t>
+  </si>
+  <si>
+    <t>Река Бастак – крупнейший водоток заповедника «Бастак». Фото: Шаргородский М.А.</t>
+  </si>
+  <si>
+    <t>https://bastak-eao.ru/thumb/2/bF_ymh2R6DRvse5DkpByHA/580r450/d/1.jpg</t>
+  </si>
+  <si>
+    <t>images/bastak_2.webp</t>
+  </si>
+  <si>
+    <t>images/bastak_3.jpg</t>
+  </si>
+  <si>
+    <t>Птенец дальневосточного аиста. Фото: Павел Петрушин</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/w/index.php?curid=267628</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/news/646115/</t>
+  </si>
+  <si>
+    <t>images/bastak_4.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1370/1369510.jpg?ea42b13d08eaa369451a2e3dc23b8670</t>
+  </si>
+  <si>
+    <t>images/bastak_5.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1370/1369509.jpg?ea42b13d08eaa369451a2e3dc23b8670</t>
+  </si>
+  <si>
+    <t>images/bastak_6.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_sinagoga_1.jpg</t>
+  </si>
+  <si>
+    <t>https://livebir.ru/content/images/2025/07/14.jpg</t>
+  </si>
+  <si>
+    <t>https://livebir.ru/content/images/2025/07/8-1.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_sinagoga_2.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/3036/3035405.jpg</t>
+  </si>
+  <si>
+    <t>Вокзал деревянный молодого Биробиджана. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>images/bir_vokzal_1.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/3036/3035555.jpg</t>
+  </si>
+  <si>
+    <t>Сопка с телевышкой. Вид с крыши Дома Пионеров. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>images/bir_sopka_1.jpg</t>
+  </si>
+  <si>
+    <t>https://nasledie-eao.ru/sites/default/files/2025-11/3.webp</t>
+  </si>
+  <si>
+    <t>images/bir_sopka_2.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/970/969806.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_vokzal_2.jpg</t>
+  </si>
+  <si>
+    <t>Здание Биробиджанского железнодорожного вокзала, 1940-е годы. Фото: Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>Здание Биробиджанского железнодорожного вокзала, наши дни</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1010/1009103.jpg?8350ffb60655a6c421eca0e4be9496f5</t>
+  </si>
+  <si>
+    <t>Памятник первым переселенцам на привокзальной площади</t>
+  </si>
+  <si>
+    <t>images/bir_vokzal_3.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_vokzal_4.jpg</t>
+  </si>
+  <si>
+    <t>https://biradm.ru/files/potr/pict/photo_kon.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_memorial_sholom_1.jpg</t>
+  </si>
+  <si>
+    <t>https://biradm.ru/files/potr/pict/photo_shol_al.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/3182/3181294.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_memorial_sholom_2.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f1/Birobidzhan%2C_Beit_Menachem_Synagogue_-01.jpg?_=20241101052750</t>
+  </si>
+  <si>
+    <t>images/bir_freid_1.jpg</t>
+  </si>
+  <si>
+    <t>https://autotravel.ru/phalbum/91941/108.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_freid_2.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_freid_3.jpg</t>
+  </si>
+  <si>
+    <t>https://autotravel.ru/phalbum/91941/107.jpg</t>
+  </si>
+  <si>
+    <t>Логотип ПГУ имени Шолом-Алейхема</t>
+  </si>
+  <si>
+    <t>images/bir_institute_1.jpg</t>
+  </si>
+  <si>
+    <t>https://historydepositarium.ru/npolk/pgusa/</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/w/index.php?curid=22588376</t>
+  </si>
+  <si>
+    <t>images/bir_institute_2.jpg</t>
+  </si>
+  <si>
+    <t>Приамурский государственный университет имени Шолом-Алейхема. Фото: Pgusa</t>
+  </si>
+  <si>
+    <t>https://m.sibogni.ru/sites/default/files/pictures/gorodskoy_dvorec_kultury_birobidzhana_kopiya.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_dom_culture_2.jpg</t>
+  </si>
+  <si>
+    <t>Городской дворец культуры Биробиджана</t>
+  </si>
+  <si>
+    <t>Дворец культуры в Биробиджане, 1960-е годы. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/970/969762.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_dom_culture_1.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1010/1009081.jpg?97a0969e39f48d1d088306b832aa2a09</t>
+  </si>
+  <si>
+    <t>images/bir_kinoteatr_1.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_kinoteatr_2.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_kinoteatr_3.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1010/1009082.jpg?cf700e080e4669b6ae386a681c460e92</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1010/1009087.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_redaktsia_gazet_1.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_redaktsia_gazet_2.jpg</t>
+  </si>
+  <si>
+    <t>Деревянное здание типографии. 1930-е годы. Фото: архив БШ</t>
+  </si>
+  <si>
+    <t>https://www.gazetaeao.ru/resurs/uploads/2020/11/NAT_8638tsv.jpg</t>
+  </si>
+  <si>
+    <t>https://www.gazetaeao.ru/resurs/uploads/2020/10/9-2-4.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_redaktsia_gazet_3.jpg</t>
+  </si>
+  <si>
+    <t>https://www.gazetaeao.ru/resurs/uploads/2020/10/3-1-6.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_simxa_1.jpg</t>
+  </si>
+  <si>
+    <t>images/bijan_1.webp</t>
+  </si>
+  <si>
+    <t>Памятник односельчанам, погибшим в годы Великой Отечественной войны</t>
+  </si>
+  <si>
+    <t>https://avatars.mds.yandex.net/get-altay/2816622/2a0000017469d447bf827c160dc5a9b8aa58/XXXL</t>
+  </si>
+  <si>
+    <t>https://img.tourister.ru/files/3/3/0/5/8/8/4/2/original.jpg</t>
+  </si>
+  <si>
+    <t>Вид на реку Биджан</t>
+  </si>
+  <si>
+    <t>https://catcher.fish/wp-content/uploads/2017/08/bijan.jpg</t>
+  </si>
+  <si>
+    <t>images/bijan_2.jpg</t>
+  </si>
+  <si>
+    <t>http://биджан.школа-биджанского-сп.рф/wp-content/uploads/2011/11/sch1.jpg</t>
+  </si>
+  <si>
+    <t>images/bijan_3.jpg</t>
+  </si>
+  <si>
+    <t>Здание старой школы в с. Биджан. 1930-е годы.</t>
+  </si>
+  <si>
+    <t>http://биджан.школа-биджанского-сп.рф/wp-content/uploads/2011/11/schola2.jpg</t>
+  </si>
+  <si>
+    <t>Школа в с. Биджан. Современное состояние</t>
+  </si>
+  <si>
+    <t>images/bijan_4.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_bibl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b9/%D0%9C%D1%83%D0%B7%D0%B5%D0%B9_%D0%B8_%D0%B1%D0%B8%D0%B1%D0%BB%D0%B8%D0%BE%D1%82%D0%B5%D0%BA%D0%B0.jpg/1920px-%D0%9C%D1%83%D0%B7%D0%B5%D0%B9_%D0%B8_%D0%B1%D0%B8%D0%B1%D0%BB%D0%B8%D0%BE%D1%82%D0%B5%D0%BA%D0%B0.jpg</t>
+  </si>
+  <si>
+    <t>Здание областной библиотеки им. Шолом-Алейхема. Фото: Николь 1972</t>
+  </si>
+  <si>
+    <t>https://bounb.ru/files/pamyatki/sholom-aleihem/ris31.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_simxa_2.jpg</t>
+  </si>
+  <si>
+    <t>Здание областной библиотеки им. Шолом-Алейхема. 1940-е годы.</t>
+  </si>
+  <si>
+    <t>https://bounb.ru/files/pamyatki/sholom-aleihem/ris02.jpg</t>
+  </si>
+  <si>
+    <t>Иллюстрации к произведениям Шолом-Алейхема в фойе библиотеки</t>
+  </si>
+  <si>
+    <t>https://bounb.ru/files/pamyatki/sholom-aleihem/ris05.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_memorial_lv_1.jpg</t>
+  </si>
+  <si>
+    <t>Поэтесса Л.Ш. Вассерман в центре. 1960-е гг. Фото: Биробиджанская звезда</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/ru/c/c3/Vasserman.jpg?_=20070203014106</t>
+  </si>
+  <si>
+    <t>https://i2016.otzovik.com/2016/11/01/3997028/img/5239925.jpeg</t>
+  </si>
+  <si>
+    <t>Мемориальная доска поэтессе Л.Ш. Вассерман</t>
+  </si>
+  <si>
+    <t>images/bir_memorial_lv_2.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1357/1356329.jpg?f88c551f43514e33d281acabda192367</t>
+  </si>
+  <si>
+    <t>images/bir_street_len_1.jpg</t>
+  </si>
+  <si>
+    <t>Строительство Биробиджана. Улица Ленина, 1935 год. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1359/1358453.jpg</t>
+  </si>
+  <si>
+    <t>На ул. Ленина в Биробиджане (детско-юношеский центр, синагога Бейт-Менахем, раввин, трубящий в шофар). Фото: Гречанюк Виталий, ИА PrimaMedia</t>
+  </si>
+  <si>
+    <t>images/bir_street_len_2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://eaomedia.ru/f/big/1358/1357993.jpg </t>
+  </si>
+  <si>
+    <t>images/bir_brodvey_1.jpg</t>
+  </si>
+  <si>
+    <t>Улица Октябрьская в Биробиджане. Фото: Евгений Карпов</t>
+  </si>
+  <si>
+    <t>Дамба на берегу Биры в Биробиджане, 1962 год. Фото: Из фондов областного краеведческого музея</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/1010/1009114.jpg?4cea0056f1261c06cc326e541ff21449</t>
+  </si>
+  <si>
+    <t>images/reka_bira_1.jpg</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/2707/2706141.png?154d2ff34009e49fe5c9f2ee29fbe005</t>
+  </si>
+  <si>
+    <t>Строительство на ул. Горького. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>https://eaomedia.ru/f/big/2707/2706143.png?154d2ff34009e49fe5c9f2ee29fbe005</t>
+  </si>
+  <si>
+    <t>images/bir_brodvey_2.png</t>
+  </si>
+  <si>
+    <t>images/bir_brodvey_3.png</t>
+  </si>
+  <si>
+    <t>images/bir_brodvey_4.jpg</t>
+  </si>
+  <si>
+    <t>Улица Октябрьская. 1935-1936 года</t>
+  </si>
+  <si>
+    <t>https://riabir.ru/photo</t>
+  </si>
+  <si>
+    <t>Биробиджан, центральная набережная, река Бира. 2024 год. Фото: I13Robin</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/%D0%91%D0%B8%D1%80%D0%BE%D0%B1%D0%B8%D0%B4%D0%B6%D0%B0%D0%BD-%D0%BD%D0%B0%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%BD%D0%B0%D1%8F-%D1%80%D0%B5%D0%BA%D0%B0-%D0%91%D0%B8%D1%80%D0%B0-2024.jpg/1920px-%D0%91%D0%B8%D1%80%D0%BE%D0%B1%D0%B8%D0%B4%D0%B6%D0%B0%D0%BD-%D0%BD%D0%B0%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%BD%D0%B0%D1%8F-%D1%80%D0%B5%D0%BA%D0%B0-%D0%91%D0%B8%D1%80%D0%B0-2024.jpg?_=20241025003650</t>
+  </si>
+  <si>
+    <t>images/reka_bira_2.jpg</t>
+  </si>
+  <si>
+    <t>images/bir_jew_school_1.jpg</t>
+  </si>
+  <si>
+    <t>Здание школы №2. Фото: архив БиробиджанLive</t>
+  </si>
+  <si>
+    <t>https://sun9-72.userapi.com/s/v1/ig2/Iw3xii9IAj8pyPb0RQm3E9e_E8Et8Zp0XQHez2ap-bLz3RjgtZyJQOU1xrRVdII4ES-CPlSwgm2Q2rswviMydTKq.jpg?quality=96&amp;as=32x15,48x23,72x35,108x52,160x77,240x115,360x173,480x231,540x260,640x308,720x346,1080x520,1280x616&amp;from=bu&amp;cs=1280x0</t>
+  </si>
+  <si>
+    <t>В биробиджанском дворе. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>https://avatars.dzeninfra.ru/get-zen_doc/10349846/pub_649e8286f04be63b48f8b4eb_649e8af8334ff146b824463a/scale_1200</t>
+  </si>
+  <si>
+    <t>images/bir_15.jpg</t>
+  </si>
+  <si>
+    <t>Табличка ул. Горького на русском и идише</t>
+  </si>
+  <si>
+    <t>https://img-fotki.yandex.ru/get/51809/199172168.6b/0_1461f5_b475db4e_orig</t>
+  </si>
+  <si>
+    <t>images/bir_brodvey_5.jpg</t>
+  </si>
+  <si>
+    <t>Школа в с. Бирофельд</t>
+  </si>
+  <si>
+    <t>Община «Фрейд» (синагога Бейт-Менахем)</t>
+  </si>
+  <si>
+    <t>Редакция газеты «Биробиджанер Штерн»</t>
+  </si>
+  <si>
+    <t>Кинотеатр «Родина»</t>
+  </si>
+  <si>
+    <t>Ресторан «Симха»</t>
+  </si>
+  <si>
+    <t>Заповедник «Бастак»</t>
+  </si>
+  <si>
+    <t>Биробиджан был основан в 1916 году как станция Тихонькая в рамках освоения земель вокруг Амурской железной дороги. При станции был основан поселок. В 1928 году, после принятия постановления Президиума ЦИК СССР о закреплении за трудящимися евреями свободных земель в Приамурье Тихонькая стала базой приема переселенцев и центром снабжения переселенческого района. В 1931 году поселку было присвоено название Биробиджан – в честь протекающих в нем рек, а в 1937 году он уже стал городом.
+В 1930-х годах Биробиджан активно застраивался и развивался: возникали артели, строились дома, школы, издавались газеты и журналы, работало радио, увеличивалось население. Биробиджан являлся распределительным железнодорожным центром Еврейской автономной области.
+В годы репрессий и Великой Отечественной войны население города сильно пострадало: многие были арестованы и сосланы в лагеря, во время войны ушли на фронт и не вернулись. После войны Биробиджан не избежал гонений в связи с борьбой с космополитизмом.
+Послевоенные репрессии нанесли решающий удар проекту развития Биробиджана как национального центра. Практически прекратилась официальная поддержка инициатив, связанных с развитием и поддержанием еврейской культуры.
+В 1990-е годы подавляющее большинство биробиджанских евреев эмигрировало из России, преимущественно, в Израиль, отчего количество еврейского населения в городе сильно упало.
+Постепенно стали закрываться городские предприятия. Однако, произошло значительное оживление в развитии еврейской культуры: в городе начали работать еврейские общины, в университете открыта кафедра по изучению идиша, проводятся регулярные фестивали и праздники.</t>
+  </si>
+  <si>
+    <t>Амурзет – село в Еврейской автономной области, название которого расшифровывается как «Амурское земельное еврейское товарищество». Официально оно основано в 1929 году, хотя первые переселенцы прибыли сюда годом ранее. Основатель – уполномоченный КомЗЕТа Л.Г. Баскин. В 1929-м году организовали еврейский сельсовет, построили Дом Советов, столовую, переселенческий пункт, начальную школу и жилые дома. С 1934 года Амурзет становится центром Октябрьского (тогда Сталинского) района.
+Уже в 1928 году здесь возник колхоз «Ройтер Октябрь» («Красный Октябрь»), который не раз признавался лучшим и собирал рекордные урожаи. Местные жители сел Екатерино-Никольское и Пузино помогали переселенцам осваивать сельский труд. По воспоминаниям председателя сельсовета С. Бравермана, в 1929 году пароход «Чичерин» доставил первые 12 семей из Украины. Переселенцы застали на берегу лишь две нанайские фанзы, дубняк и орешник, но быстро взялись за топоры. Через два года три коммуны уже засевали около 30 гектаров, а к 1934 году в селе насчитывалось 27 домов и десятки тракторов. Серьёзным ударом стали репрессии – как враг народа был исключён из комсомола и репрессирован директор местной школы А. Ходос.
+С 1960-х годов в Амурзете работал аэропорт, который планировали расширить для рейсов в Китай. В октябре 1984 года открыт районный краеведческий музей.
+В настоящее время основу местной экономики по-прежнему составляет сельское хозяйство: в окрестностях села выращивают сою, зерновые. Работает средняя общеобразовательная школа, многопрофильный лицей с собственной производственной базой, детский сад, районная больница.</t>
+  </si>
+  <si>
+    <t>Бирофельд – село в Биробиджанском районе Еврейской автономной области, административный центр Бирофельдского сельского поселения. Расположено в 46 км от Биробиджана на левом берегу реки Малая Бира. Население по переписи 2022 года – 1 057 человек.
+Название села переводится с идиш как «Бирское поле». Бирофельд возник не на пустом месте: в 1910 году здесь была основана деревня Александровка, но к середине 1920-х годов из-за засухи и пожаров она пришла в упадок. Летом 1928 года на место сгоревшего села прибыли 224 еврейских переселенца.
+Село называют «колыбелью еврейского переселения» на Дальний Восток. Первое время оно рассматривалось как будущий административный центр Биро-Биджанского национального района, однако предпочтение в итоге отдали станции Тихонькая (Биробиджан). Тем не менее именно в Бирофельде в июле 1928 года был создан первый на Дальнем Востоке еврейский сельсовет. Тогда же здесь начала выходить газета «Бирофельд Эмес» («Бирофельдская правда») – первая районная газета в будущей автономии. В 1930 году в селе открылась первая изба-читальня.
+К началу 1930-х годов переселенческий колхоз «Бирофельд» насчитывал 282 колхозника, имел 1 550 гектаров посевов. Особой гордостью была пасека из 1 250 ульев. В селе были построены 120 новых квартир, кооператив, больница на десять коек, еврейская школа первой ступени.
+В годы Великой Отечественной войны жители Бирофельда активно помогали фронту, отправляю теплые вещи и продовольствие.
+С 1940 по 1994 год жизнь села была тесно связана с авиацией. Рядом с Бирофельдом действовал военный аэродром, где базировались истребительные и вертолетные полки. В послевоенные годы в селе работал духовой оркестр, кинотеатр. В 1958 году местные колхозы объединили в совхоз, был построен крупнейший в области животноводческий комплекс.
+Сегодня Бирофельд – одно из крупнейших сел Биробиджанского района, объединяющее пять окрестных населенных пунктов. В селе сохранилась развитая инфраструктура: средняя школа, детский сад, дом-интернат для пожилых, фельдшерско-акушерский пункт, Дом культуры, комната-музей ветеранов. Действуют волонтерские и общественные организации.</t>
+  </si>
+  <si>
+    <t>Валдгейм – село в Биробиджанском районе Еврейской автономной области, административный центр Валдгеймского сельского поселения. Название переводится с идиш как «дом в лесу».
+Село основано 27 мая 1928 года в ходе кампании по землеустройству трудящихся евреев. Группа переселенцев под руководством Лейба Гефена прибыла на место и поставила первые шалаши. Первоначально здесь находилась казарма, затем переселенческий пункт Худзиновка. Уже к осени 1928 года были построены первые дома, а к июню 1929 года насчитывалось 10 жилых домов и 20 хозяйственных построек. В октябре 1929 года переселенцы объединились в колхоз «Валдгейм», а в 1930 году село получило официальное название.
+В 1930-е годы Валдгейм стал одним из передовых хозяйств района. В 1933 году здесь организована первая женская бригада овощеводов. Помимо свиноводства, огородничества и пчеловодства, работали кирпичный завод, швейная мастерская, чулочная артель. Имелись клуб на 300 мест, школа, ясли-сад, хлебопекарня, почта, больница.
+В 1950 году к колхозу присоединён колхоз «20 лет Октября» из села Птичник, новое хозяйство названо «33-я годовщина Октября». Спустя десять лет к нему присоединились колхозы сел Желтый Яр и Пронькино, а укрупнённый колхоз получил название «Заветы Ильича».  В 1965 году колхоз стал лучшим в дальневосточной зоне.
+В настоящее время в Валдгейме находятся районная больница, районный краеведческий музей, районная библиотека, дом культуры, православный храм во имя святых Веры, Надежды и Любови, средняя школа, детский дом для детей-инвалидов, детская музыкальная школа, детский сад, отделение связи и несколько магазинов.</t>
+  </si>
+  <si>
+    <t>Соцгородок – село в Смидовичском районе Еврейской автономной области. Сегодня это тихое поселение с населением менее 150 человек (2025 г.). Его название – не случайный отголосок советской эпохи, а памятник амбициозному социально-утопическому эксперименту: попытке создать «социалистический штетл» – поселение нового типа, где еврейские трудящиеся должны были отбросить традиционный уклад и заняться производительным сельским трудом.
+Идея возникла в середине 1920-х годов в среде левой еврейской интеллигенции США. Ключевым идеологом стал социолог Чарльз Кунц (уроженец местечка под Киевом), который в 1924 году участвовал в создании организации ИКОР (еврейская колонизационная организация в России). В 1928 году советское правительство закрепило за КомЗЕТом земли в Приамурье для сплошного заселения трудящимися евреями. Кунц прибыл в Биробиджан и разработал программу создания коммун-соцштетлов.
+Летом 1931 года на базе коммуны «ИКОР» (основанной в 1928 году двенадцатью бывшими учащимися еврейской агрошколы из Белоруссии) был организован агроиндустриальный комбинат «Соцгородок» в трёх километрах от станции Волочаевка-2. Сюда приезжали идеалисты из США, Аргентины, Германии, Польши, Румынии. Из-за границы поступала современная техника: тракторы «Фордзон», электростанции, экскаваторы, грузовики. За два с половиной года вырос процветающий посёлок с двухэтажными общежитиями, семилетней школой на идише, библиотекой, клубом, столярной мастерской, кузницей, электростанцией, молочно-свиным хозяйством, пекарней. Коммуна стала образцовым хозяйством на весь Дальневосточный край.
+Однако золотой век оказался недолгим. Неурожай 1933 года вызвал голод и отток части переселенцев. Настоящая трагедия разразилась в 1937 году: волна репрессий обрушилась на иностранных членов коммуны. Председатель колхоза Иосиф Форер (из Аргентины) и десятки других были арестованы как «шпионы». Клуб и школа закрылись. В 1939 году колхоз переименовали и присоединили к соседнему хозяйству. К началу Великой Отечественной войны от былого процветания почти не осталось следа.
+После войны связи с ИКОРом были разорваны, само название стало опальным. В 1960–70-е годы поселок пережил ограниченный подъём как центр лесной промышленности (мебельный цех Тунгусского ДОКа), но идеологическая основа была утрачена. К концу советской эпохи промышленность пришла в упадок, население массово покинуло село. Сегодня Соцгородок – это тихое поселение, где живут в основном пенсионеры. Название осталось горькой иронией – немым напоминанием о грандиозной мечте, разрушенной ветром истории.</t>
+  </si>
+  <si>
+    <t>История завода началась в 1938 году с основания Биробиджанского обозного завода, который выпускал тележные ходы, сани и повозки. В годы войны предприятие переключилось на выпуск автоприцепов, дегазационных повозок и даже пуль для фронта. В 1960 году завод был перепрофилирован на выпуск гусеничных комбайнов и получил новое имя — «Дальсельмаш». К 1970-м годам он стал единственным в СССР производителем зерноуборочных комбайнов на гусеничном ходу, выпуская 97% всей продукции этого сегмента. В его цехах трудились более 3 тысяч рабочих, а годовой выпуск достигал 3 тысяч единиц техники. Продукция завода шла на экспорт в социалистические страны, а комбайн СКГ-4 в 1970 году получил серебряную медаль на выставке в Будапеште.
+После распада СССР завод столкнулся с тяжелым кризисом. В 1992 году прекратился выпуск кормоуборочных комбайнов, а годом позже предприятие приватизировали. Несмотря на попытки модернизации, уже в 2004 году «Дальсельмаш» признали банкротом.
+Большинство заводских корпусов сегодня заброшены и представляют собой руины. Несмотря на это, комбайны, собранные здесь десятилетия назад, все еще работают на полях области.
+Память о заводе сохраняется в названиях учреждений и объектов, а его наследие продолжает жить в развивающейся социальной инфраструктуре. В микрорайоне Дальсельмаш в 2025 году завершилось благоустройство сквера имени Иосифа Бумагина. Сердцем района остается стадион «Дальсельмаш», построенный в 1965 году силами заводчан. В настоящее время запланирована его масштабная рекострукция, а в зимнее время он по-прежнему работает как самый большой открытый каток Биробиджана.</t>
+  </si>
+  <si>
+    <t>Обелиск жертвам Холокоста находится во дворе еврейского общинного центра «Фрейд» в Биробиджане. Памятник представляет собой вертикальную плиту из черного отшлифованного камня, который известен как «плачущий гранит» благодаря вкраплениям блестящей слюды, создающей эффект застывших слез. На лицевой стороне высечена шестиконечная звезда Маген Давид и надпись: «Памяти жертв Холокоста. 1933–1945 годы».
+Памятник был открыт 20 апреля 2001 года по инициативе еврейской общины «Фрейд» при поддержке регионального правительства. Камень изготовили в Хабаровске, затем доставили и установили в Биробиджане. До его появления в области не было официального места, чтобы почтить память жертв нацистского режима.
+Этот обелиск уникален для России: он стал первым в стране памятником, датированным 1933–1945 годами — то есть охватывающим весь период нацистского террора от прихода Гитлера к власти до окончания Второй мировой войны. Все остальные подобные мемориалы открывались с датой «1941–1945». Кроме того, это был первый памятник жертвам Холокоста на всем Дальнем Востоке. Со временем мемориал стал естественным центром притяжения для всех, кому небезразлична память о трагедии.
+Обелиск остается действующим мемориалом и ежегодно служит главной площадкой для памятных церемоний. 27 января, в Международный день памяти жертв Холокоста, у его подножия собираются десятки людей — представители общины, студенты, школьники, ветераны и официальные лица области. Собравшиеся зажигают свечи и возлагают к памятнику маленькие камни — символ окаменевших слез по безвинно погибшим. Затем раввин читает поминальную молитву Кадиш, и присутствующие склоняют головы в минуте молчания.</t>
+  </si>
+  <si>
+    <t>Первый обелиск установили в 1947 году по инициативе  региональных властей. Памятник изготовили из бираканского мрамора японские военнопленные. В 1970 году на его месте появилась новая бетонная стела со скошенной вершиной и надписью «Вечная слава героям...». В 1975 году сквер, где располагался мемориал получил имя 30-летия Победы. В 1985 году к 40-летию Победы провели масштабную реконструкцию: памятник назвали «Боевая и Трудовая Слава» (скульптор Михаил Чернис), а сквер переименовали в Сквер Победы. Годом ранее здесь зажгли Огонь Славы, ставший позднее известным, как Вечным огонь. Позже появились памятные знаки воинам-интернационалистам и участникам СВО. В 2001 году в сквере построили часовню.
+В 2025 году, к 80-летию Победы, завершилась масштабная реконструкция (архитектор Константин Фомин) комплекса. Был открыт мемориал «Матерям победителей»: женщина-мать и двое склонивших колена воинов — солдат ВОВ и участник СВО. Обновлены стела, брусчатка, добавлена подсветка, заложена Аллея Героев. Вечный огонь зажгли от частицы, привезенной из Москвы. Сегодня обновленный сквер — основное место памяти о Великой Отечественной войне и торжественных церемоний в городе.</t>
+  </si>
+  <si>
+    <t>Сквер имени Героя Советского Союза Иосифа Романовича Бумагина находится в микрорайоне Дальсельмаш — том самом, который вырос вокруг легендарного завода.
+В 1960-е годы на территории будущего сквера был сооружён мемориальный комплекс в память о Победе в Великой Отечественной войне. Его центральный элемент — танк-памятник «ИС-3», который и сегодня привлекает внимание и взрослых, и детей, став одной из визитных карточек микрорайона.
+В 1966 году, 9 мая, здесь появился ещё один важный памятник — самому Герою Советского Союза Иосифу Бумагину. Главным героем, давшим имя скверу и целому микрорайону, стал Иосиф Романович Бумагин. В Биробиджан он переехал в 1937 году из Белоруссии, работал на обозостроительном заводе — сначала в кузнечном цехе рабочим, затем мастером. На фронт попал только осенью 1944 года, отправившись после переподготовки во Владивостокское военное училище. Свой подвиг он совершил 24 апреля 1945 года при штурме города Бреслау (ныне Вроцлав): под ураганным огнём противника лейтенант Бумагин подобрался к дому, где засели два вражеских пулемёта, и забросал первую огневую точку гранатами. Ценой собственной жизни он обеспечил успех наступления. Похоронен он там же, в Польше, всего за две недели до Победы.</t>
+  </si>
+  <si>
+    <t>Гимназия №1 — старейшее общеобразовательное учреждение Еврейской автономной области, ведущее свою историю с октября 1932 года. Тогда в рабочем поселке Биро-Биджан была открыта еврейская школа фабрично-заводского обучения №2. Первое здание было деревянным, барачного типа, учеников было так много, что мест катастрофически не хватало.
+В 1936 году для школы построили новое каменное здание, в котором к 1938–1939 учебному году обучалось уже 497 детей. Среди её первых педагогов были известный поэт, писатель и журналист Бузи Миллер, создатель первого букваря на идиш Григорий Рабинков, поэтесса и художница Римма Лавочкина.
+Однако уже к концу 1930-х годов школа столкнулась с тяжелейшими проблемами. Родители всё чаще не желали отдавать детей в национальную школу, поскольку к тому времени уже были закрыты все высшие учебные заведения на еврейском языке (в Москве, Киеве, Минске), и они не видели для своих детей дальнейшей перспективы. Многие книги на идиш были уничтожены, после массовых репрессий возникли проблемы с преподаванием еврейского языка.
+В военные годы в школе размещался госпиталь, уроки шли в две смены, но при этом работал драматический кружок.
+Основной удар по школе пришёлся на 1947–1949 годы. Из-за полного отсутствия учебников на еврейском языке было решено перевести преподавание всех предметов на русский, оставив идиш лишь в качестве отдельного предмета. Наполняемость старших классов резко упала, и в 1948 году школу преобразовали из средней в семилетнюю. Наконец, в 1949 году в Биробиджане была закрыта последняя школа, в которой велось преподавание на идише. Одновременно был почти полностью уничтожен еврейский фонд областной библиотеки: сожжено 40 тысяч томов, в их числе практически все учебники.
+Ситуация стала меняться только в начале 1990-х годов, с принятием закона о языках народов России и новой Конституции РФ. В 1992 году на базе школы №2 открылась государственная еврейская школа с углублённым изучением еврейских языков, истории и культуры еврейского народа, ставшая центром еврейского образования в автономии.
+В сентябре 2010 года школа переехала в современное трёхэтажное здание на 1000 мест, оснащённое бассейном и большим спортивным городком. 27 июня 2016 года постановлением мэрии города школа получила статус гимназии и была переименована в гимназию №1.
+Сегодня здесь действует детская школьная республика, работает музей, проводятся ежегодные парады наук и военно-спортивные эстафеты, приуроченные к памятным датам.</t>
+  </si>
+  <si>
+    <t>Синагога «Бейт Тшува» (с иврита  «Дом покаяния»), в каком-то смысле является наследницей первой биробиджанской синагоги, открытой в 1947 году. Эта первая синагога появилась благодаря усилиям и помощи американской еврейской организации  «Амбиджан»: власти под международным давлением разрешили общине приобрести частный дом. Торжественное открытие совпало с празднованием Йом-Кипура и собрало около 400 человек при официальной численности общины всего в 57 верующих. В те годы иудеям жилось нелегко: местная пресса публиковала статьи с требованием усилить антирелигиозную пропаганду, а раввинов и священников лишали избирательных прав; многие верующие были репрессированы.
+В 1956 году первая синагога сгорела при загадочных обстоятельствах — по одной из версий, мог иметь место поджог. Пламя быстро охватило деревянное здание, но прихожане сумели спасти главные святыни: свитки Торы и старинные молитвенники. После пожара власти отказались выделить новое помещение, и несколько лет верующие собирались тайно.
+Нынешнее деревянное здание синагоги было построено в 1986 году и считается последней синагогой, открытой в Советском Союзе. Общину официально зарегистрировали в 1996 году. Долгое время здание оставалось в аварийном состоянии, но в 2017 году на частные пожертвования провели капитальный ремонт. Интерьер сохраняет дух «дома-музея»: здесь находятся спасенные из огня пожара первой синагоги реликвии — молитвенники первых переселенцев и свиток Торы старше 200 лет, а также уникальная мебель 1957 года (шкаф для свитков Торы и кафедра для чтения Торы), созданная еврейскими мастерами.
+Сегодня «Бейт Тшува» — действующий духовный центр, открытый для прихожан и туристов, памятник эпохи и символ возрождения еврейской религиозной жизни в автономии.</t>
+  </si>
+  <si>
+    <t>Дворец культуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Биробиджанская телевизионная башня, установленная на вершине сопки Тихонькой, по праву считается главным символом Биробиджана. Развитие телерадиовещания в регионе началось в 1938 году, когда в Биробиджане заработал первый радиопередатчик. В 1961 году на сопке появилась 55-метровая телебашня, с помощью которой в городе начали транслировать черно-белые телепередачи из Хабаровска.
+Качество сигнала оставляло желать лучшего, поэтому, в 1970 году было принято решение о строительстве новой телебашни. Сооружение должно было обеспечить уверенный телевизионный сигнал для большей части Еврейской автономной области. Уже в 1971 году на сопке Тихонькой, видной практически из любой точки города, начала расти ажурная металлическая конструкция. В январе 1973 года была завершена установка и настройка антенн.
+Собственная высота башни составляет 225 метров (по другим данным — 234 метра). На её вершине установлен 16-метровый шпиль. Благодаря тому, что башня стоит на сопке высотой около 100 метров, общая высота сооружения над уровнем моря достигает почти 350 метров. Это одна из самых высоких телевышек в стране.
+Контур телевышки вместе с сопкой, на которой она стоит, и главной рекой города Бирой стал элементом герба Биробиджана. В 2012 году, к 75-летию города, на телебашне смонтировали архитектурную подсветку. Освещение разделено на три уровня: два нижних яруса освещают прожекторы, а верхний — восемь светодиодных прожекторов, которые меняют цвет в зависимости от заданной программы. Многоцветная динамическая подсветка включается каждые выходные и праздники. Биробиджанская телевышка стала единственной на Дальнем Востоке с подобной иллюминацией.
+</t>
+  </si>
+  <si>
+    <t>История вокзала началась задолго до основания города. В 1912 году при строительстве Амурской железной дороги на этом месте возник полустанок Тихонькая. Первое пассажирское здание представляло собой небольшой деревянный домик. С 1928 года станция стала местом прибытия первых еврейских переселенцев, что дало мощный импульс для развития всего региона.
+В 1933 году было принято решение о строительстве нового каменного здания. Эскизный проект выполнил знаменитый швейцарский архитектор Ханнес Мейер, в то время работавший над генеральным планом Биробиджана. Возведение велось силами заключенных 13-го отделения БАМЛАГа в рекордно короткие сроки, и 29 декабря 1935 года здание было сдано в эксплуатацию, став первым каменным зданием в городе.
+Здание стало настоящим украшением молодого города. Внутреннее убранство поражало воображение: вестибюль, выложенный мозаичными плитами бираканского мрамора; стены, отделанные панелями из ясеня; изящная лепнина на потолках в стиле постконструктивизма; помещения, оснащенные по последнему слову техники: зал ожидания, ресторан, библиотека, комната матери и ребенка, гостиница.
+К сожалению, спешка при строительстве привела к трагическим последствиям. Уже в 1937 году из-за допущенных просчетов произошел обвал потолка центрального вестибюля, уничтоживший часть уникальных интерьеров. Восстановительные работы были проведены, но в 1938 году случился сильный пожар, который полностью уничтожил всё великолепное внутреннее убранство вокзала.
+После войны здание было восстановлено, но его интерьеры стали намного скромнее. Именно внешний вид, обретенный вокзалом в середине 1940-х годов, во многом сохранился до наших дней.
+К 70-летию области проведена масштабная реконструкция здания. Тогда же привокзальная площадь обрела современный вид: была выложена брусчатка, установлены символический фонтан с восьмиметровой менорой и скульптурная композиция «Переселенцам».
+Сегодня здание вокзала является объектом культурного наследия регионального значения. С 2025 по 2026 год здесь проходит очередная масштабная реставрация, приуроченная к 90-летию здания.</t>
+  </si>
+  <si>
+    <t>Памятник классику еврейской литературы Шолом-Алейхему (настоящее имя — Соломон Наумович Рабинович) был торжественно открыт 10 сентября 2004 года в дни празднования 70-летия Еврейской автономной области. Монумент расположен в сквере в начале главной улицы Биробиджана, носящей имя писателя.
+Идея установки памятника возникла задолго до его воплощения. Впервые предложение увековечить память писателя в Биробиджане выдвинул в 1947 году скульптор Абрам Мильчин, который даже выполнил пластилиновый макет будущей скульптуры. Однако тогда этим замыслам не суждено было сбыться. Повторно к идее вернулись в 1988–1989 годах: горисполком объявил конкурс на проект памятника, был даже открыт специальный счёт для сбора средств. В конкурсе участвовали около десяти художников из Москвы, Красноярска, Биробиджана и даже Израиля, но ни один из проектов не был реализован.
+Новая попытка была предпринята в 2002 году по инициативе еврейской областной общественной писательской организации, общины «Фрейд» и мэрии Биробиджана. Был объявлен конкурс, в котором участвовали скульпторы из Москвы, Хабаровска, Благовещенска, Биробиджана, а также китайских городов Харбина и Хэгана. Выбор пал на биробиджанского художника Владислава Цапа, разработавшего макеты памятника. Воплотил замысел китайский скульптор Цю Вэйгуй. Отливка и изготовление скульптуры были выполнены в китайском городе Цзямусы, правительство которого взяло на себя все расходы по созданию монумента.
+Скульптура представляет собой двухметровое медное изображение писателя, сидящего в кресле с ручкой и бумагой в руках. Взгляд Шолом-Алейхема устремлен вперед, на центральную улицу города, носящую его имя. Постамент выполнен из камня, на нём размещены бронзовые барельефы со сценами из жизни еврейских местечек, а также изображения героев произведений писателя. Табличка с именем и годами жизни писателя содержит надпись на двух языках — русском и идиш.</t>
+  </si>
+  <si>
+    <t>Возведение синагоги стало возможным благодаря возрождению еврейской общины в постсоветский период. В 1997 году общественность города приняла решение о создании еврейской религиозной общины «Фрейд». Ключевую роль в этом сыграл Лев Тойтман, участник Великой Отечественной войны, кавалер двух орденов Славы, почётный гражданин ЕАО, который руководил общиной десять лет.
+В 2002 году по предложению главного раввина России Берла Лазара в Биробиджан из Израиля приехал раввин Мордехай Шейнер с супругой и детьми. К тому моменту вопрос о строительстве новой синагоги уже обсуждался, и, пока шли подготовительные работы, раввин проводил службы в помещении общинного центра.
+10 сентября 2004 года, в год празднования 70-летия Еврейской автономной области, состоялось торжественное открытие синагоги «Бейт Менахем». Церемонию провел главный раввин России Берл Лазар. Здание синагоги было спроектировано и построено в соответствии со всеми канонами иудейской храмовой архитектуры.
+«Бейт Менахем» с иврита переводится как «Дом утешителя». Оно дано в честь Любавичского Ребе Менахема-Мендла Шнеерсона — одной из самых значительных фигур в иудаизме XX века, лидера хасидского движения «Хабад».
+«Бейт Менахем» представляет собой не только молитвенный дом, но и пространство для духовного и культурного развития общины. Здесь находятся: шаббатный зал, место для молитв и собраний общины, детско-юношеский центр еврейской культуры, музей иудаики, биробиджанский еврейский народный университет, творческие клубы и благотворительная организация «Хэсэд».</t>
+  </si>
+  <si>
+    <t>Приамурский государственный университет имени Шолом-Алейхема — единственное высшее учебное заведение на территории Еврейской автономной области. Сегодня это современный многопрофильный университет, ведущий центр образования, науки и культуры всего региона.
+Первые шаги к созданию системы педагогического образования в регионе были сделаны ещё в 1930-е годы. 1 октября 1932 года в Биробиджане открылся педагогический техникум, который готовил учителей начальных классов. В 1935 году состоялся первый выпуск. Техникум, позже преобразованный в педагогическое училище, оставался основным источником педагогических кадров для области на протяжении нескольких десятилетий. Лишь в 1998 году он вошёл в состав Биробиджанского государственного педагогического института, завершив свой самостоятельный путь.
+Биробиджанский государственный педагогический институт был основан постановлением Совета Министров СССР от 1 марта 1984 года, однако фактическая реализация проекта началась в 1989 году. Первый набор был сделан в 1989 году. В 1994 году институт выпустил первых дипломированных специалистов: 119 человек.
+Развитие института было стремительным. К 1992 году на пяти факультетах вуза уже обучалось около 600 студентов. В 2005 году, с ростом потребностей области в высококвалифицированных кадрах в экономике, управлении и технической сфере, институт был преобразован в Дальневосточную государственную социально-гуманитарную академию.
+Ключевым событием стало присвоение вузу статуса университета. Приказом Министерства образования и науки Российской Федерации от 24 ноября 2011 года академия была переименована в Приамурский государственный университет имени Шолом-Алейхема.
+Сегодня университет — это современный образовательный комплекс, охватывающий все уровни подготовки. В его структуру входят 9 факультетов, объединяющих 22 кафедры. В университете обучаются около трёх тысяч студентов, в том числе порядка двух тысяч на очном отделении. Учебное заведение реализует программы высшего образования по 28 направлениям бакалавриата, 16 магистерским программам и аспирантуре.</t>
+  </si>
+  <si>
+    <t>Городской Дворец культуры сегодня является крупнейшим учреждением культурно-досугового типа в Еврейской автономной области. Он представляет собой здание с мощными колоннами и огромными окнами с полукруглым верхом.
+В начале 1930-х годов здание под будущий Дворец культуры начали возводить на улице Ленина, и на его стройке даже работал будущий известный писатель Эммануил Казакевич. Однако завершить его не удалось, и недостроенное здание со временем передали другому ведомству. К идее вернулись только в конце 1950-х годов.
+Строительство началось в 1957 году силами завода силовых трансформаторов. С 1959 года к работам подключился трест «Биробиджанстрой», и через четыре года грандиозный проект был завершён. Вопреки хрущевской борьбе с архитектурными излишествами, новый Дворец был возведён по проекту, заказанному ещё в сталинскую эпоху. Его автором выступил московский архитектор Константин Константинович Барташевич.
+8 июля 1963 года здание было официально принято в эксплуатацию. А 11 июля, в день торжественного открытия, первый концерт посетили строители, пришедшие на сцену, которую они помогли создать. Вскоре Дворец стал центром притяжения горожан. Здесь работали 12 кружковых комнат, действовала стационарная киноустановка, проходили регистрации брака и новогодние утренники. С 1989 года в здании находится Музей современного искусства.
+Сегодня здесь работают 27 клубных формирований, 15 из которых носят звания «Народный».</t>
+  </si>
+  <si>
+    <t>Газета «Биробиджанер Штерн» (в переводе с идиша — «Биробиджанская звезда») — является одним из старейших периодических изданий Еврейской автономной области.
+Ее история началась осенью 1930 года, когда на станции Тихонькая, где только зарождался будущий Биробиджан, полным ходом шло заселение еврейских переселенцев. Им был крайне необходим источник информации на родном языке.
+Первый номер газеты вышел 30 октября 1930 года решением секретариата Дальневосточного краевого комитета партии. Изначально предполагалось, что это будет районная газета. Редакция ютилась в маленьком деревянном домике на улице Октябрьской, где нередко не было электричества, и работать приходилось при свете керосиновых ламп. Печатный станок и еврейский шрифт для газеты были привезены из Харбина (Китай). В 1934 году, с образованием Еврейской автономной области, газета получила статус областной.
+Судьба издания неразрывно связана с репрессиями, обрушившимися на его сотрудников в конце 1930-х годов. Первая волна арестов прошла уже в 1937–1938 годах, когда были репрессированы многие сотрудники.  В 1937 году по обвинению по «политической» 58-й статье был арестован и расстрелян первый редактор газеты Янкель Левин. Волна репрессий достигла своего апогея в конце 1940-х годов, когда по стране прокатилась антисемитская кампания по борьбе с «космополитизмом». В 1948-1949 годах были репрессированы редактор Бузи Миллер, переводчик Григорий Рабинков, ответственный секретарь Наум Фридман и многие другие.
+Несмотря на все испытания, газета смогла выстоять, сохранив свою уникальность. С 1990 года «Биробиджанер Штерн» начала выходить на двух языках — идиш и русском, и сегодня является единственной газетой в России, имеющей постоянную полосу на идише.
+Сейчас в редакции трудится небольшой, но очень преданный делу коллектив. Газета активно участвует в общественной и культурной жизни области. Так, к своему 95-летию издание проделало колоссальную работу по оцифровке своего архива, переведя в электронный формат тысячи страниц, чтобы сделать свою историю доступной для всех.</t>
+  </si>
+  <si>
+    <t>Путь школы начался в 1928 году, когда она была открыта как школа первой ступени с преподаванием на идише. В то время в ней работали всего два класса, а само здание было небольшим, бревенчатым, с печным отоплением. Учебное заведение быстро стало важной частью жизни растущего села.
+Годы шли, и вместе с ними менялась и развивалась школа. В послевоенный период в ней была открыта комната-музей ветеранов, ставшая хранительницей памяти о подвиге односельчан в Великой Отечественной войне. И по сей день школа проводит классные часы и мероприятия, посвященные этому важному событию. В 1970-е годы учреждение обрело своего первого директора.
+2009 году здесь установили пластиковые окна и открыли современный компьютерный класс. К своему 90-летнему юбилею в 2018 году учебное заведение подошло уже как современный образовательный комплекс, реализующий не только программы начального, среднего и основного общего образования, но и дошкольного. Сегодня на ее базе работают три разновозрастные дошкольные группы.</t>
+  </si>
+  <si>
+    <t>Биджан – одно из крупнейших и старейших сел Ленинского района Еврейской автономной области. Основано в 1873 году переселенцами из соседних деревень Вецлево и Дежнево. Название происходит от тунгусского «бира джикан» – «стойбище людей в далёком месте». Первые жители занимались охотой, рыболовством и землепашеством, а к 1910 году в селе проживало уже около 600 человек.
+До 1926 года Биджан входил в состав Екатерино-Никольской волости. В марте 1929 года здесь образовали колхоз имени Ф.К. Мухина – одного из организаторов советской власти в Приморье. Первым председателем стал Павел Терентьевич Попов, а в 1933 году, когда колхоз возглавил Николай Федорович Золотарев, в Биджан прибыли первые тракторы.
+В годы Великой Отечественной войны на фронт ушли более ста биджанцев, около сорока из них не вернулись. В 1967 году в селе установили мемориальный памятник погибшим землякам. После войны, в 1948 году, здесь создали машинно-тракторную станцию, а в январе 1960 года ее ликвидировали, организовав вместо нее совхоз «Добринский». В него вошли колхозы сел Биджан, Венцелево, Преображеновка, Новотроицкое. До 1990 года совхоз оставался одним из крупнейших сельхозпредприятий ЕАО и основой экономики Биджана.
+В 1960–1970-е годы в селе построили больницу, пекарню, дом культуры, кинотеатр, детский сад и новую школу.
+Сегодня в Биджане действуют сельскохозяйственные, торговые и строительные предприятия, работают администрация поселения, медицинская амбулатория, средняя школа, детско-юношеская спортивная школа, детский сад, дом культуры, библиотека и сеть магазинов.</t>
+  </si>
+  <si>
+    <t>Кульдур – поселок в Облученском районе ЕАО, знаменитый своими горячими источниками, ставшими основой первого санатория Дальнего Востока.
+Название происходит от тунгусского «горячий». Местные источники с древности почитались коренным населением. По легенде, старый охотник выследил раненого изюбра и увидел, как зверь опустил больной бок в ямку с горячей водой, а рядом лечились волк и медведь. Изумленный охотник воскликнул: «Хуль-Джи-Ури» – что в переводе с тунгусского означает «целебный источник». Позже русские переселенцы узнали об источниках.
+Первые печатные сведения о Кульдуре появились в 1897 году. Главное лечебное средство – термальная азотно-кремниевая минеральная вода с температурой у выхода 72 °C. Она помогает при более чем 300 заболеваниях: болезнях опорно-двигательного аппарата, нервной системы, кожи и других.
+Особую известность Кульдур приобрел в 1910-е годы, во время строительства Амурской железной дороги. Поток желающих лечиться рос с 35 человек в 1914 году до более 2,5 тысяч в 1918-м. В годы Гражданской войны курорт пришел в упадок, но в 1920 году его национализировали. В 1920-е годы построили лечебные корпуса, электростанцию, метеостанцию, улучшили дорогу.
+В годы Великой Отечественной войны кульдурские лечебницы стали военными госпиталями: раненые проходили реабилитацию в 3–4 недели вместо нескольких месяцев. После войны Кульдур превратился в ведущую здравницу Дальнего Востока.
+Сегодня в Кульдуре работают четыре санатория: профсоюзный «Кульдур» (в 2025 году полностью перешедший в собственность ЕАО), частный «Санус», ведомственные «Горняк» и «Кульдурский». Санаторий «Кульдур», носящий статус курорта федерального значения, находится в процессе передачи региону и требует серьезной модернизации. В планах правительства области – привлечение инвесторов для реновации здравницы, что позволит создать современный курорт и возродить былую славу уникального уголка Дальнего Востока.</t>
+  </si>
+  <si>
+    <t>Теплоозерск – поселок городского типа в Облученском районе Еврейской автономной области. Расположен вблизи озера Теплое, подземные источники которого не дают ему промерзать зимой — отсюда и название. В 1916 году здесь основан железнодорожный разъезд Теплое Озеро. В 1928-м году на берегу озера построили Тепловский рыбоводный завод — один из первых на Дальнем Востоке.
+Главное событие произошло в 1949-м году: здесь запустили цементный завод, и поселок начал активно расти. В 1958 году Теплоозерск получил статус поселка городского типа. В советские годы здесь были асфальтированные улицы, фонтаны, построен парк аттракционов, два кинотеатра и Дом культуры.
+Сегодня жизнь Теплоозерска по-прежнему тесно связана с цементным заводом. Предприятие переживает непростой период: завод передан государству, численность работников сокращается. Однако на предприятии продолжается модернизация. Завод остается главной опорой посёлка: шефствует над больницей, помогает с ремонтом дорог и благоустройством.
+Тепловский рыбоводный завод — ровесник посёлка, основанный в 1928 году. Он по-прежнему работает, используя уникальные свойства озера Теплое для выращивания молоди кеты. В поселке благоустроен Сквер Победы, работает школа, детский сад, больница, Дом культуры. Население, по данным на 2025 год, составляет около 3,4 тысячи человек и продолжает сокращаться.</t>
+  </si>
+  <si>
+    <t>Официальной датой основания считается 27 мая 1928 года, когда было принято решение собрать разрозненные книжные коллекции в единую библиотеку, призванную обслуживать весь национальный район. Основу ее фонда составили книги, бережно привезенные первыми переселенцами в деревянных чемоданчиках и заплечных узлах, а также литература, подаренная библиотеками Москвы, Киева, Харькова и Минска.
+Долгое время учреждение ютилось в тесном деревянном доме по улице Постышева (ныне Ленина). Возведение нового здания началось в 1936 году, а торжественное открытие двухэтажного каменного строения по проекту архитектора Кобзаря состоялось уже в 1940 году.
+В 1946 году, к 30-летию со дня смерти писателя, областной библиотеке было присвоено имя еврейского писателя Шолом-Алейхема, чье творчество стало символом еврейской культуры. Уже к концу 1940-х годов фонд еврейской литературы в библиотеке считался одним из крупнейших в стране, насчитывая около 35 тысяч экземпляров книг на идише. Ситуация кардинально изменилась в 1949 году, когда в рамках государственной кампании по борьбе с «космополитизмом» началось планомерное уничтожение культурного наследия: из фондов изымалась литература на еврейском языке на основании секретных приказов, а процесс уничтожения носил публичный, демонстративный характер. В результате, по разным оценкам, к середине 1950-х годов еврейский книжный фонд библиотеки был уничтожен практически полностью.
+Уничтожение коллекции сделало ее восстановление крайне сложной задачей. Только в 1978 году стартовала работу по восстановлению еврейского книжного фонда. Позже, библиотека начала целенаправлено приобретать литературу по еврейской истории, культуре и религии. Сегодня фонд иудаики насчитывает тысячи уникальных изданий и является одной из главных гордостей библиотеки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Улица была заложена в начале 1930-х годов как одна из первых четырех улиц рабочего поселка. В 1932 году по решению местных властей улица стала носить имя советского партийного деятеля П.П. Постышева. 17 марта 1938 года улица была переименова в улицу Ленина, в связи с тем, что Постышев был объявлен врагом народа.
+Улица Ленина (Постышева) уникальна тем, что на ней сохранилась застройка 1930-1940-х годов, передающая «дух старого Биробиджана». По этой причине в 2023 году региональные власти признали улицу Ленина достопримечательным местом регионального значения.
+На улице Ленина, сформировавшей «старый центр», находятся важнейшие культурные объекты города: Биробиджанская областная филармония, областной краеведческий музей, синагога Бейт Менахем и др.
+В 1930-е годы на улице располагались и другие важные для молодого города здания, такие как Дом Советов (ныне мэрия), педагогическое училище и школа №2, которые впоследствии были снесены.
+Сегодня пространство вокруг площади имени Ленина остается главной точкой притяжения для общегородских праздников, концертов и фестивалей. Кроме того, в области реализуется проект «Еврейский квартал», который будет объединять исторические и культурные объекты по улице Ленина. </t>
+  </si>
+  <si>
+    <t>Решение о строительстве первого городского кинотеатра было принято в 1935 году, когда президиум облисполкома ЕАО утвердил соответствующий проект.Изначально чертежи кинотеатра были разработаны хабаровским Дальпрогором. Однако тогдашний председатель облисполкома Иосиф Либерберг настоял на существенной доработке проекта, так как считал, что одного зала на сто мест для растущей столицы области недостаточно. После его вмешательства в Биробиджане появился единственный на тот момент на Дальнем Востоке двухзальный кинотеатр.Доработкой занялся архитектор Павел Елисеевич Аппак.
+Строительство велось в 1936–1937 годах. Здание стало ярким образцом ранней сталинской архитектуры с элементами классицизма: его украшают колонны с капителями чистого коринфского ордера и акантовый орнамент. Торжественное открытие кинотеатра состоялось 7 ноября 1937 года — и с тех пор он неизменно встречает своих зрителей. Открытие было приурочено к праздничной дате — 20-летию Октябрьской революции.
+За свою долгую историю кинотеатр сменил три названия: с 1935 года, еще на этапе строительства он носил имя Г. Казакевича, журналиста, первого редактора газеты «Биробиджанская звезда». С 1937 года, после открытия он назывался «Биробиджан». Название «Родина» было присвоено кинотеатру только в 1966 году.
+В годы Великой Отечественной войны кинотеатр пережил сильный пожар, который уничтожил большой зрительный зал, бухгалтерию и архив. Однако жизнь здесь не остановилась. Пока шло восстановление, сеансы продолжали проводить прямо в фойе. Перед каждым показом играл штатный оркестр, выступали самодеятельные и профессиональные артисты эстрады.
+В дальнейшем, здание кинотеатра несколько раз ремонтировалось: в 1984 году был капитальный ремонт с закупкой нового оборудования и появлением полумягких кресел в большом зале, в 2002 и 2011 годах здание реконструировалось. В его стенах помимо кино, стали проходить выставки и фестивали.
+В 2013 году кионтеатр открылся после очередного ремонта. В нем появились два зала — «Красный» и «Черный», был установлен цифровой проектор для 3D-показов, оборудованы зоны отдыха в стиле книжного кабинета и скрипки, а пол украсили изображения старых еврейских улиц.
+В 2014 году кинотеатр был признан объектом культурно-исторического наследия Еврейской автономной области.</t>
+  </si>
+  <si>
+    <t>Любовь (Люба) Шамовна Вассерман (1907–1975) родилась в бедной еврейской семье в польском местечке Славатыче. В 1925 году она эмигрировала в Палестину, где работала на изнурительных работах, вступила в местную компартию и в 1931 году издала свой первый поэтический сборник «Вечера» на идише.
+Вскоре, идеалы привели ее в далекий Биробиджан. В 1932 году, вслед за мечтой о создании «нового еврейского дома», Вассерман приехала в Советский Союз. В Биробиджане талант поэтессы раскрылся с новой силой. Она работала в легендарной газете «Биробиджанер штерн», заведовала отделом на идиш в областной библиотеке им. Шолом-Алейхема, вела передачи на областном радио, публикуя свои стихи и очерки. Она была частью плеяды местных литераторов.
+Судьба Любы Вассерман, как и многих деятелей еврейской культуры, была сломана в конце 1940-х годов. В 1949 году ее арестовали по сфабрикованному «Биробиджанскому делу № 68». Ее обвинили в «организованной антисоветской деятельности», направленной на обособление ЕАО от остального СССР. Результатом стали 10 лет сибирских лагерей.
+После освобождения в 1956 году и последовавшей реабилитации Люба Вассерман вернулась в Биробиджан и продолжила литературную деятельность. Память о ней была увековечена в виде мемориальной доски, которая находится на фасаде трехэтажного дома № 9 в Театральном переулке, где проживала поэтесса. Доска представляет собой барельефный портрет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ресторан «Симха» был открыт в 2013 году. Скорее, «Симха» представляет собой комплекс, объединяющей кафе и ресторан с разными концепциями.В одном здании располагаются два заведения: основное кафе «Симха» (или «Симха уютное местечко») и ресторан «Симха Kosher».
+Кухня кафе специализируется на некошерной еврейской еде, которая была широко распространена в Биробиджане в 70-90-е годы прошлого века. Здесь подают традиционные блюда, такие как «Флейш мид пирожкес» (мясо с пирожками), форшмак, гефилте фиш (фаршированная щука) и шницель по-биробиджански. Кафе стремится быть «уютным местечком» для всей семьи. Здесь есть детская игровая комната и специальное меню для малышей, что привлекает гостей с детьми. Для молодежи и пар работает уютный зал с живой музыкой, а для семейных торжеств и банкетов на втором этаже оборудованы просторные залы в еврейском стиле.
+«Симха Kosher» - ресторан кошерной кухни. Все блюда здесь готовятся в строгом соответствии с кашрутом, на кухне постоянно присутствует специально обученный человек. Ресторан соблюдает шаббат и в субботу не работает.
+«Симха» является активным участником и инициатором событий, направленных на возрождение еврейской культуры в регионе. Многие блюда, которые сейчас здесь подают, уже не готовят в домашних условиях, и «Симха» стала местом, где можно вновь ощутить вкус детства и юности. Повара «Симхи» регулярно участвуют в городских и областных гастрономических фестивалях.
+ </t>
+  </si>
+  <si>
+    <t>Река Бира, левый приток Амура протяженностью 424 км, была важной транспортной артерией, разделяла город на две части, и, конечно, берег оставался естественным местом притяжения горожан.
+В 1960-х годах здесь начали возводить берегоукрепительные сооружения для защиты от весенних паводков, а в 1979 году появилась улица с соответствующим названием, застроенная жилыми домами. Тем не менее, жители тянулись к воде: стихийный отдых на естественных берегах был обычным делом, а в жару горожане выезжали за город на «дикие» пляжи, расположенные выше по течению.
+Строительство современной набережной, как зоны отдыха, было приурочено к 75-летию Еврейской автономной области. 11 сентября 2010 года состоялось торжественное открытие новой прогулочной зоны. Береговая линия преобразилась до неузнаваемости: появилась широкая аллея, вымощенная гранитной брусчаткой, с удобными скамейками, беседками и клумбами.
+Пространство украсили скульптуры — изящные «Журавли», быстро ставшие популярным местом у молодоженов, фигура художника с мольбертом, авангардные композиции, а позднее — топиарные фигуры, например, зеленые павлины. Вечером включается подсветка, открывающая живописный вид на освещенную телебашню на сопке. Для молодежи оборудовали скейт-парк и амфитеатр, которые быстро превратились в точки притяжения и площадки для городских мероприятий.</t>
+  </si>
+  <si>
+    <t>Лондоко – поселок в Облученском районе Еврейской автономной области. Он был основан в 1909 году как один из железнодорожных пунктов при строительстве восточного участка Амурской железной дороги, а его станция была введена в эксплуатацию в 1915 году. Название поселка, по разным версиям, переводится с тунгусского как «самое высокое место» или «сопка», либо с нанайского означает место, где вялят рыбу.
+В 1930-е годы здесь началось активное промышленное освоение: геологи открыли богатые залежи известняка, что привело к строительству Лондоковского известкового завода. В 1938 году поселок получил статус рабочего поселка. Предприятие стало градообразующим и обеспечивало строительными материалами весь Дальний Восток.
+В годы Великой Отечественной войны около 200 жителей Лондоко ушли на фронт. После войны на заводе трудились японские военнопленные. Предприятие продолжало работать и в 1990-е годы, переориентировавшись на выпуск щебня, но в 2010 году оно было официально ликвидировано, что стало переломным моментом в жизни поселка.
+Сегодня Лондоко входит в состав Теплоозерского городского поселения. Поселок разделен на две части: собственно село Лондоко с населением около 100 человек (по данным 2025 года) и поселок Лондоко-завод с населением около 900 человек. Бывший Лондоковский известковый завод теперь является подразделением Теплоозерского цементного завода и выпускает доломитовый щебень.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Государственный природный заповедник «Бастак» является особо охраняемой природной территорией федерального значения в Еврейской автономной области, расположенной к северу от Биробиджана.
+Природоохранный статус территории был присвоен ещё в 1981 году, когда здесь организовали Бастакский ботанический заказник для охраны редких лекарственных растений. Уже в следующем году на этой же территории был учрежден комплексный охотничий заказник краевого значения с целью восстановления популяции соболя. Звание государственного природного заповедника Бастак получил только в 1997 году.
+Общая площадь заповедника составляет 128 055 гектаров. Территория «Бастака» уникальна тем, что находится на стыке двух природных зон. Горная часть представлена юго-восточными отрогами Буреинского хребта, где возвышаются самые высокие вершины — гора Быдыр (1207 м), гора Туколали (1103 м) и гора Балябинская (893 м). Равнинная часть — это заболоченная Среднеамурская низменность с редколесьями и лотосовыми озерами. По настоящему разнообразна флора и фауна заповедниека: около 819 видов растений и 2448 видов насекомых, а также 56 видов млекопитающих и 272 вида птиц.
+Кроме того, «Бастак» стал местом уникального эксперимента по возвращению в дикую природу амурского тигра. Сегодня на территории Еврейской автономной области постоянно обитает от 18 до 22 амурских тигров.
+Сегодня в заповеднике ведется активная научно-исследовательская и туристическая работа: открываются новые виды, разрабатываются маршруты и экологические тропы.
+</t>
+  </si>
+  <si>
+    <t>132.92544</t>
+  </si>
+  <si>
+    <t>48.791716</t>
+  </si>
+  <si>
+    <t>132.888409</t>
+  </si>
+  <si>
+    <t>48.806814</t>
+  </si>
+  <si>
+    <t>Завод «Дальсельмаш»</t>
+  </si>
+  <si>
+    <t>[А как Биробиджан называть сокращенно? Или, может быть, какое-то есть слово для Биробиджана?] Ну, обычно «Бирик», а если просто уже как быдло рассказывать, то просто «Бирдон». [Как-как?] «Бирдон». [Почему?] Я не знаю, ты просто периодически слышишь, типа, это такое слово, как будто бы… Что-то плохое, прям, откуда ты? с Бирдона. А так, если просто сокращённо, то просто «Бирик».</t>
+  </si>
+  <si>
+    <t>[А, и еще вспомнила вот такое уже не совсем еврейское, а скорее про какие-то уменьшительно-ласкательные или не очень ласкательные названия Биробиджана и Еврейской автономной областьи — как-то принято называть это коротко.] Бирдон. Бирдон, да. Бирик. Бирик. Бирдон. Я не знаю, я так не говорю. Ну, типа поехать в Бирик. Ну, я так тоже не говорю, Бирик. Конечно, нет. Да, ну и никогда не говорила. Ну, это больше какой-то молодёжный сленг, да, я не знаю. Вообще так говорят, да. Мы не употребляем.</t>
+  </si>
+  <si>
+    <t>Элемент этой конструкции, потому что это первая еврейская территория, которая появилась вообще на карте мира. Мы с вами понимаем, да? И когда в 1948-м году было создано государство Израиль, а в 1949-м году... Пошли вот эти сюжеты, наверное, знаете, опять-таки из истории, борьба с космополитизмом и прочее. В Биробиджане закрывались еврейские школы, сжигались книги, ну и все остальное. И последствия вот этого очень долго-долго-долго это были до 1990-го года. Да, в семьях это как-то помнилось, и была идишистская речь на улицах, но это было в семьях. А вот с 1990-го года немножечко пошло, там воскресная школа, потом Еврейский филиал открылся, и потихонечку что-то мы пытались сделать. Но тогда еще. Как же правильно сказать? В 1995-м году был принят закон «О языках народов России», сейчас, кстати, принят новый, вы знаете, вот сейчас совсем недавно подписали «Закон о языках народов России».</t>
+  </si>
+  <si>
+    <t>Вообще это было когда-то окраина. В пятидесятых годах это было окраина. То есть, ну, в принципе, этих домов еще ж не было. Тут просто частный сектор был. Синагога даже высока, это сейчас просто насыпь. Это был вообще отшиб. Но дом уже стоял, он уже после войны, этот дом. Зимой волки приходили. [Ну, хоть не тигры. Да, уже хорошо]. То есть в пятьдесятых годах еще волки приходили. Это сейчас уже не это. Тигры, тигры, вот. Тигры, мы это зимой видели, тигры. Уже две зимы подряд тигры. Они ходят и собак едят по городу. Это уже обычное явление стало. [По городу?] Да, край города уже... [Заходят, да?] Да, тигры уже заходят. Уже мы как-то едем в Хабаровск вечером.</t>
+  </si>
+  <si>
+    <t>И вот этот момент типа «ненавижу евреев», он связан именно на бытовом каком-то уровне, он не связан с национальностью, он перерастал иногда в какие-то социальных сетях были моменты. И Эли Рисс хорошо тогда раскладывал, давал понять, что есть бытовой... Потому что в Биробиджане ты в кипе можешь прогуляться, и евреи ходят к мусульманам на праздники, мусульмане к евреям, православные и туда, и туда. И поэтому спокойно в Биробиджане, тут компактно. То есть, например, приезжают люди, которые вот хотят на старости спокойно пожить. У них есть там уже хорошая пенсия или какой-то пассивный доход.</t>
+  </si>
+  <si>
+    <t>Вообще завод «Дальсельмаш» был большой. Ну к тому моменту где-то более трех тысяч человек там работало. [А сейчас?] А сейчас этого завода нету, в период нашей так сказать перестройки он где-то до 2000-го года еще существовал, что-то делал. Вообще раньше было плановое производство, и как бы завод мог существовать только в связи с тем, что были предприятия, которые снабжали их чем-то. Ну то есть, допустим, здесь на завод с Красноярска приходили молотилки для комбайна, а на заводе «Дальсельмаш» собирали хода на гусеничном ходу: вот ставили эти молотилки, которые приходили с Красноярска. Здесь ставили на хода гусеничные и все. И это обеспечило… Здесь у нас местность такая болотистая. По-видимому, для нашей местности более были приемлемые комбайны, которые не на колесах, а на гусеничном ходу. Завод сам тоже производил комбайны, но тоже мы зависели от комплектующих. Комплектующие были, я не помню, откуда приходили двигателя, то есть все было взаимосвязано. Когда в начале 90-х пошла эта перестройка, все это закрывалось, естественно, завод не мог сам существовать, сам не быть самодостаточным. Он зависел от многих факторов. Ну, естественно, вот он потихонечку, потихонечку и закрылся. Хотя я считаю, что завод был на тот момент очень сильный.</t>
+  </si>
+  <si>
+    <t>[А вот Вы уже начали говорить про названия улиц, а ещё были какие-то альтернативные названия?] Да, районы были, это типично биробиджанский — «Фаланга». «Фаланга-один», «Фаланга-два», «Фаланга-три». [А какие у них были официальные названия?] Это все Дальсельмаш, посёлок Дальсельмаш. Был завод, градообразующий строительный и туда, у, как правило, на Дальнем Востоке кто жил, кто приехал, люди, которые.. С небольшой судимостью. Люди приезжали на заводы, работали. Да, химики и так далее. У них было прошлое там, поэтому были определенные свои поселки, где жили рабочие люди, рабочий лад, которые вот..</t>
+  </si>
+  <si>
+    <t>Обозный завод – это будущий завод «Дальсельмаш», который был родным и для меня, и для моего отца, и для матери. Мы все там были. Она работала сразу в войну. И вот то, что много рассказывают и пишут про фронтовую бригаду, фронтовые бригады, одна из лучших фронтовых бригад, передовых, о которых много говорят, бригада Кириллова, это та бригада, в которой работала и моя мать. И вот Остапенко, Кириллов... Еще несколько человек, ну, девушки такие же и мужчины, они были в этой бригаде, всю войну она проработала, естественно, у станка.</t>
+  </si>
+  <si>
+    <t>Вот здесь был район – свои дома, где я жил. Вот дома – они и дальше продолжались, а здесь уже вот с этой стороны уже были каменные дома, пятиэтажки были. Вот они здесь, это вот дома. Здесь был, это при мне, я помню, ну то есть, потом это всё снесли, построили этот район имени Бумагина. Вот здесь был стадион, этот «Дальсельмаш». Вот здесь был лес, а вот здесь Бира текла. Вот здесь вот весь был лес. Лес чуть ближе и вот здесь Бира текла. Потом это все снесли и построили район Бумагина. [Бумагина это что за район? Бумагин это кто такой?] Вот я рассказывал, что завод «Дальсельмаш» был образован еще до войны, и очень много людей, которые работали на этом заводе, пошли на войну, в том числе Иосиф Романович Бумагин. Он повторил подвиг Матросова. В 1945 году он погиб, в апреле месяце он погиб. И поэтому в его честь назвали район Бумагина. Здесь на заводе «Дальсельмаш» он работал, кузнечный цех, я там рядом работал.</t>
+  </si>
+  <si>
+    <t>Я не знаю... Город, который любишь, вот, к которому относишься как к дому, да, как к своей квартире, ну, ты хочешь о нем рассказать, да, так скажем? Если ты любишь женщину, ты хочешь ей что-то сказать, да? И ты говоришь, правильно? Вот.  А назвать это источником, вот такая в жизни у нас зопа, да? Вот. Вот это стоит первая школа. Ну, не нравится мне, что тут первую школу построили, потому что снесли вторую, сделали, соединили вторую и третью школу, сделали двадцать третью. Вот. Второй школы нет. Коллектива нет. Вторая школа, это была легенда. Во время войны это был эвакуационный госпиталь военный.</t>
+  </si>
+  <si>
+    <t>О «женском» Биробиджане в 30-е годы</t>
+  </si>
+  <si>
+    <t>Вот нам рассказывал свои первые впечатления, когда он приехал в Биробиджан двадцатилетним, что город женский, так много красивых девушек. Вы бы заметили, что город был более женский?]   Ну, во-первых, я не заметил, я это знаю. Ну, во-первых, смотрите, предприятия: биробиджанская швейная фабрика, чулочная фабрика, чулочно-трикотажная фабрика — это женские предприятия. Ну, а что тут замечать или не замечать? Просто это знаю, конечно, он женским был.</t>
+  </si>
+  <si>
+    <t>О превращении школы в еврейскую гимназию в 1990-е годы</t>
+  </si>
+  <si>
+    <t>То есть вы находитесь... Нет такого в еврейском понятии, вы знаете, что старое есть первое. Старое нет вообще синагога, выражения нет. На иврите нет выражений «старое». Есть первое, дальше идёт второе, есть это, ну как, емрешон, то есть это самое. То есть вот некоторые вещи, то есть первые два здания первой синагоги были уничтожены, одно забрали, одно сожгли, и вот что вытаскивали, вот видите, все подожженное, да? Вот это следы пожара, это со второго здания.</t>
+  </si>
+  <si>
+    <t>Община «Фрейд», они на праздники  едут в разные села, то, что они планируют, с кем они дружат. Есть и Смидовический район, есть Ленинский район, есть там дальше Амурзет. То есть они сотрудничают и возят туда концерты, то есть люди знают язык.</t>
+  </si>
+  <si>
+    <t>в 2013 году, когда было наводнение, я возглавляла пункт временного размещения пострадавших. У меня полностью 2 населённых пункта, 200 с лишним человек, в основном это старики и дети. И первыми, кто пришел на помощь, это была наша община. То есть они первые начали привозить гуманитарную помощь. И самое главное, в этот период был праздник, и они привозили яблоко, мед, пряник. Каждому гостиницы такие. Мы еще все чаевничали в нашей столовой. Они первые откликнулись, потому что Израиль откликнулся.</t>
+  </si>
+  <si>
+    <t>[А вот еще нам говорили, что раньше в университете, да, или институте Шолом-Алейхема, что там был факультатив… Англоидиш.] Англоидиш, правильно, был такой</t>
+  </si>
+  <si>
+    <t>Но иногда у нас в ДК интересные выставки выходят. ГДК, который Дворец культуры, и там на втором этаже делают выставки. Ну ладно, давно. Была выставка, посвященная еврейским писателям и (писателям) Дальнего Востока. Также наш ансамбль, когда был... В том году у нас был юбилей, и в том году там тоже проходила выставка нашего ансамбля («Мазлтов»). Часто можно увидеть что-то интересное.</t>
+  </si>
+  <si>
+    <t>Ну, про газету вы знаете, что газета издавалась, издается давно очень, «Биробиджанерштерн». В редакции работало, наверное, человек 40 сотрудников, 50. Была большая интересная газета. Она и сейчас интересная. Но сотрудников там 5 человек. [Это сотрудников было 40-50, когда?] Какие годы? До 1990-х. Газета издавалась здесь, распространялась по всему миру, читали ее везде, большим тиражом отправлялась отсюда. Она была полностью на идиш, 4-, 6-страничная.</t>
+  </si>
+  <si>
+    <t>Вот, потом Кульдур. Кульдур. Вот сейчас я читала, что принято решение, что Кульдур, он будет все-таки нашей собственностью, то есть он будет федеральной собственностью и будет принадлежать Еврейской автономной области. Потому что сейчас большая часть, там, акций, чего-то оно у Хабаровского профсоюза. Когда союз разваливался, они быстренько, подешевке это дело купили. Оно будет наше. И так как был уже какой-то, был документ, о том, что он будет развиваться, Кульдур будет развиваться как курорт федерального значения. А чем он интересен, чем он значим? Там какая-то вода, я не назову ее химический состав, но она чрезвычайно полезная, наполненная всяческими минералами. И я в 2017-м году оказалась там. Я бы там никогда не оказалась, потому что, ну, Кульдур, я вот живущий тут, ну, Кульдур, что бы я туда поехала? Вот, это мне друзья подарили туда путевку. [Угу, в санаторий.] Да, ну вы понимаете, ну нельзя же ее выкинуть. Ну, пришлось поехать, пришлось поехать.Это был 2017-й год, там еще много… Там многие здания, так сказать, почти рассыпались, уют утрачен. Несмотря на это, это настолько превосходно, и я писала там в книге отзывов. Что нужны решения федеральные, вот что его надо развивать. И вот там, в это время, в это время, когда там было, ну, скажем так, лечение и питание, остальное – ничего. Ну, и чистота была в относительно скромных этих самых, как они называют, палатах, комнатках. Живешь один, но все равно все скромненько, по-советски. Вот. Но вы понимаете, в чем дело? Уже в то время там было очень много людей из Белоруссии. Вот, из центра, из Москвы были, из Санкт-Петербурга. То есть там они лечили болячки, которые в принципе могут вылечиться только этой водой.</t>
+  </si>
+  <si>
+    <t>Два раза в год топили. Вот просыпаешься, вода в доме, все, залазишь на вышку, на крышу, на крыше живешь. [А сейчас не топит?] АС: Нет, когда построили, когда отрезали, когда отрезали парк, парк был островом, я еще раз повторяю, а центральное русло Биры, это вот где сейчас этот идет, «Самбери», вот это было центральное русло Биры, по нему ходили огромные баржи, заходили с углем и так далее. Да, до Головино тоже доходили баржи, катера, она судоходная была Бира. А сейчас она очень обмелела, очень. Мы спускались на шлюпках, ой, я не скажу вам, какой-то был, вот 1979.., нет, 1982, наверное, мы с колхозниками это… И прям вроде посередине идешь, и дно прям под лодкой, она стала мелеть. А так, ходили, почему вот Головино освоили, они же не по дорогам шли, это же невозможно было.</t>
+  </si>
+  <si>
+    <t>Вот улица Ленина, по которой Вы шли сюда, она не всегда называлась Ленина. А как она называлась? Постышева. А когда в 1935 году или в 1936 году Постышева расстреляли, как врага народа, может носить улица имя врага народа? Нет, взяли и назвали улицу Ленина. А потом Постышева оправдали, и он уже не враг народа, и в городе Биробиджане появилась улица Постышева №2, на котором стоит мой дом, где я живу. Чувствуете?</t>
+  </si>
+  <si>
+    <t>А какие вот есть, получается, в области, вы бы назвали именно еврейскими местами?] Еврейские места? Никакие. Для меня все, связанное сейчас с евреями, вот эта вот «Симха», как называется, молельный дом, синагога, это все новодел. Боже мой, это все появилось в середине 1990-х. Для меня они совершенно не еврейские. Библиотека, пожалуй, еврейское место такое. Пожалуй, вот эта старая улица Ленина, там как-то всё концентрировалось.</t>
+  </si>
+  <si>
+    <t>Я как-то вообще была очень хорошо. Я такой была, что вот все-все-все-все расскажу до. Литературу, конечно, много читала, но мне приходилось, да. Но я доказала. Первый год я доказала, потом за мной люди пошли. А то, как говорят: «ну, много кто приехал, уехал, ну, имей в виду». Все, все нормально. [Вы говорите, что в Валдгейме было лучше, чем в Хабаровске. А сейчас люди отличаются от тех, что были?] Вы знаете, есть у многих стремление, но изменения, конечно, вы видите, никакого нету. Люди, которые... раньше же все специалисты нужны были. И у которых не было там, телятниц, коровниц – им в то время предоставлялись квартиры. Всё время раздавали квартиры.</t>
+  </si>
+  <si>
+    <t>Скажите, пожалуйста, ну и вот они здесь приехали, поселились, то есть это было преимущественно еврейское село в тот момент?] Да, сто процентов. [То есть из одних евреев-переселенцев?] Да, да, сто процентов было еврейское. [А потом уже какие-то люди других?] Потом уже практически я ещё был ребенком, я как бы знал всех, обходил всех, были все свои, как бы, ну, не было приезжих. Потом уже начало все вот это обживаться. [То есть вы &lt;19&gt;61-го года рождения, это значит в 1960-е годы там...] Ну, 1960-е это. Практически... [Были еще свои.] Да, практически это... Ну, колхоз-то развивался, нужны были люди и... Даже опять были, опять были переселенцы, уже были... Ну, людей было уже посторонних много. Уже как бы изначально</t>
+  </si>
+  <si>
+    <t>У нас на территории Валдгейма было в свое время несколько детских домов. Первый детский дом колхозный, но там не было детей из Валдгейма, потому что это были с района, валдгеймских детей не отдавали в детские дома. Потом детский дом был во время войны, привозили из центра сюда, и уже сюда в детский дом, у кого-то на фронт забирали, тяжелое материальное положение было, дети туда ходили. И был детский дом в 1930-е годы, был детский дом для детей репрессированных. Как в одно время говорили, что не было... В Валдгейме репрессированные были, но не по доносу. В основном же по доносу забирали людей. А здесь увозили ночью. А детей оставляли. Вот забрали отца с матерью, а детей...  Вот, рядом семья. Прихожу, приношу, а он сидит, мальчик, плачет. — «Что ты плачешь?» — «Забрали родителей». Вот. И колхозники, видя такое, куда их девать детей, организовали детский дом для таких.</t>
+  </si>
+  <si>
+    <t>Название первое Валдгейма, поселение... Ну, Худзиновка, сначала Кирма была, а потом Худзиновка. Худзиновка, да. По фамилии Худзинского. Так, оно как бы... Я всё вспоминаю, не могу... [А потом сделали вот как с еврейского, то есть это не сначала так было?] Нет, нет, нет, сначала была Кирма, стояло несколько домиков, кто тут жил. Промысловики в основном. А потом вот Худзинский, здесь был переселенческий пункт, который принимал людей и все. Его фамилия была Худзинский. Пока строили дома, так и было. — «Ты куда?» — «Да в Худзиновку». У нас и улицы так названы. У нас улицы получили свое название где-то в начале 1960-х годов вот такие вот конкретные. [И что они потом голосовали, как назвать?]Конечно, наверное, как всегда в советское время, все голосуют, все проголосовали за это название. Значит, я вам скажу со слов, конечно, моих стариков, которые здесь, вот так же они собрались: «Ну что, как назовем?» Кто-то встает из селян и говорит: «А как назвать, как назвать? Дом стоит в тайге. Что это как? А, дом в тайге, так и в тайге! Валдгейм! Дом в тайге! [Ну, кто-то из евреев, наверное, да, раз на еврейском?] Ну, как назвать, как? Ну, дом стоит в тайге. Ну, да. 3 дома. Говорили, что как бы Школьник там предложил… Не, не, не, не. Нет! Кто-то встал… Кто-то встал и сказал, да. «Что-то в тайге дом. О, дом в тайге — Валдгейм.» И все согласились, все были… Ой, говорит, как хорошо — Валдгейм. Кругом очень... Вообще, знаете, не стало деревьев.</t>
+  </si>
+  <si>
+    <t>Гора «Быдыр«</t>
+  </si>
+  <si>
+    <t>Общий вид завода «Дальсельмаш». Сентябрь 1972 года</t>
+  </si>
+  <si>
+    <t>Механообрабатывающий цех № 9 завода Дальсельмаш. 1980-е годы</t>
+  </si>
+  <si>
+    <t>Завод «Дальсельмаш». Современное состояние</t>
+  </si>
+  <si>
+    <t>Кионтеатр «Строитель» в Теплоозерске</t>
+  </si>
+  <si>
+    <t>Станция «Теплое озеро»</t>
+  </si>
+  <si>
+    <t>Озеро «Теплое»</t>
+  </si>
+  <si>
+    <t>В заповеднике «Бастак»</t>
+  </si>
+  <si>
+    <t>Синагога Бейт Тшува. Вид снаружи. Фото: Наталья Матиенко</t>
+  </si>
+  <si>
+    <t>Синагога Бейт Тшува. Вид внутри. Фото: Наталья Матиенко</t>
+  </si>
+  <si>
+    <t>Макет, изготовленный Абрамом Мильчиным в 1947 году. Фото: Фото: Газета «Биробиджанская звезда»</t>
+  </si>
+  <si>
+    <t>Синагога «Бейт Менахем» в Биробиджане. Фото: ИА ЕАОМедиа</t>
+  </si>
+  <si>
+    <t>Синагога «Бейт Менахем». Внутри. Фото: DS.Molotkov</t>
+  </si>
+  <si>
+    <t>Кинотеатр «Родина» в Биробиджане, 1938 год. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>Биробиджанский кинотеатр «Родина», 1990 год. Фото: Из фондов областного краеведческого музея</t>
+  </si>
+  <si>
+    <t>Кинотеатр «Родина». Фото: Баграновская Наталья, ИА EAOMedia</t>
+  </si>
+  <si>
+    <t>Сотрудники газеты «Биробиджанер Штерн» за работой. Фото: архив БШ</t>
+  </si>
+  <si>
+    <t>Газета «Биробиджанер Штерн»</t>
+  </si>
+  <si>
+    <t>Ресторан «Симха» в Биробиджане</t>
+  </si>
+  <si>
+    <t>Фундамент ресторана «Симха». Изображения персонажей Шолом-Алейхема</t>
+  </si>
+  <si>
+    <t>Ресторан «Биробиджан» на ул. Горького. Фото: Госархив ЕАО</t>
+  </si>
+  <si>
+    <t>Амурский тигр</t>
+  </si>
+  <si>
+    <t>https://www.gazetaeao.ru/resurs/uploads/2023/05/Amurzet-livebir.ru-84785.jpg</t>
+  </si>
+  <si>
+    <t>images/amurzet_2.jpg</t>
+  </si>
+  <si>
+    <t>images/amurzet_1.webp</t>
+  </si>
+  <si>
+    <t>images/bir_vokzal.webp</t>
+  </si>
+  <si>
+    <t>Мебельная фабрика. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>Дежурный станции Биробиджан. 1937 год. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>Рабочий завода. 1935 год. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>images/socgorodok_2.webp</t>
+  </si>
+  <si>
+    <t>images/birofeld_5.webp</t>
+  </si>
+  <si>
+    <t>Отправка пшеницы на ссыпной пункт. 1936-1937 годы. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>https://collection.ethnomuseum.ru/api/spf/fhkSy2h_aJ53fAW0DDVjmYuTf6FFbZHcoqS_w12qHsdwCOgUW8R4cM4s50NAm_-5.webp?w=1000&amp;h=1000</t>
+  </si>
+  <si>
+    <t>images/amurzet_3.webp</t>
+  </si>
+  <si>
+    <t>Отличники учебы средней школы №2. 1937 год. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>https://collection.ethnomuseum.ru/api/spf/fhkSy2h_aJ53fAW0DDVjmQMR-vMTqxMKfl616aubInxufw3G8alfLIMoqGPO8iwj.webp?w=1000&amp;h=1000</t>
+  </si>
+  <si>
+    <t>В столярной мастерской средней школы №2. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>https://collection.ethnomuseum.ru/api/spf/fhkSy2h_aJ53fAW0DDVjmRoBeUNRpi24knwoeHvgrR8gn_2mhWZmGyl8RcXBCYo_.webp?w=1000&amp;h=1000</t>
+  </si>
+  <si>
+    <t>images/bir_jew_school_3.webp</t>
+  </si>
+  <si>
+    <t>images/bir_jew_school_2.webp</t>
+  </si>
+  <si>
+    <t>Стелла на въезде в с. Амурзет. Фото: БиробиджанLive</t>
+  </si>
+  <si>
+    <t>https://collection.ethnomuseum.ru/api/spf/fhkSy2h_aJ53fAW0DDVjmYo5dkGwB80avTQKQT4n-gvWxvtsWQ3GAMNtFytSc8m_.webp?w=1000&amp;h=1000</t>
+  </si>
+  <si>
+    <t>Cтахановцы-токари. 1937 год. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>Проектирование большого Биробиджана. 1932-1934 годы. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>Ударники бригады. Артель «Колесо революции». 1935-1937 гг. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t>Школа. 1935-1937 годы. Фото: архив РЭМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Общий вид Лондоковского известкового завода. 1937 год. Фото: Х. Гринберг. </t>
+  </si>
+  <si>
+    <t>Школа имени И.А. Пришкольника. Фото: архив «Сэфер»</t>
+  </si>
+  <si>
+    <t>Мемориал воинам Великой Отечественной войны. Фото: архив «Сэфер»</t>
+  </si>
+  <si>
+    <t>Экипаж около самолета на аэродроме «Бирофельд». Фото: из личного архива информанта</t>
+  </si>
+  <si>
+    <t>Группа детского сада около самолета времен ВОВ на аэродроме «Бирофельд». Фото: из личного архива информанта</t>
+  </si>
+  <si>
+    <t>[А давно живете здесь?] С шестьдесят восьмого года. [А почему приехали?] Ну, отца сослали. [Сослали?] Да. Выслали отца. [И сюда?] Да. [А из Прибалтики откуда? Литва? Латвия?] Латвии. [Латвии?] С Риги, да. Непосредственно с Риги. [А в шестьдесят восьмом году получает свое ребенком сюда, да?] Ну, пять лет-то что? Ну, сразу мы попали на это, как раз на войну попали. Мы только приехали, на следующий день война началась на Даманском (полуострове).</t>
+  </si>
+  <si>
+    <t>И она говорит: «За 25 лет я так, — говорит, — не привыкла к той земле». И они бы с удовольствием сюда вернулись, но некуда. Не так просто. Они, думаете, там деньги лопатой гребут? Нет, там же и работают и поэтому скопить на жилье… Вот кто может. Ну некоторые же и вернулись, и живут в Биробиджане. АС: Я вам таки сейчас скажу. Я некогда был руководителем на товарной конторе. Это где, откуда высылают, контейнера посылают. Пример. Уезжает… Знакомых-то много, контейнер грузят. «Чего ты, куда ты, Петя, Гриша?» Туда, на запад, это как называется, куда все едут, Краснодар, Белгород, туда-туда. Один ушел, второй ушел, третий ушел, четвертый ушел, пятый ушел. Проходит 2 года, встречаю, что такое, все, назад? Не катит? Во-первых, климат, те, кто родились здесь, а там же у нас же организм как, он же ждет зиму, мы же не можем вечно в лете быть.</t>
+  </si>
+  <si>
+    <t>А из Биробиджана уезжали, ну, мне кажется, это все вот тяжелые вот эти 1990-е, люди боялись и уезжали туда. Тем более это была, ну, как видно, реклама у них там была, что как там хорошо, как там все прекрасно. Но я не видела, чтобы прям там расцвели в Израиле, нет, средненькие. Вот те, кто здесь работал учителем, то полы моют, то где-то на заводе на каком-то там работает, какой-то там известковый или на вредных каких-то там производствах работает.</t>
+  </si>
+  <si>
+    <t>Из истории вы, наверное, помните, это были годы страшной алии, всего остального. Вот, и эта, скажем так, ситуация. Не будем оценивать, плохая она или хорошая. Эта ситуация, она коснулась и Еврейской автономной области. И в Еврейской автономной области тоже было немало людей, которые уехали. Но в то же время Еврейская автономная область, она была той территорией, где люди уезжали как раз вот по тем, что называется, колбасным сюжетам. То есть вот эти экономические какие-то вопросы 1990-х годов тяжелые. Но наряду с этим в Еврейской автономной области, я это на Библию, на Тору, куда угодно, на Конституцию руку положу и повторю снова. Вот. У нас, как бы сказать, активно действовали представители Сохнута.</t>
+  </si>
+  <si>
+    <t>[А как папа приехал? Вот как родители приехали в Биробиджан?]  Родители… Ну, папу привезли, это моя бабушка и дедушка – они жили уже под Гомелем. И в тридцать втором году, когда после погромов еврейских в Белоруссии, они убежали оттуда сюда, на Дальний Восток, и оказались тут есть недалеко, в сторону Облучья, в поселке Биракан. И, в общем, они там жили до определенного возраста, мне кажется, до сороковых годов они там жили.</t>
+  </si>
+  <si>
+    <t>Значит, я чистокровный еврей, то есть и папа, и мама, они евреи. Значит… Как оказался отец мой на Дальнем Востоке, в Биробиджане. Значит, это как раз, когда организовывали нашу область… Украина. Есть такой славный город Бердичев в Житомирской области. Он уроженец города Бердичева. Значит, и…</t>
+  </si>
+  <si>
+    <t>А мне-таки есть о чем рассказывать, потому что по линии моей жены её папа приехал сюда в начале тридцатых годов, тридцать первый, тридцать второй год, в посёлке Биракан Еврейской автономной области был еврейский колхоз. Найе Лебен назывался. Новая жизнь. Его родители привезли туда всю свою семью. Его. И он там жил, и рос, и учился. Моя тёща, любимая, ныне, к сожалению, покойная, мир праху её, приехала сюда из Крыма. Вот вам еще одна эпопея еврейской жизни, крымский вариант, Феодосия. Мои дедушка и бабушка по маминой линии приехали сюда из славного города Николаева. Догадываетесь, где это? [Угу.] Да? Да, да. А по папиной линии? Знаменитый город Белая Церковь. То есть вся моя родня как бы показывала маршрутизацию, маршруты, как сюда попали евреи, когда и зачем. То есть мне в этом отношении довольно просто увязывать историю движения еврейского населения на Дальний Восток. Вот это надо знать и надо понимать, что всё это пережито, прочувствованно через свои личные воспоминания, да? И знания.</t>
+  </si>
+  <si>
+    <t>Они в юношеском возрасте уехали, будем так говорить. Не катит, все сюда приехали. В Биробиджане живут. [А людей побуждает вернуться вот любовь к Биробиджану или, скорее, какие-то другие факторы?] Значит, есть такая поговорка. Рыба ищет, где глубже, а человек ищет… [Где лучше?] Где рыба. &lt;смеется&gt;  Ну, даже вот мы смотрим пост в интернете, смотрим, что многие же представляют наши фотографии нашего города, и пошла ностальгия. Вот прекрасно все, и столько теплых чувств у людей, но вернуться они не могут. И они живут тем Биробиджаном, который был, когда они уехали. Поэтому это же две большие разницы. Тогда были заводы, тогда во дворах сидели мужчины, играли в домино. Я им только рассказал анекдот. Я им рассказывал уже.</t>
+  </si>
+  <si>
+    <t>Потому что евреи-то тоже ехали, в принципе, их тоже загоняли сюда, они же добровольно-то не ехали. [А, загоняли?..] Ну, предложили уехать или... Ну, можете себе представить, с Одессы человек поедет в Биробиджан, что такое? С Одессы в Биробиджан, в Валдгейм! Ну, наверное, поставили такие условия, если ты не поедешь, то там и останешься, или сюда приедешь, ну, это, в Будукан или куда-то там еще, я не знаю, в Комсомольск&lt;-на-Амуре&gt;, там копать ямы зимой и летом, дрова пилить. Ну, это мое субъективное мнение, но, в принципе, так оно и было. Если брать историю нашу, то большинство высельцев было. [Откуда?] АС: С запада. Дальний Восток сам по себе это ссылка.</t>
+  </si>
+  <si>
+    <t>И из Америки они эмигрировали в этот Соцгородок. Они хотели построить еврейское государство. Ну и потом там тоже было очень тяжело, не было работы и люди искали, где работать, вот только в этом, в этом все. [В этом все и упиралось?] Ну честно, людям же надо деньги на еду, на проживание и так далее, вот они ехали сюда, здесь давали деньги, здесь работы было полно, люди зарабатывали, знаете как, устроиться на работу и получать зарплату. Давали, ну не сильно большие, раньше там, раньше квартиры-то были крошечные, но давали квартиры. Люди жили, в общем-то. [Понятно. Мы вот много прочитали перед тем, как ехать. Мы хотели узнать ваше мнение. Вот как вы считаете, сколько сейчас примерно евреев в области? По ощущениям. По вашим ощущениям. Не по статистике.] Даже не знаю. Мне кажется, что как было, так и осталось.</t>
+  </si>
+  <si>
+    <t>Но они были счастливы, в первую очередь, что их перестанут бить. Известный герой России, да, запоздало получивший героя, Жорж Абрамович Коваль, да, легендарнейший разведчик, легендарнейший. Он родился, такое местечко было, Телеханы. Это на месте современной Белоруссии. Там сейчас нет ни одного еврея. А там было еврейское местечко. И они жили счастливо, пока их не начали бить. Пока не начались погромы. Они уехали в Америку. Там Жорж окончил колледж. И однажды его папа проходил мимо парка, а там была написана табличка «Вход евреям и собакам запрещен». После этого они собрались сюда приехать. Поэтому «искатели счастья». Вот они истинное счастье нашли, ну, в том, что их...</t>
+  </si>
+  <si>
+    <t>Вокруг меня жили, можно сказать, одни евреи, среди моих подружек все были еврейки, получается, и они все уехали в Израиль. [А вы с ними поддерживаете какой-то контакт?] С некоторыми, да, продолжаю общаться. [А сейчас у вас в вашем круге общения есть еврейские друзья?] Вы знаете, нет. Потому что в основном, ну, во-первых, я уехала учиться, да, тут потерялись некоторые связи. Но из тех, с которыми я сейчас общаюсь, это, ну, вот они две еврейки, они проживают в Израиле, ну, и одна московская моя подруга. Вот так вот. [А они сами приезжают сюда или нет?] Нет. [Бывает такое?] Нет, нет. Давно их здесь не было, не приезжают. Разве только… Евреи сюда сейчас приезжают только чтобы пенсию оформить, на могиле какой-нибудь убраться, да.</t>
+  </si>
+  <si>
+    <t>[1930-е, наверное, годы? Это вот период первого &lt;переселения&gt;?] Это прабабушка у меня была завезена сюда. То есть их прям привезли. Это был 1956-1957, 1956-1957. Потому что период войны моя бабушка, она встречала на Украине, то есть получается, с прабабушкой. То есть они в подвалах, там, когда рассказывали, довольно страшно было на самом деле слушать. Дедушка, он как раз у меня, тоже у него корни были украинские, но почему-то они приезжали с Центральной России. Его еще прапрапрадеды, получается, жили на Украине, а потом, получается, жили где-то там в России. По линейке отца у меня вообще это Тверь, Рязань, то есть тоже переселенцы. [ По линии отца тоже в &lt;19&gt;50-х годах приехали сюда?]</t>
+  </si>
+  <si>
+    <t>С Украины. С Украины, да. Они из Винницкой области. [С обеих линий, получается, приехали?] Папина бабушка с Винницкой области, и баба Соня, по маминой – тоже, по-моему, они отттуда. [А в какое время они, получается, приехали сюда?] Во время войны была репатриация. После войны. Там, буквально в сороковые, может, в сорок шестом. Ну, то есть вот-вот, прям совсем. Бабушка была ребёнком маленьким. Она рассказывала, что когда она приехала сюда, она знала только идиш. Ее определили в какой-то интернат местный, то есть, соответственно, он никакой не еврейский, обычный, да, интернат для детей. Потому что, ну, просто родителям надо было работать, жить негде было и всё такое. Дети были там недели в интернате, на выходные их забирали домой – такая обычная практика.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нет, в дальневосточных регионах, конечно же, это процент большой, то есть все равно мы коммуницируем. И тут еще на Дальнем Востоке есть большой фактор это семьи, то есть, ну, очень много жителей Еврейской автономной области уезжают в соседние регионы. То есть отток населения у нас продолжается, и, к сожалению, его сложно остановить, когда вот мы посерединке, с одной стороны находится Хабаровск, с другой стороны Благовещенск, два крупных мегаполиса совершенно с другими заработными платами. И они вот высасывают просто людей, в том числе, ну, конечно, большинство молодых людей, когда они поступают в хабаровские ВУЗы, в благовещенские ВУЗы, или там Владивосток, ДВФУ, они остаются там. Но связь вот эта семейная, то есть родители здесь остались, друзья, она сохраняется, и поэтому, конечно, на Дальнем Востоке одна большая семья. </t>
+  </si>
+  <si>
+    <t>Ну, поехали. [Подскажите, пожалуйста, в каком году вы родились и где?] Я родился в 1956 году, 19 сентября, в городе Биробиджане. [В Биробиджане. А родители ваши?] Папа мой родился на Украине. Ну, село Ольховатка, Валуйского района. [И приехал сюда в каком году?] Значит, мои родители, мои предки, приехали сюда ориентировочно в &lt;19&gt;35-34 году.</t>
+  </si>
+  <si>
+    <t>Популярна была шутка: "Когда из Биробиджана будет уезжать последний еврей, на вокзал его провожать придут десять тысяч евреев". Я тоже вернулась из Израиля. Я вернулась, я не могла без Биробиджана.</t>
+  </si>
+  <si>
+    <t>А до этого я приехала со Ставрополья, тогда было переселение, и мы, как переселенцы, муж, двое детей и я приехали сюда.
+Тут деревня Благословенное называется так.  [В области?]  Да, да, в области, в Еврейской автономной области. Это Октябрьский район, рядом с Амурзетом. Может, знаете Амурзет наш?  [Ну вот вчера были там, посещали.]  Там были?  Да.  Ну вот, вы когда из Амурзета выехали сюда, в Биробиджан, вы проезжали село вот это Благословенное. Вот я там жила. Оно как раз в то время строилось, расстраивалось, улицы новые были, там были сначала деревянные дома, и таких блочных мало было. А потом, когда оно расстроилось, и вот было переселение. Нужны были работники сельского хозяйства, там совхоз был очень богатый, и все села в Октябрьском районе хорошо жили, богатые жили там.</t>
+  </si>
+  <si>
+    <t>[А как родители сюда попали?] Могу сказать. Отец попал во время эвакуации. Он жил в Евпатории. Когда немцы пришли, они бежали-бежали, ну… там, в Среднюю Азию. И попали в Биробиджан.</t>
+  </si>
+  <si>
+    <t>Нет, наверное, какой-то причины такой прям глобальной, почему они остались. Не могу сказать, что это из-за великой любви к Биробиджану. Конечно, нет. Боялись, наверное. Было здесь тяжело, боялись, что будет ещё труднее там. Ну, вообще, в принципе, в 90-е везде было, наверное, непросто. Почему-то не решились, хотя такие мысли были. Да, прям я помню, что много об этом говорили. Когда очень много уезжало людей, правда, я помню, у нас полдома уехало. Очень много евреев уехало в то время. Тут было очень много евреев. В нашем дворе, вот в моём доме –  ведь я живу до сих пор в этом доме, правда, было очень много евреев и достаточно много тех бабушек, которые еще говорили на идиш. И все репатриировались вместе со своими детьми. Девяносто шестой год. Это был массовый какой-то отток людей. Я помню, как провожали всем двором. Это правда, людей провожали всем двором и пели песни про Биробиджан. [И не возвращались?] Кто-то вернулся, кто-то возвращался.</t>
+  </si>
+  <si>
+    <t>[А почему... Почему Биробиджан? Ну, в плане, там не было вариантов обустроиться, там было всё… ] Она сказала, что дома их больше не было, не существовало, всё было уничтожено, возвращаться было некуда, у них не было ничего. Ну, вот они вышли пустые с этими документами, которые им только что дали из гетто. Ну и всё, людям что делать? И тут по всем объявляли громкоговорителям, вот: «Собирайтесь, евреи, в Биробиджан». Да, будет поезд, всех отвезёт, кто хочет, там будет классное место. Но тут не классно было. Вам дадут там кусок земли. Кусок земли дали на болоте. Да они жили в бараках старых. [А куда они, кстати, приехали? Ну, как бы на эту станцию, как она называлась? Тихонькая?] Тихонькая, да. Прямо здесь. Прямо здесь. Да, они жили в бараке, потом вот был этот барак. [Уже не сохранился, наверное?] Нет, ничего не сохранилось. Были бараки, потом уже стали строить дома, они жили в доме, потом квартиры, всё. И вот, ну, уже заводы появились, они работали.</t>
+  </si>
+  <si>
+    <t>А мама… мама, была голодовка на Украине. Ее семья, там даже умирали, вот они решили ее спасти. Она была первым ребенком, ей было восемь месяцев. И не было просто еды на Украине, и работы не было. И сюда уехали родители ее. [В каком году?] В 1934-м. [То есть прям в основании, да?] Да. Дело в том, что они в начале жили в Амурзете, а потом перебрались сюда, в Биробиджан. Вот. Некоторое время они там перебрались.</t>
+  </si>
+  <si>
+    <t>Мемориальная доска Э.Г. Казакевичу. Фото: архив «Сэфер»</t>
+  </si>
+  <si>
+    <t>images/bir_redaktsia_gazet_4.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7292,13 +9075,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -7314,7 +9109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7323,6 +9118,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7389,18 +9189,18 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3246120</xdr:colOff>
-      <xdr:row>695</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:colOff>2910840</xdr:colOff>
+      <xdr:row>684</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5074920</xdr:colOff>
-      <xdr:row>708</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>4739640</xdr:colOff>
+      <xdr:row>698</xdr:row>
+      <xdr:rowOff>36195</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="place_id">
@@ -7423,7 +9223,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7433,7 +9233,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6301740" y="26753820"/>
+              <a:off x="5966460" y="24635460"/>
               <a:ext cx="1828800" cy="2466975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7467,24 +9267,24 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3246120</xdr:colOff>
-      <xdr:row>554</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:colOff>2796540</xdr:colOff>
+      <xdr:row>555</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5074920</xdr:colOff>
-      <xdr:row>567</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>4625340</xdr:colOff>
+      <xdr:row>569</xdr:row>
+      <xdr:rowOff>51435</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="place_id 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC86B3DE-AA72-49A9-A65A-E331D562EDA6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F1DB6BD-D683-4D2C-AF65-35F45CE0BC47}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7501,7 +9301,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7511,7 +9311,85 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6301740" y="967740"/>
+              <a:off x="5852160" y="1059180"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="ru-RU" sz="1100"/>
+                <a:t>Эта фигура представляет срез таблицы. Срезы таблиц не поддерживаются в этой версии Excel.
+Если фигура была изменена в более ранней версии Excel или если книга была сохранена в Excel 2007 или более ранней версии, использовать срез невозможно.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1790700</xdr:colOff>
+      <xdr:row>553</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>3619500</xdr:colOff>
+      <xdr:row>566</xdr:row>
+      <xdr:rowOff>97155</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="place_id 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AA414D5-54A2-4B1B-BCE5-A52257AF92FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="place_id 2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="18714720" y="556260"/>
               <a:ext cx="1828800" cy="2466975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7575,8 +9453,9 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="place_id" xr10:uid="{3DC117B7-CF46-4D2E-9EF9-F809BC8D7B74}" cache="Срез_place_id" caption="place_id" rowHeight="234950"/>
-  <slicer name="place_id 1" xr10:uid="{E6C0CD29-EF38-4DE6-A86C-52E4F2A09582}" cache="Срез_place_id" caption="place_id" startItem="30" rowHeight="234950"/>
+  <slicer name="place_id" xr10:uid="{3DC117B7-CF46-4D2E-9EF9-F809BC8D7B74}" cache="Срез_place_id" caption="place_id" startItem="15" rowHeight="234950"/>
+  <slicer name="place_id 1" xr10:uid="{4F99C03C-7B84-42C5-B049-E3B71C454A3C}" cache="Срез_place_id" caption="place_id" startItem="116" rowHeight="234950"/>
+  <slicer name="place_id 2" xr10:uid="{26E11490-1A41-4180-A2B0-60E49C197555}" cache="Срез_place_id" caption="place_id" startItem="43" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -7585,7 +9464,7 @@
   <autoFilter ref="A1:I553" xr:uid="{E1ADB881-A709-4600-8EA3-52AB4D935509}">
     <filterColumn colId="0">
       <filters>
-        <filter val="bir_memorial"/>
+        <filter val="bir_museum_iudaika"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -14370,7 +16249,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>332</v>
       </c>
@@ -14399,7 +16278,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>332</v>
       </c>
@@ -14428,7 +16307,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>332</v>
       </c>
@@ -15006,7 +16885,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>911</v>
       </c>
@@ -15035,7 +16914,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>911</v>
       </c>
@@ -23793,13 +25672,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="40.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" customWidth="1"/>
@@ -23822,15 +25701,15 @@
       <c r="E1" s="2" t="s">
         <v>1944</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="11" t="s">
         <v>1945</v>
       </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -23846,343 +25725,355 @@
         <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1954</v>
-      </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
+        <v>2735</v>
+      </c>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>2084</v>
+        <v>2070</v>
       </c>
       <c r="C3" t="s">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
+      <c r="E3" s="3" t="s">
+        <v>2736</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>888</v>
       </c>
       <c r="B4" t="s">
-        <v>2093</v>
+        <v>2079</v>
       </c>
       <c r="C4" t="s">
-        <v>2092</v>
+        <v>2078</v>
       </c>
       <c r="D4" t="s">
         <v>889</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1915</v>
       </c>
       <c r="B5" t="s">
-        <v>2094</v>
+        <v>2080</v>
       </c>
       <c r="C5" t="s">
-        <v>2095</v>
+        <v>2081</v>
       </c>
       <c r="D5" t="s">
-        <v>2044</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
+        <v>2040</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1186</v>
       </c>
       <c r="B6" t="s">
-        <v>2097</v>
+        <v>2083</v>
       </c>
       <c r="C6" t="s">
-        <v>2096</v>
+        <v>2082</v>
       </c>
       <c r="D6" t="s">
-        <v>2045</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
+        <v>2041</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>2737</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>934</v>
       </c>
       <c r="B7" t="s">
-        <v>2099</v>
+        <v>2085</v>
       </c>
       <c r="C7" t="s">
-        <v>2098</v>
+        <v>2084</v>
       </c>
       <c r="D7" t="s">
         <v>935</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1910</v>
       </c>
       <c r="B8" t="s">
-        <v>2101</v>
+        <v>2087</v>
       </c>
       <c r="C8" t="s">
-        <v>2100</v>
+        <v>2086</v>
       </c>
       <c r="D8" t="s">
-        <v>2048</v>
-      </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
+        <v>2044</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2085</v>
+        <v>2071</v>
       </c>
       <c r="B9" t="s">
-        <v>2103</v>
+        <v>2089</v>
       </c>
       <c r="C9" t="s">
-        <v>2102</v>
+        <v>2088</v>
       </c>
       <c r="D9" t="s">
-        <v>2133</v>
-      </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
+        <v>2119</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>789</v>
       </c>
       <c r="B10" t="s">
-        <v>2105</v>
+        <v>2091</v>
       </c>
       <c r="C10" t="s">
-        <v>2104</v>
+        <v>2090</v>
       </c>
       <c r="D10" t="s">
         <v>790</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
+      <c r="E10" s="3" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>681</v>
       </c>
       <c r="B11" t="s">
-        <v>2107</v>
+        <v>2093</v>
       </c>
       <c r="C11" t="s">
-        <v>2106</v>
+        <v>2092</v>
       </c>
       <c r="D11" t="s">
         <v>682</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="10" t="s">
         <v>561</v>
       </c>
       <c r="B12" t="s">
-        <v>2108</v>
+        <v>2094</v>
       </c>
       <c r="C12" t="s">
-        <v>2109</v>
+        <v>2095</v>
       </c>
       <c r="D12" t="s">
         <v>562</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2086</v>
+        <v>2072</v>
       </c>
       <c r="B13" t="s">
-        <v>2110</v>
+        <v>2096</v>
       </c>
       <c r="C13" t="s">
-        <v>2111</v>
+        <v>2097</v>
       </c>
       <c r="D13" t="s">
-        <v>2134</v>
-      </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
+        <v>2120</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2087</v>
+        <v>2073</v>
       </c>
       <c r="B14" t="s">
-        <v>2112</v>
+        <v>2098</v>
       </c>
       <c r="C14" t="s">
-        <v>2113</v>
+        <v>2099</v>
       </c>
       <c r="D14" t="s">
-        <v>2135</v>
-      </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
+        <v>2121</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2088</v>
+        <v>2074</v>
       </c>
       <c r="B15" t="s">
-        <v>2114</v>
+        <v>2100</v>
       </c>
       <c r="C15" t="s">
-        <v>2115</v>
+        <v>2101</v>
       </c>
       <c r="D15" t="s">
         <v>758</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
+      <c r="E15" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1912</v>
       </c>
       <c r="B16" t="s">
-        <v>2116</v>
+        <v>2102</v>
       </c>
       <c r="C16" t="s">
-        <v>2117</v>
+        <v>2103</v>
       </c>
       <c r="D16" t="s">
-        <v>2063</v>
-      </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
+        <v>2054</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2089</v>
+        <v>2075</v>
       </c>
       <c r="B17" t="s">
-        <v>2118</v>
+        <v>2104</v>
       </c>
       <c r="C17" t="s">
-        <v>2119</v>
+        <v>2105</v>
       </c>
       <c r="D17" t="s">
-        <v>2066</v>
-      </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
+        <v>2056</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>988</v>
       </c>
       <c r="B18" t="s">
-        <v>2120</v>
+        <v>2106</v>
       </c>
       <c r="C18" t="s">
-        <v>2121</v>
+        <v>2107</v>
       </c>
       <c r="D18" t="s">
-        <v>2136</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -24190,13 +26081,13 @@
         <v>673</v>
       </c>
       <c r="B19" t="s">
-        <v>2122</v>
+        <v>2108</v>
       </c>
       <c r="C19" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D19" t="s">
         <v>2123</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -24204,10 +26095,10 @@
         <v>735</v>
       </c>
       <c r="B20" t="s">
-        <v>2124</v>
+        <v>2110</v>
       </c>
       <c r="C20" t="s">
-        <v>2125</v>
+        <v>2111</v>
       </c>
       <c r="D20" t="s">
         <v>736</v>
@@ -24218,27 +26109,27 @@
         <v>717</v>
       </c>
       <c r="B21" t="s">
-        <v>2126</v>
+        <v>2112</v>
       </c>
       <c r="C21" t="s">
-        <v>2127</v>
+        <v>2113</v>
       </c>
       <c r="D21" t="s">
-        <v>2076</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2090</v>
+        <v>2076</v>
       </c>
       <c r="B22" t="s">
-        <v>2128</v>
+        <v>2114</v>
       </c>
       <c r="C22" t="s">
-        <v>2129</v>
+        <v>2115</v>
       </c>
       <c r="D22" t="s">
-        <v>2074</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -24246,10 +26137,10 @@
         <v>750</v>
       </c>
       <c r="B23" t="s">
-        <v>2130</v>
+        <v>2116</v>
       </c>
       <c r="C23" t="s">
-        <v>2131</v>
+        <v>2117</v>
       </c>
       <c r="D23" t="s">
         <v>751</v>
@@ -24257,16 +26148,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2091</v>
+        <v>2077</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>2171</v>
+        <v>2157</v>
       </c>
       <c r="C24" t="s">
-        <v>2132</v>
+        <v>2118</v>
       </c>
       <c r="D24" t="s">
-        <v>2062</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -24274,13 +26165,16 @@
         <v>214</v>
       </c>
       <c r="B25" t="s">
-        <v>2232</v>
+        <v>2215</v>
       </c>
       <c r="C25" t="s">
-        <v>2231</v>
+        <v>2214</v>
       </c>
       <c r="D25" t="s">
-        <v>2230</v>
+        <v>2770</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2740</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -24288,13 +26182,16 @@
         <v>940</v>
       </c>
       <c r="B26" t="s">
-        <v>2249</v>
+        <v>2230</v>
       </c>
       <c r="C26" t="s">
-        <v>2250</v>
+        <v>2231</v>
       </c>
       <c r="D26" t="s">
-        <v>2248</v>
+        <v>2229</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>2741</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -24302,13 +26199,418 @@
         <v>332</v>
       </c>
       <c r="B27" t="s">
-        <v>2256</v>
+        <v>2237</v>
       </c>
       <c r="C27" t="s">
-        <v>2257</v>
+        <v>2238</v>
       </c>
       <c r="D27" t="s">
-        <v>2258</v>
+        <v>2239</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2769</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>429</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D30" t="s">
+        <v>430</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>919</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>520</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>741</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>961</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>855</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2731</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>921</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>771</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>493</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2455</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2383</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2732</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2385</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>406</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>743</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2453</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2734</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2765</v>
       </c>
     </row>
   </sheetData>
@@ -24322,14 +26624,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE8D39E-D634-4D2B-9415-34710137330E}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
     <col min="3" max="3" width="17.5546875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
     <col min="5" max="5" width="30.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" customWidth="1"/>
     <col min="11" max="11" width="32.88671875" customWidth="1"/>
     <col min="12" max="12" width="26.21875" customWidth="1"/>
     <col min="13" max="13" width="29" customWidth="1"/>
@@ -24352,16 +26655,16 @@
         <v>1949</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2172</v>
+        <v>2158</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -24369,25 +26672,25 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C2" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D2" t="s">
-        <v>2262</v>
+        <v>2771</v>
       </c>
       <c r="E2" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="K2" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="L2" t="s">
         <v>1199</v>
       </c>
       <c r="M2" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -24395,25 +26698,25 @@
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C3" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D3" t="s">
-        <v>2263</v>
+        <v>2772</v>
       </c>
       <c r="E3" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="K3" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="L3" t="s">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="M3" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -24421,28 +26724,28 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C4" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D4" t="s">
-        <v>2264</v>
+        <v>2773</v>
       </c>
       <c r="E4" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="F4" t="s">
-        <v>2276</v>
+        <v>2252</v>
       </c>
       <c r="K4" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="L4" t="s">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="M4" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -24450,28 +26753,28 @@
         <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D5" t="s">
-        <v>2265</v>
+        <v>2774</v>
       </c>
       <c r="E5" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="F5" t="s">
-        <v>2281</v>
+        <v>2257</v>
       </c>
       <c r="K5" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="L5" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="M5" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -24479,28 +26782,28 @@
         <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C6" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D6" t="s">
-        <v>2266</v>
+        <v>2243</v>
       </c>
       <c r="E6" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="F6" t="s">
-        <v>2279</v>
+        <v>2255</v>
       </c>
       <c r="K6" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="L6" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="M6" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -24508,28 +26811,28 @@
         <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C7" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="D7" t="s">
-        <v>2267</v>
+        <v>2244</v>
       </c>
       <c r="E7" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="F7" t="s">
-        <v>2279</v>
+        <v>2255</v>
       </c>
       <c r="K7" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="L7" t="s">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="M7" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -24537,28 +26840,28 @@
         <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="D8" t="s">
-        <v>2268</v>
+        <v>2245</v>
       </c>
       <c r="E8" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="F8" t="s">
-        <v>2275</v>
+        <v>2251</v>
       </c>
       <c r="K8" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="L8" t="s">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="M8" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -24566,28 +26869,28 @@
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C9" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="D9" t="s">
-        <v>2269</v>
+        <v>2246</v>
       </c>
       <c r="E9" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="F9" t="s">
-        <v>2283</v>
+        <v>2259</v>
       </c>
       <c r="K9" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="L9" t="s">
         <v>1824</v>
       </c>
       <c r="M9" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -24595,28 +26898,28 @@
         <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C10" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="D10" t="s">
-        <v>2270</v>
+        <v>2247</v>
       </c>
       <c r="E10" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="F10" t="s">
-        <v>2282</v>
+        <v>2258</v>
       </c>
       <c r="K10" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="L10" t="s">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="M10" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -24624,28 +26927,28 @@
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C11" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="D11" t="s">
         <v>1575</v>
       </c>
       <c r="E11" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="F11" t="s">
-        <v>2284</v>
+        <v>2260</v>
       </c>
       <c r="K11" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="L11" t="s">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="M11" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -24653,25 +26956,25 @@
         <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C12" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="F12" t="s">
-        <v>2285</v>
+        <v>2261</v>
       </c>
       <c r="K12" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="L12" t="s">
-        <v>2000</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -24679,28 +26982,28 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C13" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="D13" t="s">
-        <v>2271</v>
+        <v>2775</v>
       </c>
       <c r="E13" t="s">
-        <v>2038</v>
+        <v>2034</v>
       </c>
       <c r="F13" t="s">
-        <v>2278</v>
+        <v>2254</v>
       </c>
       <c r="K13" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="L13" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="M13" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -24708,28 +27011,28 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C14" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D14" t="s">
-        <v>2272</v>
+        <v>2248</v>
       </c>
       <c r="E14" t="s">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="F14" t="s">
-        <v>2277</v>
+        <v>2253</v>
       </c>
       <c r="K14" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="L14" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="M14" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -24737,28 +27040,28 @@
         <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C15" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D15" t="s">
-        <v>2273</v>
+        <v>2249</v>
       </c>
       <c r="E15" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="F15" t="s">
-        <v>2280</v>
+        <v>2256</v>
       </c>
       <c r="K15" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="L15" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="M15" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -24766,25 +27069,25 @@
         <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C16" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="D16" t="s">
-        <v>2274</v>
+        <v>2250</v>
       </c>
       <c r="E16" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="F16" t="s">
-        <v>2280</v>
+        <v>2256</v>
       </c>
       <c r="K16" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="L16" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -24792,25 +27095,25 @@
         <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C17" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D17" t="s">
-        <v>2233</v>
+        <v>2776</v>
       </c>
       <c r="E17" t="s">
-        <v>2234</v>
+        <v>2216</v>
       </c>
       <c r="F17" t="s">
-        <v>2245</v>
+        <v>2226</v>
       </c>
       <c r="K17" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="L17" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -24818,25 +27121,25 @@
         <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C18" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D18" t="s">
-        <v>2235</v>
+        <v>2217</v>
       </c>
       <c r="E18" t="s">
-        <v>2236</v>
+        <v>2218</v>
       </c>
       <c r="F18" t="s">
-        <v>2244</v>
+        <v>2225</v>
       </c>
       <c r="K18" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="L18" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -24844,19 +27147,19 @@
         <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C19" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D19" t="s">
-        <v>2237</v>
+        <v>2219</v>
       </c>
       <c r="E19" t="s">
-        <v>2238</v>
+        <v>2220</v>
       </c>
       <c r="F19" t="s">
-        <v>2247</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -24864,19 +27167,19 @@
         <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C20" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="D20" t="s">
-        <v>2288</v>
+        <v>2777</v>
       </c>
       <c r="E20" t="s">
-        <v>2290</v>
+        <v>2265</v>
       </c>
       <c r="F20" t="s">
-        <v>2289</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -24884,19 +27187,19 @@
         <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C21" t="s">
-        <v>2241</v>
+        <v>2222</v>
       </c>
       <c r="D21" t="s">
-        <v>2239</v>
+        <v>2778</v>
       </c>
       <c r="E21" t="s">
-        <v>2240</v>
+        <v>2221</v>
       </c>
       <c r="F21" t="s">
-        <v>2246</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -24904,16 +27207,16 @@
         <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C22" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D22" t="s">
-        <v>2242</v>
+        <v>2223</v>
       </c>
       <c r="E22" t="s">
-        <v>2243</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -24921,19 +27224,19 @@
         <v>940</v>
       </c>
       <c r="B23" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C23" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D23" t="s">
-        <v>2252</v>
+        <v>2233</v>
       </c>
       <c r="E23" t="s">
-        <v>2251</v>
+        <v>2232</v>
       </c>
       <c r="F23" t="s">
-        <v>2287</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -24941,19 +27244,19 @@
         <v>940</v>
       </c>
       <c r="B24" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C24" t="s">
-        <v>2255</v>
+        <v>2236</v>
       </c>
       <c r="D24" t="s">
-        <v>2253</v>
+        <v>2234</v>
       </c>
       <c r="E24" t="s">
-        <v>2254</v>
+        <v>2235</v>
       </c>
       <c r="F24" t="s">
-        <v>2287</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -24961,19 +27264,19 @@
         <v>332</v>
       </c>
       <c r="B25" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C25" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="D25" t="s">
-        <v>2259</v>
+        <v>2240</v>
       </c>
       <c r="E25" t="s">
-        <v>2260</v>
+        <v>2241</v>
       </c>
       <c r="F25" t="s">
-        <v>2291</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -24981,19 +27284,1396 @@
         <v>332</v>
       </c>
       <c r="B26" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C26" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="D26" t="s">
         <v>342</v>
       </c>
       <c r="E26" t="s">
-        <v>2261</v>
+        <v>2242</v>
       </c>
       <c r="F26" t="s">
-        <v>2286</v>
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2779</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2289</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2780</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2310</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2782</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>297</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>429</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>429</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2784</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2322</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>429</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F37" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>429</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2326</v>
+      </c>
+      <c r="F38" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>429</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F39" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F40" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>919</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F41" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>919</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2336</v>
+      </c>
+      <c r="F42" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>919</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F43" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>520</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F44" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>520</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F45" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>520</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>741</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F47" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2785</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2359</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2786</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F50" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>280</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>280</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F52" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>961</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F53" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>961</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F54" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>855</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F55" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>855</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F56" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2410</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F57" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2413</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F58" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F59" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>921</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>2417</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>921</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>921</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2421</v>
+      </c>
+      <c r="F62" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>771</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2422</v>
+      </c>
+      <c r="F63" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F64" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F66" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>344</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F68" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>406</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E70" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F70" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>743</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F71" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>743</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E72" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F72" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>743</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F73" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>743</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E74" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F74" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>493</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2792</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>493</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2793</v>
+      </c>
+      <c r="E77" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E78" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E79" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>789</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E80" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>789</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>789</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E82" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>789</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2795</v>
+      </c>
+      <c r="E83" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>789</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>2492</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2796</v>
+      </c>
+      <c r="E84" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>789</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D85" t="s">
+        <v>2797</v>
+      </c>
+      <c r="E85" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E86" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D87" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E87" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E88" t="s">
+        <v>2470</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D89" t="s">
+        <v>2471</v>
+      </c>
+      <c r="E89" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D90" t="s">
+        <v>2490</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E91" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D92" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E92" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F92" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D93" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E93" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F93" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D94" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E94" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F94" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>789</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E95" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F95" t="s">
+        <v>2485</v>
       </c>
     </row>
   </sheetData>
@@ -25004,343 +28684,1607 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F9037D-2FFF-4A89-AE76-23434A393A5B}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="4" width="40.6640625" customWidth="1"/>
-    <col min="5" max="5" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1950</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>1950</v>
+        <v>1987</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E1" s="2" t="s">
         <v>1951</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>2218</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
-      <c r="C3" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>2219</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="C4" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>2220</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
-      <c r="C5" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>2221</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2221</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2221</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>2843</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>2222</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="7" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>2223</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C9" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>2224</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C10" s="7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>2225</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>2226</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="7" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>2227</v>
-      </c>
-      <c r="E13" t="s">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C13" s="7" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>2228</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C14" s="7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>2229</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>214</v>
       </c>
-      <c r="C16" t="s">
-        <v>2296</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>2294</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>214</v>
       </c>
-      <c r="C17" t="s">
-        <v>2298</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>2299</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>214</v>
       </c>
-      <c r="C18" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>2293</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2292</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>940</v>
       </c>
-      <c r="C19" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>2301</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2302</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>940</v>
       </c>
-      <c r="C20" t="s">
-        <v>2305</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>2304</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2306</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>332</v>
       </c>
-      <c r="C21" t="s">
-        <v>2308</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>2307</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2309</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>332</v>
       </c>
-      <c r="C22" t="s">
-        <v>2311</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>2310</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2312</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>332</v>
       </c>
-      <c r="C23" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>2313</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2315</v>
+      <c r="B23" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>921</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>921</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>921</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>921</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>921</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>921</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>789</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>789</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>789</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>789</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>789</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>789</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2569</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>771</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>771</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>771</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>771</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>771</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>429</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>429</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>919</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>520</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>919</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>520</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>520</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>520</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2629</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>741</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>741</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>280</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>280</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>2646</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>961</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>961</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>855</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>855</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>855</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>406</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2673</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D85" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2680</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D87" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D89" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>406</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D90" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>344</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>344</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D92" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>493</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D93" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>493</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D94" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>743</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>743</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D96" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>174</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D97" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>174</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D98" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>297</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D101" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D102" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>174</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D103" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D104" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>520</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D107" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D108" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D109" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>297</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D110" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>297</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2834</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>2835</v>
+      </c>
+      <c r="D111" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>855</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D112" t="s">
+        <v>2872</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{27E7CDCB-A0A8-4370-9150-CA844240B6A9}"/>
-    <hyperlink ref="D3" r:id="rId2" location="/media/%D0%A4%D0%B0%D0%B9%D0%BB:%D0%91%D0%B8%D1%80%D0%BE%D0%B1%D0%B8%D0%B4%D0%B6%D0%B0%D0%BD_%D0%B3%D0%B5%D1%80%D0%B1.svg" xr:uid="{6B198038-6F1C-480B-8D52-B1262A7E0C69}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{32875EC6-FFFC-40BA-807F-770B994307A6}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{9DC3686B-319F-41DB-A6EA-F01122A4679A}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{AE9398FE-2E18-463C-8B4A-F6AF279A2FF4}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{180D55C4-142C-444F-989D-EE4C50EE674C}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{56F2E4F1-40B5-4EB2-9402-2FE5DFBCF9EE}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{DD4E52E2-1BE1-472A-B5D4-422D2A93352B}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{259377A8-76F3-4D50-B93F-BC882F4D58C7}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{B4D27034-CBD1-4809-823D-E6278C4BDC94}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{C4BE3D76-7EB4-4964-845F-A4DA97115652}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{3C8D2EE5-B094-4A1F-877D-5373FFE28F24}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{CA81C2A2-ED57-47CA-85EC-26DCFED90C68}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{C647C96D-9DED-440B-9D46-858CFDDDD6A1}"/>
-    <hyperlink ref="D18" r:id="rId15" xr:uid="{0DF66E0B-B820-4652-AD44-C30F04FACBFA}"/>
-    <hyperlink ref="D16" r:id="rId16" xr:uid="{1DAE4836-C456-4FAD-A8BA-293EBDEE3491}"/>
-    <hyperlink ref="D17" r:id="rId17" xr:uid="{B27057F4-25B4-4F41-8870-A2B222C5B37F}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{DAB740DD-B136-473F-BCCF-350FFB1D8B70}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{92E3EAC3-B177-4926-A6B3-DBCD576CEAD4}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{E334FD46-F658-4D33-BA78-CFFD524CFED9}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{292F3B59-22B3-43AE-84E5-F684A62FB244}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{2C18FD8F-8517-4D05-B42B-0E54DA2FA940}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{27E7CDCB-A0A8-4370-9150-CA844240B6A9}"/>
+    <hyperlink ref="C3" r:id="rId2" location="/media/%D0%A4%D0%B0%D0%B9%D0%BB:%D0%91%D0%B8%D1%80%D0%BE%D0%B1%D0%B8%D0%B4%D0%B6%D0%B0%D0%BD_%D0%B3%D0%B5%D1%80%D0%B1.svg" xr:uid="{6B198038-6F1C-480B-8D52-B1262A7E0C69}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{32875EC6-FFFC-40BA-807F-770B994307A6}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{9DC3686B-319F-41DB-A6EA-F01122A4679A}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{AE9398FE-2E18-463C-8B4A-F6AF279A2FF4}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{180D55C4-142C-444F-989D-EE4C50EE674C}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{56F2E4F1-40B5-4EB2-9402-2FE5DFBCF9EE}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{DD4E52E2-1BE1-472A-B5D4-422D2A93352B}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{259377A8-76F3-4D50-B93F-BC882F4D58C7}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{B4D27034-CBD1-4809-823D-E6278C4BDC94}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{C4BE3D76-7EB4-4964-845F-A4DA97115652}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{3C8D2EE5-B094-4A1F-877D-5373FFE28F24}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{CA81C2A2-ED57-47CA-85EC-26DCFED90C68}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{C647C96D-9DED-440B-9D46-858CFDDDD6A1}"/>
+    <hyperlink ref="C18" r:id="rId15" xr:uid="{0DF66E0B-B820-4652-AD44-C30F04FACBFA}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{1DAE4836-C456-4FAD-A8BA-293EBDEE3491}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{B27057F4-25B4-4F41-8870-A2B222C5B37F}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{DAB740DD-B136-473F-BCCF-350FFB1D8B70}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{92E3EAC3-B177-4926-A6B3-DBCD576CEAD4}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{E334FD46-F658-4D33-BA78-CFFD524CFED9}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{292F3B59-22B3-43AE-84E5-F684A62FB244}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{2C18FD8F-8517-4D05-B42B-0E54DA2FA940}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{AD37188A-1B0B-4A72-A0B9-6DCB06A2F384}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{45CE2B64-3AA9-40A9-9E9C-3176E049716D}"/>
+    <hyperlink ref="C31" r:id="rId25" xr:uid="{A14CA844-5BCB-43E5-8A19-B75696C7CAC2}"/>
+    <hyperlink ref="C32" r:id="rId26" xr:uid="{E27FEAD8-7246-458A-9158-960E42269369}"/>
+    <hyperlink ref="C37" r:id="rId27" xr:uid="{9B545D9B-1FBE-4D98-88D2-9DC39F569D25}"/>
+    <hyperlink ref="C44" r:id="rId28" xr:uid="{036DA211-2FF2-4A5F-8D96-744B357BA469}"/>
+    <hyperlink ref="C45" r:id="rId29" xr:uid="{12EE533A-E2DF-4CEC-83F3-8F528D3ADC9E}"/>
+    <hyperlink ref="C46" r:id="rId30" xr:uid="{B3DE9C9C-1ADE-4DCD-AD06-A376A045E45F}"/>
+    <hyperlink ref="C47" r:id="rId31" xr:uid="{A532E9A2-8A7E-44CF-A1AC-157E550E8D26}"/>
+    <hyperlink ref="C48" r:id="rId32" xr:uid="{3D8A23BE-FA53-46BB-B9A6-39EC8F0BD9A6}"/>
+    <hyperlink ref="C49" r:id="rId33" xr:uid="{56D0E9AC-75F5-496E-AE04-166A5F3DB9D9}"/>
+    <hyperlink ref="C50" r:id="rId34" xr:uid="{32E38A4E-7776-4EB2-B83E-05BC2A3E860E}"/>
+    <hyperlink ref="C51" r:id="rId35" xr:uid="{58F8E0DB-7398-4994-83E3-7C68D1EACC4C}"/>
+    <hyperlink ref="C52" r:id="rId36" xr:uid="{A1EDBE7D-C2F8-45CA-B14C-0262BC102CCD}"/>
+    <hyperlink ref="C53" r:id="rId37" xr:uid="{215E9EC6-CFE6-4000-BE8D-035F44FADA3D}"/>
+    <hyperlink ref="C54" r:id="rId38" xr:uid="{DE831A14-EB45-4D75-B896-2C344A82F321}"/>
+    <hyperlink ref="C55" r:id="rId39" xr:uid="{7931C111-D192-4D65-AAEF-D008DCB590F9}"/>
+    <hyperlink ref="C56" r:id="rId40" xr:uid="{FB41801A-A13F-4460-AE65-26EFD58A35C5}"/>
+    <hyperlink ref="C57" r:id="rId41" xr:uid="{68DE414B-1142-4D93-AD86-144BC8B1954F}"/>
+    <hyperlink ref="C58" r:id="rId42" xr:uid="{1EEB3A7F-B177-4DFD-B896-814353C16463}"/>
+    <hyperlink ref="C59" r:id="rId43" xr:uid="{8AD8EA5B-2FE1-4B67-907E-5604AC0BD4BE}"/>
+    <hyperlink ref="C60" r:id="rId44" xr:uid="{584084A4-6D7B-458E-B568-4261B479FE99}"/>
+    <hyperlink ref="C62" r:id="rId45" xr:uid="{E41C41BB-BB24-4C28-B5EF-ED7C28D12CC1}"/>
+    <hyperlink ref="C61" r:id="rId46" xr:uid="{DF827818-0B56-41AB-A12A-FF3D5D412AAA}"/>
+    <hyperlink ref="C63" r:id="rId47" xr:uid="{DE9858D5-64F9-4A78-AC14-A4039A12D85E}"/>
+    <hyperlink ref="C64" r:id="rId48" xr:uid="{03858558-29A2-4A63-B263-854AB4F21684}"/>
+    <hyperlink ref="C65" r:id="rId49" xr:uid="{DA27F113-0765-4162-B9B0-B07FED6C8456}"/>
+    <hyperlink ref="C66" r:id="rId50" xr:uid="{1FA927D1-861F-4D6B-A354-AC3A63D513BA}"/>
+    <hyperlink ref="C67" r:id="rId51" xr:uid="{5DDDCC82-5973-48A3-AFE3-6918189FD3A0}"/>
+    <hyperlink ref="C68" r:id="rId52" xr:uid="{6BF9F416-B919-4B87-BDF0-B0A47D70DC27}"/>
+    <hyperlink ref="C69" r:id="rId53" xr:uid="{60F23DC4-D38A-4BA0-B72E-080E5D24F7B0}"/>
+    <hyperlink ref="C70" r:id="rId54" xr:uid="{4F1352A0-2519-45DC-80AA-AABAF576D870}"/>
+    <hyperlink ref="C71" r:id="rId55" xr:uid="{381E3215-175F-408C-9AE4-57344A2D3087}"/>
+    <hyperlink ref="C72" r:id="rId56" xr:uid="{DEB8E8C6-3200-4525-8093-E15B76A7451D}"/>
+    <hyperlink ref="C73" r:id="rId57" xr:uid="{C8C30B8B-0062-4283-B1F3-0D19EF4B30A5}"/>
+    <hyperlink ref="C74" r:id="rId58" xr:uid="{5445F3D0-CAA6-4181-8538-CFDAE534D350}"/>
+    <hyperlink ref="C75" r:id="rId59" xr:uid="{8E19C425-5DE7-49B2-930F-97A6AA2DBA1C}"/>
+    <hyperlink ref="C76" r:id="rId60" xr:uid="{52CC2529-B991-409D-9FDA-60FB716E3803}"/>
+    <hyperlink ref="C77" r:id="rId61" xr:uid="{0AF157CB-A618-4AF0-A89C-70724CC73EF5}"/>
+    <hyperlink ref="C78" r:id="rId62" xr:uid="{22E94577-DC35-4DE4-80A2-C6B14DACC639}"/>
+    <hyperlink ref="C79" r:id="rId63" xr:uid="{C1CF336C-4CE1-48B3-86A8-4F1893A4F941}"/>
+    <hyperlink ref="C80" r:id="rId64" xr:uid="{4728872B-7778-49CB-B629-B02BCA910886}"/>
+    <hyperlink ref="C81" r:id="rId65" xr:uid="{4AD47725-A5D9-48F6-8C9E-0707A18E408D}"/>
+    <hyperlink ref="C82" r:id="rId66" xr:uid="{2A83656F-012D-491B-B699-22C7A20F81B6}"/>
+    <hyperlink ref="C83" r:id="rId67" xr:uid="{A1583923-1921-49BB-9773-A96F9A19B250}"/>
+    <hyperlink ref="C84" r:id="rId68" xr:uid="{B7ABDF8C-0FFA-49C8-9950-E05993202C5C}"/>
+    <hyperlink ref="C85" r:id="rId69" xr:uid="{3B93F33C-1BEB-4D42-B781-302022233ACA}"/>
+    <hyperlink ref="C86" r:id="rId70" xr:uid="{AEFCF2B1-9997-4AC0-B2EF-3DB6A955ADF8}"/>
+    <hyperlink ref="C90" r:id="rId71" xr:uid="{AF515C10-815A-49EA-95CA-87854D10184E}"/>
+    <hyperlink ref="C88" r:id="rId72" xr:uid="{0EF846F5-B8F8-45EA-B958-D70230022333}"/>
+    <hyperlink ref="C89" r:id="rId73" xr:uid="{FCA1B6A0-3E2C-4AFD-BB1A-A69FCA18F9C4}"/>
+    <hyperlink ref="C92" r:id="rId74" xr:uid="{C907E72B-0D9F-443F-800A-59881E576224}"/>
+    <hyperlink ref="C91" r:id="rId75" xr:uid="{ADACA191-42C5-4D27-8ACA-77F34CBA23B0}"/>
+    <hyperlink ref="C93" r:id="rId76" xr:uid="{7F42E1C4-80A4-4D0E-9CCA-76E8836E3BD9}"/>
+    <hyperlink ref="C94" r:id="rId77" xr:uid="{01110205-39B8-4CB4-845E-4FF96424CD41}"/>
+    <hyperlink ref="C97" r:id="rId78" xr:uid="{0B7BCE72-6D73-4605-97A6-44FE0897EB55}"/>
+    <hyperlink ref="C95" r:id="rId79" xr:uid="{F0BBD4F7-DCC7-488C-A551-9C968F744156}"/>
+    <hyperlink ref="C98" r:id="rId80" xr:uid="{009F2EAF-606A-41AE-A5CE-3BAA6504D251}"/>
+    <hyperlink ref="C99" r:id="rId81" xr:uid="{3FED2AD9-62F2-41E5-8962-8EE8AA5705D5}"/>
+    <hyperlink ref="C100" r:id="rId82" xr:uid="{3FEBFCA0-0EF3-411F-9AB6-DD45191CD41B}"/>
+    <hyperlink ref="C101" r:id="rId83" display="https://sun9-72.userapi.com/s/v1/ig2/Iw3xii9IAj8pyPb0RQm3E9e_E8Et8Zp0XQHez2ap-bLz3RjgtZyJQOU1xrRVdII4ES-CPlSwgm2Q2rswviMydTKq.jpg?quality=96&amp;as=32x15,48x23,72x35,108x52,160x77,240x115,360x173,480x231,540x260,640x308,720x346,1080x520,1280x616&amp;from=bu&amp;cs=1280x0" xr:uid="{B89B88D2-B719-4313-8447-F01F7254019F}"/>
+    <hyperlink ref="C102" r:id="rId84" xr:uid="{59A0FC15-3E7F-4095-8E93-FB453941B149}"/>
+    <hyperlink ref="C103" r:id="rId85" xr:uid="{C645FCFB-0C40-4EB0-8E44-0A40F08E8A61}"/>
+    <hyperlink ref="C105" r:id="rId86" xr:uid="{03ED6BAE-B3ED-455E-9649-D95A63DF67D5}"/>
+    <hyperlink ref="C106" r:id="rId87" xr:uid="{DA24EC53-1A2D-4E14-A84C-84F095DE4992}"/>
+    <hyperlink ref="C107" r:id="rId88" xr:uid="{226BD253-DFE0-41D0-909B-BF60B02672E3}"/>
+    <hyperlink ref="C108" r:id="rId89" xr:uid="{F2B94FC6-16EB-4AD2-892C-26EE19B6728E}"/>
+    <hyperlink ref="C109" r:id="rId90" xr:uid="{6559EF98-F304-472E-B48C-025D5516F850}"/>
+    <hyperlink ref="C110" r:id="rId91" xr:uid="{53FE4C00-0458-40D7-99EA-61AAEEC7C448}"/>
+    <hyperlink ref="C111" r:id="rId92" xr:uid="{4968C57C-D7FA-4D6E-9443-DCD1C641F0A7}"/>
+    <hyperlink ref="C104" r:id="rId93" xr:uid="{6C8ABDD9-1552-4631-890C-72858AE7FED7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25364,19 +30308,19 @@
   <sheetData>
     <row r="1" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2169</v>
+        <v>2155</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2183</v>
+        <v>2167</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2170</v>
+        <v>2156</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2184</v>
+        <v>2168</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1946</v>
@@ -25391,13 +30335,13 @@
         <v>1949</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>2172</v>
+        <v>2158</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>1950</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>1951</v>
@@ -25405,7 +30349,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2138</v>
+        <v>2124</v>
       </c>
       <c r="B2" t="s">
         <v>888</v>
@@ -25420,68 +30364,68 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G2" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="H2" t="s">
-        <v>2173</v>
+        <v>2870</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2187</v>
+        <v>2171</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1973</v>
-      </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>1972</v>
+      </c>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2139</v>
+        <v>2125</v>
       </c>
       <c r="B3" t="s">
         <v>1915</v>
       </c>
       <c r="C3" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="D3" t="s">
         <v>1186</v>
       </c>
       <c r="E3" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="F3" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G3" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="H3" t="s">
         <v>1556</v>
       </c>
       <c r="I3" t="s">
-        <v>2188</v>
+        <v>2172</v>
       </c>
       <c r="J3" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2140</v>
+        <v>2126</v>
       </c>
       <c r="B4" t="s">
         <v>888</v>
@@ -25496,29 +30440,29 @@
         <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G4" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="H4" t="s">
-        <v>1117</v>
+        <v>2869</v>
       </c>
       <c r="I4" t="s">
-        <v>2189</v>
+        <v>2173</v>
       </c>
       <c r="J4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2141</v>
+        <v>2127</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -25533,35 +30477,35 @@
         <v>935</v>
       </c>
       <c r="F5" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G5" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="H5" t="s">
-        <v>1128</v>
+        <v>2868</v>
       </c>
       <c r="I5" t="s">
-        <v>2190</v>
+        <v>2174</v>
       </c>
       <c r="J5" t="s">
-        <v>2175</v>
-      </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
+        <v>2160</v>
+      </c>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2142</v>
+        <v>2128</v>
       </c>
       <c r="B6" t="s">
         <v>1910</v>
       </c>
       <c r="C6" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="D6" t="s">
         <v>65</v>
@@ -25570,29 +30514,29 @@
         <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G6" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="H6" t="s">
-        <v>2082</v>
+        <v>2867</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2191</v>
+        <v>2175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2143</v>
+        <v>2129</v>
       </c>
       <c r="B7" t="s">
         <v>888</v>
@@ -25607,35 +30551,35 @@
         <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G7" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="H7" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="I7" t="s">
-        <v>2192</v>
+        <v>2176</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
+        <v>2161</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2144</v>
+        <v>2130</v>
       </c>
       <c r="B8" t="s">
-        <v>2085</v>
+        <v>2071</v>
       </c>
       <c r="C8" t="s">
-        <v>2133</v>
+        <v>2119</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
@@ -25644,29 +30588,29 @@
         <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="G8" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>2051</v>
+        <v>2866</v>
       </c>
       <c r="I8" t="s">
-        <v>2193</v>
+        <v>2177</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2145</v>
+        <v>2131</v>
       </c>
       <c r="B9" t="s">
         <v>934</v>
@@ -25681,29 +30625,29 @@
         <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="G9" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>2053</v>
+        <v>2865</v>
       </c>
       <c r="I9" t="s">
-        <v>2194</v>
+        <v>2178</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
+        <v>2162</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2146</v>
+        <v>2132</v>
       </c>
       <c r="B10" t="s">
         <v>888</v>
@@ -25718,29 +30662,29 @@
         <v>790</v>
       </c>
       <c r="F10" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G10" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>2054</v>
+        <v>2864</v>
       </c>
       <c r="I10" t="s">
-        <v>2195</v>
+        <v>2179</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
+        <v>2159</v>
+      </c>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2147</v>
+        <v>2133</v>
       </c>
       <c r="B11" t="s">
         <v>65</v>
@@ -25755,35 +30699,35 @@
         <v>682</v>
       </c>
       <c r="F11" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="G11" t="s">
-        <v>2057</v>
+        <v>2049</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>2056</v>
+        <v>2863</v>
       </c>
       <c r="I11" t="s">
-        <v>2196</v>
+        <v>2180</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2175</v>
-      </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
+        <v>2160</v>
+      </c>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2148</v>
+        <v>2134</v>
       </c>
       <c r="B12" t="s">
-        <v>2086</v>
+        <v>2072</v>
       </c>
       <c r="C12" t="s">
-        <v>2185</v>
+        <v>2169</v>
       </c>
       <c r="D12" t="s">
         <v>65</v>
@@ -25792,24 +30736,24 @@
         <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>2058</v>
+        <v>2050</v>
       </c>
       <c r="G12" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>2059</v>
+        <v>2862</v>
       </c>
       <c r="I12" t="s">
-        <v>2197</v>
+        <v>2181</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2176</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2149</v>
+        <v>2135</v>
       </c>
       <c r="B13" t="s">
         <v>888</v>
@@ -25821,27 +30765,27 @@
         <v>1186</v>
       </c>
       <c r="E13" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="F13" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G13" t="s">
-        <v>2061</v>
+        <v>2052</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>2060</v>
+        <v>2051</v>
       </c>
       <c r="I13" t="s">
-        <v>2198</v>
+        <v>2182</v>
       </c>
       <c r="J13" t="s">
-        <v>2178</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2150</v>
+        <v>2136</v>
       </c>
       <c r="B14" t="s">
         <v>888</v>
@@ -25856,24 +30800,24 @@
         <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>2058</v>
+        <v>2050</v>
       </c>
       <c r="G14" t="s">
-        <v>2061</v>
+        <v>2052</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1198</v>
+        <v>2861</v>
       </c>
       <c r="I14" t="s">
-        <v>2199</v>
+        <v>2183</v>
       </c>
       <c r="J14" t="s">
-        <v>2178</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2151</v>
+        <v>2137</v>
       </c>
       <c r="B15" t="s">
         <v>65</v>
@@ -25888,30 +30832,30 @@
         <v>935</v>
       </c>
       <c r="F15" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G15" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1254</v>
+        <v>2860</v>
       </c>
       <c r="I15" t="s">
-        <v>2200</v>
+        <v>2184</v>
       </c>
       <c r="J15" t="s">
-        <v>2179</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2152</v>
+        <v>2138</v>
       </c>
       <c r="B16" t="s">
-        <v>2087</v>
+        <v>2073</v>
       </c>
       <c r="C16" t="s">
-        <v>2135</v>
+        <v>2121</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -25920,62 +30864,62 @@
         <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G16" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1352</v>
+        <v>2859</v>
       </c>
       <c r="I16" t="s">
-        <v>2201</v>
+        <v>2185</v>
       </c>
       <c r="J16" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2153</v>
+        <v>2139</v>
       </c>
       <c r="B17" t="s">
-        <v>2091</v>
+        <v>2077</v>
       </c>
       <c r="C17" t="s">
-        <v>2186</v>
+        <v>2170</v>
       </c>
       <c r="D17" t="s">
-        <v>2088</v>
+        <v>2074</v>
       </c>
       <c r="E17" t="s">
         <v>758</v>
       </c>
       <c r="F17" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G17" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1309</v>
+        <v>2858</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>2202</v>
+        <v>2186</v>
       </c>
       <c r="J17" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2154</v>
+        <v>2140</v>
       </c>
       <c r="B18" t="s">
         <v>1912</v>
       </c>
       <c r="C18" t="s">
-        <v>2063</v>
+        <v>2054</v>
       </c>
       <c r="D18" t="s">
         <v>65</v>
@@ -25984,24 +30928,24 @@
         <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G18" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1823</v>
+        <v>2857</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>2203</v>
+        <v>2187</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>2176</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2155</v>
+        <v>2141</v>
       </c>
       <c r="B19" t="s">
         <v>934</v>
@@ -26016,24 +30960,24 @@
         <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G19" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>2064</v>
+        <v>2856</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>2204</v>
+        <v>2188</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2156</v>
+        <v>2142</v>
       </c>
       <c r="B20" t="s">
         <v>888</v>
@@ -26048,30 +30992,30 @@
         <v>562</v>
       </c>
       <c r="F20" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G20" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>2067</v>
+        <v>2855</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>2205</v>
+        <v>2189</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2157</v>
+        <v>2143</v>
       </c>
       <c r="B21" t="s">
-        <v>2089</v>
+        <v>2075</v>
       </c>
       <c r="C21" t="s">
-        <v>2066</v>
+        <v>2056</v>
       </c>
       <c r="D21" t="s">
         <v>65</v>
@@ -26080,30 +31024,30 @@
         <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G21" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>2067</v>
+        <v>2855</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>2206</v>
+        <v>2190</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2158</v>
+        <v>2144</v>
       </c>
       <c r="B22" t="s">
         <v>988</v>
       </c>
       <c r="C22" t="s">
-        <v>2136</v>
+        <v>2122</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
@@ -26112,24 +31056,24 @@
         <v>66</v>
       </c>
       <c r="F22" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G22" t="s">
-        <v>2069</v>
+        <v>2057</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>2068</v>
+        <v>2854</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>2207</v>
+        <v>2191</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2159</v>
+        <v>2145</v>
       </c>
       <c r="B23" t="s">
         <v>888</v>
@@ -26144,30 +31088,30 @@
         <v>736</v>
       </c>
       <c r="F23" t="s">
+        <v>2050</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2059</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>2058</v>
       </c>
-      <c r="G23" t="s">
-        <v>2071</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>2070</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>2208</v>
+        <v>2192</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>2182</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2160</v>
+        <v>2146</v>
       </c>
       <c r="B24" t="s">
         <v>673</v>
       </c>
       <c r="C24" t="s">
-        <v>2137</v>
+        <v>2123</v>
       </c>
       <c r="D24" t="s">
         <v>561</v>
@@ -26176,30 +31120,30 @@
         <v>562</v>
       </c>
       <c r="F24" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G24" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>2072</v>
+        <v>2853</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>2209</v>
+        <v>2193</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2161</v>
+        <v>2147</v>
       </c>
       <c r="B25" t="s">
-        <v>2090</v>
+        <v>2076</v>
       </c>
       <c r="C25" t="s">
-        <v>2074</v>
+        <v>2061</v>
       </c>
       <c r="D25" t="s">
         <v>561</v>
@@ -26208,56 +31152,56 @@
         <v>562</v>
       </c>
       <c r="F25" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G25" t="s">
-        <v>2075</v>
+        <v>2062</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>2073</v>
+        <v>2060</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>2210</v>
+        <v>2194</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2162</v>
+        <v>2148</v>
       </c>
       <c r="B26" t="s">
         <v>717</v>
       </c>
       <c r="C26" t="s">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="D26" t="s">
         <v>1186</v>
       </c>
       <c r="E26" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="F26" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G26" t="s">
-        <v>2077</v>
+        <v>2064</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>1781</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>2211</v>
+        <v>2195</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2163</v>
+        <v>2149</v>
       </c>
       <c r="B27" t="s">
         <v>65</v>
@@ -26272,24 +31216,24 @@
         <v>935</v>
       </c>
       <c r="F27" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G27" t="s">
-        <v>2078</v>
+        <v>2065</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>932</v>
+        <v>2852</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>2212</v>
+        <v>2196</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2164</v>
+        <v>2150</v>
       </c>
       <c r="B28" t="s">
         <v>65</v>
@@ -26304,24 +31248,24 @@
         <v>935</v>
       </c>
       <c r="F28" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G28" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>2180</v>
+        <v>2851</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>2213</v>
+        <v>2197</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>2181</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2165</v>
+        <v>2151</v>
       </c>
       <c r="B29" t="s">
         <v>934</v>
@@ -26336,24 +31280,24 @@
         <v>66</v>
       </c>
       <c r="F29" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="G29" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1876</v>
+        <v>2850</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>2214</v>
+        <v>2198</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>2177</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2166</v>
+        <v>2152</v>
       </c>
       <c r="B30" t="s">
         <v>681</v>
@@ -26368,25 +31312,25 @@
         <v>790</v>
       </c>
       <c r="F30" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="G30" t="s">
-        <v>2079</v>
+        <v>2066</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>679</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>2215</v>
+        <v>2199</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>2176</v>
+        <v>2161</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2167</v>
+        <v>2153</v>
       </c>
       <c r="B31" t="s">
         <v>750</v>
@@ -26401,24 +31345,24 @@
         <v>66</v>
       </c>
       <c r="F31" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="G31" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>755</v>
+        <v>2849</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>2216</v>
+        <v>2200</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2168</v>
+        <v>2154</v>
       </c>
       <c r="B32" t="s">
         <v>888</v>
@@ -26433,19 +31377,19 @@
         <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="G32" t="s">
-        <v>2081</v>
+        <v>2068</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>2080</v>
+        <v>2067</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>2217</v>
+        <v>2201</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
     </row>
   </sheetData>
